--- a/data/input/Excel_files/Soortenlijst_Maatwerkgebieden.xlsx
+++ b/data/input/Excel_files/Soortenlijst_Maatwerkgebieden.xlsx
@@ -5780,7 +5780,7 @@
         <v>1</v>
       </c>
       <c r="L90" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="91" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -6616,7 +6616,7 @@
         <v>0</v>
       </c>
       <c r="L112" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="113" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -7072,7 +7072,7 @@
         <v>0</v>
       </c>
       <c r="L124" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="125" spans="1:12" x14ac:dyDescent="0.3">
@@ -12993,19 +12993,6 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:L277">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="Amfibieën"/>
-        <filter val="Dagvlinders"/>
-        <filter val="Libellen"/>
-        <filter val="Reptielen"/>
-        <filter val="Sprinkhanen"/>
-        <filter val="Vaatplanten"/>
-        <filter val="Vissen"/>
-        <filter val="Vogels"/>
-        <filter val="Zoogdieren"/>
-      </filters>
-    </filterColumn>
     <filterColumn colId="3">
       <filters>
         <filter val="ja"/>

--- a/data/input/Excel_files/Soortenlijst_Maatwerkgebieden.xlsx
+++ b/data/input/Excel_files/Soortenlijst_Maatwerkgebieden.xlsx
@@ -7110,7 +7110,7 @@
         <v>1</v>
       </c>
       <c r="L125" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="126" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -7186,7 +7186,7 @@
         <v>0</v>
       </c>
       <c r="L127" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="128" spans="1:12" x14ac:dyDescent="0.3">
@@ -7224,7 +7224,7 @@
         <v>0</v>
       </c>
       <c r="L128" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="129" spans="1:12" x14ac:dyDescent="0.3">

--- a/data/input/Excel_files/Soortenlijst_Maatwerkgebieden.xlsx
+++ b/data/input/Excel_files/Soortenlijst_Maatwerkgebieden.xlsx
@@ -7262,7 +7262,7 @@
         <v>1</v>
       </c>
       <c r="L129" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="130" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -8022,7 +8022,7 @@
         <v>1</v>
       </c>
       <c r="L149" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="150" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -12993,6 +12993,19 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:L277">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="Amfibieën"/>
+        <filter val="Dagvlinders"/>
+        <filter val="Libellen"/>
+        <filter val="Reptielen"/>
+        <filter val="Sprinkhanen"/>
+        <filter val="Vaatplanten"/>
+        <filter val="Vissen"/>
+        <filter val="Vogels"/>
+        <filter val="Zoogdieren"/>
+      </filters>
+    </filterColumn>
     <filterColumn colId="3">
       <filters>
         <filter val="ja"/>

--- a/data/input/Excel_files/Soortenlijst_Maatwerkgebieden.xlsx
+++ b/data/input/Excel_files/Soortenlijst_Maatwerkgebieden.xlsx
@@ -2401,7 +2401,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="2" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>20</v>
       </c>
@@ -2477,7 +2477,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="4" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>244</v>
       </c>
@@ -2515,7 +2515,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="5" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>244</v>
       </c>
@@ -2553,7 +2553,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="6" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>526</v>
       </c>
@@ -2591,7 +2591,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="7" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>363</v>
       </c>
@@ -2667,7 +2667,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="9" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>244</v>
       </c>
@@ -2743,7 +2743,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="11" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>244</v>
       </c>
@@ -2819,7 +2819,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="13" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>374</v>
       </c>
@@ -2857,7 +2857,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="14" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>244</v>
       </c>
@@ -2971,7 +2971,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="17" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>374</v>
       </c>
@@ -3047,7 +3047,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="19" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>526</v>
       </c>
@@ -3085,7 +3085,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="20" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>244</v>
       </c>
@@ -3123,7 +3123,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="21" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>20</v>
       </c>
@@ -3161,7 +3161,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="22" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>374</v>
       </c>
@@ -3275,7 +3275,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="25" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>244</v>
       </c>
@@ -3313,7 +3313,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="26" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>244</v>
       </c>
@@ -3351,7 +3351,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="27" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>244</v>
       </c>
@@ -3389,7 +3389,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="28" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>244</v>
       </c>
@@ -3465,7 +3465,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="30" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>20</v>
       </c>
@@ -3503,7 +3503,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="31" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>244</v>
       </c>
@@ -3541,7 +3541,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="32" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>244</v>
       </c>
@@ -3959,7 +3959,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="43" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>526</v>
       </c>
@@ -3997,7 +3997,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="44" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>374</v>
       </c>
@@ -4415,7 +4415,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="55" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>526</v>
       </c>
@@ -4567,7 +4567,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="59" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>244</v>
       </c>
@@ -4795,7 +4795,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="65" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>20</v>
       </c>
@@ -4871,7 +4871,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="67" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>20</v>
       </c>
@@ -5213,7 +5213,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="76" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>526</v>
       </c>
@@ -5517,7 +5517,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="84" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>526</v>
       </c>
@@ -5631,7 +5631,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="87" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>526</v>
       </c>
@@ -5897,7 +5897,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="94" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>244</v>
       </c>
@@ -6315,7 +6315,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="105" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>526</v>
       </c>
@@ -6353,7 +6353,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="106" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>526</v>
       </c>
@@ -6429,7 +6429,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="108" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>244</v>
       </c>
@@ -6505,7 +6505,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="110" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>20</v>
       </c>
@@ -6619,7 +6619,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="113" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>3</v>
       </c>
@@ -6657,7 +6657,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="114" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>244</v>
       </c>
@@ -6695,7 +6695,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="115" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>244</v>
       </c>
@@ -6733,7 +6733,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="116" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>244</v>
       </c>
@@ -6809,7 +6809,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="118" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>374</v>
       </c>
@@ -6885,7 +6885,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="120" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>244</v>
       </c>
@@ -6961,7 +6961,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="122" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>20</v>
       </c>
@@ -6999,7 +6999,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="123" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>244</v>
       </c>
@@ -7113,7 +7113,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="126" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>244</v>
       </c>
@@ -7265,7 +7265,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="130" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>244</v>
       </c>
@@ -7417,7 +7417,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="134" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>244</v>
       </c>
@@ -7455,7 +7455,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="135" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>20</v>
       </c>
@@ -7493,7 +7493,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="136" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>244</v>
       </c>
@@ -7531,7 +7531,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="137" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>244</v>
       </c>
@@ -7607,7 +7607,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="139" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>244</v>
       </c>
@@ -7645,7 +7645,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="140" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>526</v>
       </c>
@@ -7721,7 +7721,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="142" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>363</v>
       </c>
@@ -7759,7 +7759,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="143" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>244</v>
       </c>
@@ -7835,7 +7835,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="145" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>244</v>
       </c>
@@ -7873,7 +7873,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="146" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>244</v>
       </c>
@@ -7911,7 +7911,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="147" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>244</v>
       </c>
@@ -7949,7 +7949,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="148" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>244</v>
       </c>
@@ -8025,7 +8025,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="150" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>374</v>
       </c>
@@ -8063,7 +8063,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="151" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>244</v>
       </c>
@@ -8139,7 +8139,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="153" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>244</v>
       </c>
@@ -8250,10 +8250,10 @@
         <v>1</v>
       </c>
       <c r="L155" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="156" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="156" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>244</v>
       </c>
@@ -8291,7 +8291,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="157" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>526</v>
       </c>
@@ -8329,7 +8329,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="158" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>244</v>
       </c>
@@ -8367,7 +8367,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="159" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>230</v>
       </c>
@@ -8405,7 +8405,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="160" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>244</v>
       </c>
@@ -8443,7 +8443,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="161" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>244</v>
       </c>
@@ -8481,7 +8481,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="162" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>244</v>
       </c>
@@ -8519,7 +8519,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="163" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>244</v>
       </c>
@@ -8595,7 +8595,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="165" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>374</v>
       </c>
@@ -8633,7 +8633,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="166" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>526</v>
       </c>
@@ -8709,7 +8709,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="168" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>244</v>
       </c>
@@ -8747,7 +8747,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="169" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>374</v>
       </c>
@@ -8861,7 +8861,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="172" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>244</v>
       </c>
@@ -8975,7 +8975,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="175" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>244</v>
       </c>
@@ -9279,7 +9279,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="183" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>244</v>
       </c>
@@ -9393,7 +9393,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="186" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>244</v>
       </c>
@@ -9431,7 +9431,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="187" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>526</v>
       </c>
@@ -9469,7 +9469,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="188" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>526</v>
       </c>
@@ -9545,7 +9545,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="190" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>526</v>
       </c>
@@ -9583,7 +9583,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="191" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>363</v>
       </c>
@@ -9659,7 +9659,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="193" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>244</v>
       </c>
@@ -9697,7 +9697,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="194" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>244</v>
       </c>
@@ -9811,7 +9811,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="197" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>244</v>
       </c>
@@ -9925,7 +9925,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="200" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>374</v>
       </c>
@@ -9963,7 +9963,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="201" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>244</v>
       </c>
@@ -10001,7 +10001,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="202" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>244</v>
       </c>
@@ -10077,7 +10077,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="204" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>244</v>
       </c>
@@ -10229,7 +10229,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="208" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>244</v>
       </c>
@@ -10267,7 +10267,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="209" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>45</v>
       </c>
@@ -10305,7 +10305,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="210" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>3</v>
       </c>
@@ -10381,7 +10381,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="212" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>244</v>
       </c>
@@ -10419,7 +10419,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="213" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>244</v>
       </c>
@@ -10457,7 +10457,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="214" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>244</v>
       </c>
@@ -10571,7 +10571,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="217" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>526</v>
       </c>
@@ -10609,7 +10609,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="218" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>374</v>
       </c>
@@ -10685,7 +10685,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="220" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>244</v>
       </c>
@@ -10723,7 +10723,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="221" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>244</v>
       </c>
@@ -11065,7 +11065,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="230" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
         <v>363</v>
       </c>
@@ -11255,7 +11255,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="235" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
         <v>374</v>
       </c>
@@ -11369,7 +11369,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="238" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
         <v>244</v>
       </c>
@@ -11749,7 +11749,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="248" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
         <v>526</v>
       </c>
@@ -12091,7 +12091,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="257" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
         <v>244</v>
       </c>
@@ -12471,7 +12471,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="267" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
         <v>374</v>
       </c>
@@ -12623,7 +12623,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="271" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
         <v>48</v>
       </c>
@@ -12997,6 +12997,7 @@
       <filters>
         <filter val="Amfibieën"/>
         <filter val="Dagvlinders"/>
+        <filter val="Kevers"/>
         <filter val="Libellen"/>
         <filter val="Reptielen"/>
         <filter val="Sprinkhanen"/>
@@ -13004,21 +13005,6 @@
         <filter val="Vissen"/>
         <filter val="Vogels"/>
         <filter val="Zoogdieren"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="3">
-      <filters>
-        <filter val="ja"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="4">
-      <filters>
-        <filter val="nee"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="9">
-      <filters>
-        <filter val="1"/>
       </filters>
     </filterColumn>
   </autoFilter>

--- a/data/input/Excel_files/Soortenlijst_Maatwerkgebieden.xlsx
+++ b/data/input/Excel_files/Soortenlijst_Maatwerkgebieden.xlsx
@@ -2401,7 +2401,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>20</v>
       </c>
@@ -2477,7 +2477,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>244</v>
       </c>
@@ -2515,7 +2515,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>244</v>
       </c>
@@ -2553,7 +2553,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>526</v>
       </c>
@@ -2591,7 +2591,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>363</v>
       </c>
@@ -2667,7 +2667,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>244</v>
       </c>
@@ -2743,7 +2743,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>244</v>
       </c>
@@ -2819,7 +2819,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>374</v>
       </c>
@@ -2857,7 +2857,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>244</v>
       </c>
@@ -2971,7 +2971,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>374</v>
       </c>
@@ -3047,7 +3047,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>526</v>
       </c>
@@ -3085,7 +3085,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>244</v>
       </c>
@@ -3123,7 +3123,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>20</v>
       </c>
@@ -3275,7 +3275,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>244</v>
       </c>
@@ -3313,7 +3313,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>244</v>
       </c>
@@ -3351,7 +3351,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>244</v>
       </c>
@@ -3389,7 +3389,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>244</v>
       </c>
@@ -3465,7 +3465,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>20</v>
       </c>
@@ -3503,7 +3503,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>244</v>
       </c>
@@ -3541,7 +3541,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>244</v>
       </c>
@@ -3959,7 +3959,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>526</v>
       </c>
@@ -3997,7 +3997,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>374</v>
       </c>
@@ -4415,7 +4415,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>526</v>
       </c>
@@ -4567,7 +4567,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>244</v>
       </c>
@@ -4795,7 +4795,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>20</v>
       </c>
@@ -4871,7 +4871,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>20</v>
       </c>
@@ -5213,7 +5213,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>526</v>
       </c>
@@ -5517,7 +5517,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>526</v>
       </c>
@@ -5631,7 +5631,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>526</v>
       </c>
@@ -5897,7 +5897,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>244</v>
       </c>
@@ -6315,7 +6315,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="105" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>526</v>
       </c>
@@ -6353,7 +6353,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="106" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>526</v>
       </c>
@@ -6429,7 +6429,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="108" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>244</v>
       </c>
@@ -6505,7 +6505,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>20</v>
       </c>
@@ -6657,7 +6657,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="114" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>244</v>
       </c>
@@ -6695,7 +6695,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="115" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>244</v>
       </c>
@@ -6733,7 +6733,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="116" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>244</v>
       </c>
@@ -6885,7 +6885,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="120" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>244</v>
       </c>
@@ -6961,7 +6961,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="122" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>20</v>
       </c>
@@ -6999,7 +6999,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="123" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>244</v>
       </c>
@@ -7113,7 +7113,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="126" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>244</v>
       </c>
@@ -7265,7 +7265,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="130" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>244</v>
       </c>
@@ -7417,7 +7417,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="134" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>244</v>
       </c>
@@ -7455,7 +7455,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="135" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>20</v>
       </c>
@@ -7493,7 +7493,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="136" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>244</v>
       </c>
@@ -7531,7 +7531,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="137" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>244</v>
       </c>
@@ -7607,7 +7607,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="139" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>244</v>
       </c>
@@ -7645,7 +7645,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="140" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>526</v>
       </c>
@@ -7721,7 +7721,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="142" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>363</v>
       </c>
@@ -7759,7 +7759,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="143" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>244</v>
       </c>
@@ -7835,7 +7835,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="145" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>244</v>
       </c>
@@ -7873,7 +7873,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="146" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>244</v>
       </c>
@@ -7911,7 +7911,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="147" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>244</v>
       </c>
@@ -7949,7 +7949,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="148" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>244</v>
       </c>
@@ -8025,7 +8025,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="150" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>374</v>
       </c>
@@ -8063,7 +8063,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="151" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>244</v>
       </c>
@@ -8139,7 +8139,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="153" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>244</v>
       </c>
@@ -8253,7 +8253,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="156" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>244</v>
       </c>
@@ -8291,7 +8291,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="157" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>526</v>
       </c>
@@ -8329,7 +8329,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="158" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>244</v>
       </c>
@@ -8367,7 +8367,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="159" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>230</v>
       </c>
@@ -8405,7 +8405,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="160" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>244</v>
       </c>
@@ -8443,7 +8443,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="161" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>244</v>
       </c>
@@ -8481,7 +8481,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="162" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>244</v>
       </c>
@@ -8519,7 +8519,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="163" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>244</v>
       </c>
@@ -8592,10 +8592,10 @@
         <v>0</v>
       </c>
       <c r="L164" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="165" spans="1:12" x14ac:dyDescent="0.3">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="165" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>374</v>
       </c>
@@ -8633,7 +8633,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="166" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>526</v>
       </c>
@@ -8706,10 +8706,10 @@
         <v>0</v>
       </c>
       <c r="L167" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="168" spans="1:12" x14ac:dyDescent="0.3">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="168" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>244</v>
       </c>
@@ -8747,7 +8747,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="169" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>374</v>
       </c>
@@ -8820,7 +8820,7 @@
         <v>0</v>
       </c>
       <c r="L170" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="171" spans="1:12" x14ac:dyDescent="0.3">
@@ -8858,10 +8858,10 @@
         <v>0</v>
       </c>
       <c r="L171" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="172" spans="1:12" x14ac:dyDescent="0.3">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="172" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>244</v>
       </c>
@@ -8975,7 +8975,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="175" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>244</v>
       </c>
@@ -9279,7 +9279,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="183" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>244</v>
       </c>
@@ -9393,7 +9393,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="186" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>244</v>
       </c>
@@ -9431,7 +9431,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="187" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>526</v>
       </c>
@@ -9545,7 +9545,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="190" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>526</v>
       </c>
@@ -9583,7 +9583,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="191" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>363</v>
       </c>
@@ -9659,7 +9659,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="193" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>244</v>
       </c>
@@ -9697,7 +9697,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="194" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>244</v>
       </c>
@@ -9811,7 +9811,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="197" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>244</v>
       </c>
@@ -9925,7 +9925,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="200" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>374</v>
       </c>
@@ -9963,7 +9963,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="201" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>244</v>
       </c>
@@ -10001,7 +10001,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="202" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>244</v>
       </c>
@@ -10077,7 +10077,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="204" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>244</v>
       </c>
@@ -10229,7 +10229,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="208" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>244</v>
       </c>
@@ -10381,7 +10381,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="212" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>244</v>
       </c>
@@ -10419,7 +10419,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="213" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>244</v>
       </c>
@@ -10457,7 +10457,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="214" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>244</v>
       </c>
@@ -10571,7 +10571,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="217" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>526</v>
       </c>
@@ -10685,7 +10685,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="220" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>244</v>
       </c>
@@ -10723,7 +10723,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="221" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>244</v>
       </c>
@@ -11065,7 +11065,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="230" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
         <v>363</v>
       </c>
@@ -11255,7 +11255,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="235" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
         <v>374</v>
       </c>
@@ -11369,7 +11369,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="238" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
         <v>244</v>
       </c>
@@ -11749,7 +11749,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="248" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
         <v>526</v>
       </c>
@@ -12091,7 +12091,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="257" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
         <v>244</v>
       </c>
@@ -12471,7 +12471,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="267" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
         <v>374</v>
       </c>
@@ -12623,7 +12623,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="271" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
         <v>48</v>
       </c>
@@ -13005,6 +13005,16 @@
         <filter val="Vissen"/>
         <filter val="Vogels"/>
         <filter val="Zoogdieren"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="3">
+      <filters>
+        <filter val="ja"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="4">
+      <filters>
+        <filter val="nee"/>
       </filters>
     </filterColumn>
   </autoFilter>

--- a/data/input/Excel_files/Soortenlijst_Maatwerkgebieden.xlsx
+++ b/data/input/Excel_files/Soortenlijst_Maatwerkgebieden.xlsx
@@ -3161,7 +3161,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>374</v>
       </c>
@@ -6619,7 +6619,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="113" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>3</v>
       </c>
@@ -6809,7 +6809,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="118" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>374</v>
       </c>
@@ -8934,7 +8934,7 @@
         <v>1</v>
       </c>
       <c r="L173" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="174" spans="1:12" x14ac:dyDescent="0.3">
@@ -9048,7 +9048,7 @@
         <v>0</v>
       </c>
       <c r="L176" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="177" spans="1:12" x14ac:dyDescent="0.3">
@@ -9086,7 +9086,7 @@
         <v>0</v>
       </c>
       <c r="L177" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="178" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -9352,7 +9352,7 @@
         <v>0</v>
       </c>
       <c r="L184" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="185" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -9469,7 +9469,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="188" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>526</v>
       </c>
@@ -9542,7 +9542,7 @@
         <v>0</v>
       </c>
       <c r="L189" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="190" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -9656,7 +9656,7 @@
         <v>0</v>
       </c>
       <c r="L192" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="193" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -9884,7 +9884,7 @@
         <v>0</v>
       </c>
       <c r="L198" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="199" spans="1:12" x14ac:dyDescent="0.3">
@@ -10150,7 +10150,7 @@
         <v>1</v>
       </c>
       <c r="L205" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="206" spans="1:12" x14ac:dyDescent="0.3">
@@ -10188,7 +10188,7 @@
         <v>0</v>
       </c>
       <c r="L206" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="207" spans="1:12" x14ac:dyDescent="0.3">
@@ -10226,7 +10226,7 @@
         <v>0</v>
       </c>
       <c r="L207" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="208" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -10267,7 +10267,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="209" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>45</v>
       </c>
@@ -10305,7 +10305,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="210" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>3</v>
       </c>
@@ -10609,7 +10609,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="218" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>374</v>
       </c>
@@ -12993,20 +12993,6 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:L277">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="Amfibieën"/>
-        <filter val="Dagvlinders"/>
-        <filter val="Kevers"/>
-        <filter val="Libellen"/>
-        <filter val="Reptielen"/>
-        <filter val="Sprinkhanen"/>
-        <filter val="Vaatplanten"/>
-        <filter val="Vissen"/>
-        <filter val="Vogels"/>
-        <filter val="Zoogdieren"/>
-      </filters>
-    </filterColumn>
     <filterColumn colId="3">
       <filters>
         <filter val="ja"/>
@@ -13015,6 +13001,11 @@
     <filterColumn colId="4">
       <filters>
         <filter val="nee"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="9">
+      <filters>
+        <filter val="1"/>
       </filters>
     </filterColumn>
   </autoFilter>

--- a/data/input/Excel_files/Soortenlijst_Maatwerkgebieden.xlsx
+++ b/data/input/Excel_files/Soortenlijst_Maatwerkgebieden.xlsx
@@ -10378,7 +10378,7 @@
         <v>1</v>
       </c>
       <c r="L211" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="212" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -10530,7 +10530,7 @@
         <v>1</v>
       </c>
       <c r="L215" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="216" spans="1:12" x14ac:dyDescent="0.3">
@@ -11252,7 +11252,7 @@
         <v>1</v>
       </c>
       <c r="L234" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="235" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -12164,7 +12164,7 @@
         <v>0</v>
       </c>
       <c r="L258" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="259" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -12278,7 +12278,7 @@
         <v>1</v>
       </c>
       <c r="L261" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="262" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -12544,7 +12544,7 @@
         <v>1</v>
       </c>
       <c r="L268" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="269" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -12696,7 +12696,7 @@
         <v>0</v>
       </c>
       <c r="L272" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="273" spans="1:12" hidden="1" x14ac:dyDescent="0.3">

--- a/data/input/Excel_files/Soortenlijst_Maatwerkgebieden.xlsx
+++ b/data/input/Excel_files/Soortenlijst_Maatwerkgebieden.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4815" uniqueCount="613">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4801" uniqueCount="605">
   <si>
     <t>Taxonomische groep</t>
   </si>
@@ -1846,30 +1846,6 @@
   </si>
   <si>
     <t>Groep</t>
-  </si>
-  <si>
-    <t>Automatische soorten</t>
-  </si>
-  <si>
-    <t>Manuele soorten</t>
-  </si>
-  <si>
-    <t>Model al aanwezig</t>
-  </si>
-  <si>
-    <t>Model nog te maken</t>
-  </si>
-  <si>
-    <t>Totaal</t>
-  </si>
-  <si>
-    <t>Vleermuizen</t>
-  </si>
-  <si>
-    <t>Wilde Bijen</t>
-  </si>
-  <si>
-    <t>Planten</t>
   </si>
   <si>
     <t>Gedaan</t>
@@ -2348,7 +2324,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:L291"/>
+  <dimension ref="A1:L277"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.109375" bestFit="1" customWidth="1"/>
@@ -2398,7 +2374,7 @@
         <v>570</v>
       </c>
       <c r="L1" t="s">
-        <v>612</v>
+        <v>604</v>
       </c>
     </row>
     <row r="2" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -12887,108 +12863,6 @@
       </c>
       <c r="L277" t="s">
         <v>602</v>
-      </c>
-    </row>
-    <row r="280" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="C280" t="s">
-        <v>606</v>
-      </c>
-      <c r="D280" t="s">
-        <v>608</v>
-      </c>
-      <c r="E280">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="281" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="D281" t="s">
-        <v>604</v>
-      </c>
-      <c r="E281">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="282" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="D282" t="s">
-        <v>605</v>
-      </c>
-      <c r="E282">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="283" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="C283" t="s">
-        <v>607</v>
-      </c>
-      <c r="D283" t="s">
-        <v>608</v>
-      </c>
-      <c r="E283">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="284" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="D284" t="s">
-        <v>69</v>
-      </c>
-      <c r="E284">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="285" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="D285" t="s">
-        <v>363</v>
-      </c>
-      <c r="E285">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="286" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="D286" t="s">
-        <v>609</v>
-      </c>
-      <c r="E286">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="287" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="D287" t="s">
-        <v>610</v>
-      </c>
-      <c r="E287">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="288" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="D288" t="s">
-        <v>374</v>
-      </c>
-      <c r="E288">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="289" spans="4:5" x14ac:dyDescent="0.3">
-      <c r="D289" t="s">
-        <v>611</v>
-      </c>
-      <c r="E289">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="290" spans="4:5" x14ac:dyDescent="0.3">
-      <c r="D290" t="s">
-        <v>48</v>
-      </c>
-      <c r="E290">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="291" spans="4:5" x14ac:dyDescent="0.3">
-      <c r="D291" t="s">
-        <v>20</v>
-      </c>
-      <c r="E291">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/data/input/Excel_files/Soortenlijst_Maatwerkgebieden.xlsx
+++ b/data/input/Excel_files/Soortenlijst_Maatwerkgebieden.xlsx
@@ -2415,7 +2415,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>230</v>
       </c>
@@ -2681,7 +2681,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>374</v>
       </c>
@@ -2757,7 +2757,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>374</v>
       </c>
@@ -2871,7 +2871,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>20</v>
       </c>
@@ -2909,7 +2909,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>3</v>
       </c>
@@ -2985,7 +2985,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>374</v>
       </c>
@@ -3175,7 +3175,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>20</v>
       </c>
@@ -3213,7 +3213,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>374</v>
       </c>
@@ -3403,7 +3403,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>244</v>
       </c>
@@ -3631,7 +3631,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>526</v>
       </c>
@@ -3666,7 +3666,7 @@
         <v>1</v>
       </c>
       <c r="L35" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="36" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -4782,10 +4782,10 @@
         <v>32</v>
       </c>
       <c r="D65" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="E65" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="F65">
         <v>0</v>
@@ -4806,7 +4806,7 @@
         <v>1</v>
       </c>
       <c r="L65" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="66" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -5721,7 +5721,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>230</v>
       </c>
@@ -6557,7 +6557,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="112" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>363</v>
       </c>
@@ -6747,7 +6747,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="117" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>374</v>
       </c>
@@ -6823,7 +6823,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="119" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>374</v>
       </c>
@@ -6899,7 +6899,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="121" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>526</v>
       </c>
@@ -6934,7 +6934,7 @@
         <v>1</v>
       </c>
       <c r="L121" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="122" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -7013,7 +7013,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="124" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>3</v>
       </c>
@@ -7051,7 +7051,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="125" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>20</v>
       </c>
@@ -7165,7 +7165,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="128" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>374</v>
       </c>
@@ -7203,7 +7203,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="129" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>3</v>
       </c>
@@ -7355,7 +7355,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="133" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>374</v>
       </c>
@@ -7963,7 +7963,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="149" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>20</v>
       </c>
@@ -8077,7 +8077,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="152" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>374</v>
       </c>
@@ -8153,7 +8153,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="154" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>374</v>
       </c>
@@ -8191,7 +8191,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="155" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>374</v>
       </c>
@@ -8647,7 +8647,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="167" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>374</v>
       </c>
@@ -8761,7 +8761,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="170" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>374</v>
       </c>
@@ -8875,7 +8875,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="173" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>374</v>
       </c>
@@ -8913,7 +8913,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="174" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>374</v>
       </c>
@@ -8989,7 +8989,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="176" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>3</v>
       </c>
@@ -9027,7 +9027,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="177" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>374</v>
       </c>
@@ -9103,7 +9103,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="179" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>374</v>
       </c>
@@ -9293,7 +9293,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="184" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>374</v>
       </c>
@@ -9483,7 +9483,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="189" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>3</v>
       </c>
@@ -9711,7 +9711,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="195" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>374</v>
       </c>
@@ -9749,7 +9749,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="196" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>374</v>
       </c>
@@ -9863,7 +9863,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="199" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>374</v>
       </c>
@@ -10091,7 +10091,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="205" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>237</v>
       </c>
@@ -10319,7 +10319,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="211" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>3</v>
       </c>
@@ -10471,7 +10471,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="215" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>374</v>
       </c>
@@ -10509,7 +10509,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="216" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>526</v>
       </c>
@@ -10544,7 +10544,7 @@
         <v>1</v>
       </c>
       <c r="L216" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="217" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -11193,7 +11193,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="234" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
         <v>374</v>
       </c>
@@ -11269,7 +11269,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="236" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
         <v>374</v>
       </c>
@@ -12105,7 +12105,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="258" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
         <v>374</v>
       </c>
@@ -12219,7 +12219,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="261" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
         <v>237</v>
       </c>
@@ -12485,7 +12485,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="268" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
         <v>237</v>
       </c>
@@ -12599,7 +12599,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="271" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
         <v>48</v>
       </c>
@@ -12637,7 +12637,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="272" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
         <v>374</v>
       </c>
@@ -12789,7 +12789,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="276" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
         <v>374</v>
       </c>
@@ -12824,7 +12824,7 @@
         <v>0</v>
       </c>
       <c r="L276" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="277" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -12867,14 +12867,9 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:L277">
-    <filterColumn colId="3">
+    <filterColumn colId="0">
       <filters>
-        <filter val="ja"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="4">
-      <filters>
-        <filter val="nee"/>
+        <filter val="Libellen"/>
       </filters>
     </filterColumn>
     <filterColumn colId="9">

--- a/data/input/Excel_files/Soortenlijst_Maatwerkgebieden.xlsx
+++ b/data/input/Excel_files/Soortenlijst_Maatwerkgebieden.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4801" uniqueCount="605">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4807" uniqueCount="608">
   <si>
     <t>Taxonomische groep</t>
   </si>
@@ -1849,6 +1849,15 @@
   </si>
   <si>
     <t>Gedaan</t>
+  </si>
+  <si>
+    <t>niet nuttig voor Turnhout</t>
+  </si>
+  <si>
+    <t>Wel meenemen voor Heesbossen</t>
+  </si>
+  <si>
+    <t>nergens relevant</t>
   </si>
 </sst>
 </file>
@@ -2324,7 +2333,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:L277"/>
+  <dimension ref="A1:M277"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.109375" bestFit="1" customWidth="1"/>
@@ -2605,7 +2614,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>48</v>
       </c>
@@ -2947,7 +2956,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="17" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>374</v>
       </c>
@@ -2985,7 +2994,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="18" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>374</v>
       </c>
@@ -3023,7 +3032,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="19" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>526</v>
       </c>
@@ -3061,7 +3070,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="20" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>244</v>
       </c>
@@ -3099,7 +3108,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="21" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>20</v>
       </c>
@@ -3137,7 +3146,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="22" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>374</v>
       </c>
@@ -3175,7 +3184,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="23" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>20</v>
       </c>
@@ -3213,7 +3222,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="24" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>374</v>
       </c>
@@ -3251,7 +3260,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="25" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>244</v>
       </c>
@@ -3289,7 +3298,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="26" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>244</v>
       </c>
@@ -3327,7 +3336,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="27" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>244</v>
       </c>
@@ -3365,7 +3374,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="28" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>244</v>
       </c>
@@ -3403,7 +3412,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="29" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>244</v>
       </c>
@@ -3441,7 +3450,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="30" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>20</v>
       </c>
@@ -3479,7 +3488,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="31" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>244</v>
       </c>
@@ -3517,7 +3526,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="32" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>244</v>
       </c>
@@ -3553,6 +3562,9 @@
       </c>
       <c r="L32" t="s">
         <v>602</v>
+      </c>
+      <c r="M32" t="s">
+        <v>607</v>
       </c>
     </row>
     <row r="33" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -4163,7 +4175,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="49" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>69</v>
       </c>
@@ -4201,7 +4213,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="50" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>69</v>
       </c>
@@ -4239,7 +4251,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="51" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>453</v>
       </c>
@@ -4277,7 +4289,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="52" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>453</v>
       </c>
@@ -4315,7 +4327,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="53" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>69</v>
       </c>
@@ -4353,7 +4365,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="54" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>69</v>
       </c>
@@ -4391,7 +4403,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="55" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>526</v>
       </c>
@@ -4429,7 +4441,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="56" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>69</v>
       </c>
@@ -4467,7 +4479,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="57" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>69</v>
       </c>
@@ -4505,7 +4517,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="58" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>453</v>
       </c>
@@ -4543,7 +4555,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="59" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>244</v>
       </c>
@@ -4580,8 +4592,11 @@
       <c r="L59" t="s">
         <v>602</v>
       </c>
-    </row>
-    <row r="60" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+      <c r="M59" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>69</v>
       </c>
@@ -4619,7 +4634,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="61" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>69</v>
       </c>
@@ -4657,7 +4672,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="62" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>69</v>
       </c>
@@ -4695,7 +4710,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="63" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>69</v>
       </c>
@@ -4733,7 +4748,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="64" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>69</v>
       </c>
@@ -5151,7 +5166,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>48</v>
       </c>
@@ -6595,7 +6610,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="113" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>3</v>
       </c>
@@ -6633,7 +6648,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="114" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>244</v>
       </c>
@@ -6671,7 +6686,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="115" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>244</v>
       </c>
@@ -6709,7 +6724,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="116" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>244</v>
       </c>
@@ -6747,7 +6762,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="117" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>374</v>
       </c>
@@ -6785,7 +6800,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="118" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>374</v>
       </c>
@@ -6823,7 +6838,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="119" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>374</v>
       </c>
@@ -6861,7 +6876,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="120" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>244</v>
       </c>
@@ -6898,8 +6913,11 @@
       <c r="L120" t="s">
         <v>602</v>
       </c>
-    </row>
-    <row r="121" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+      <c r="M120" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="121" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>526</v>
       </c>
@@ -6937,7 +6955,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="122" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>20</v>
       </c>
@@ -6975,7 +6993,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="123" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>244</v>
       </c>
@@ -7013,7 +7031,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="124" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>3</v>
       </c>
@@ -7051,7 +7069,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="125" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>20</v>
       </c>
@@ -7089,7 +7107,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="126" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>244</v>
       </c>
@@ -7127,7 +7145,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="127" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>48</v>
       </c>
@@ -7165,7 +7183,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="128" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>374</v>
       </c>
@@ -7203,7 +7221,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="129" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>3</v>
       </c>
@@ -7241,7 +7259,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="130" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>244</v>
       </c>
@@ -7278,8 +7296,11 @@
       <c r="L130" t="s">
         <v>602</v>
       </c>
-    </row>
-    <row r="131" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+      <c r="M130" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="131" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>69</v>
       </c>
@@ -7317,7 +7338,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="132" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>453</v>
       </c>
@@ -7355,7 +7376,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="133" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>374</v>
       </c>
@@ -7393,7 +7414,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="134" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>244</v>
       </c>
@@ -7431,7 +7452,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="135" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>20</v>
       </c>
@@ -7469,7 +7490,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="136" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>244</v>
       </c>
@@ -7507,7 +7528,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="137" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>244</v>
       </c>
@@ -7544,8 +7565,11 @@
       <c r="L137" t="s">
         <v>602</v>
       </c>
-    </row>
-    <row r="138" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+      <c r="M137" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="138" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>69</v>
       </c>
@@ -7583,7 +7607,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="139" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>244</v>
       </c>
@@ -7621,7 +7645,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="140" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>526</v>
       </c>
@@ -7659,7 +7683,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="141" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>453</v>
       </c>
@@ -7697,7 +7721,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="142" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>363</v>
       </c>
@@ -7735,7 +7759,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="143" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>244</v>
       </c>
@@ -7773,7 +7797,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="144" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>453</v>
       </c>
@@ -8533,7 +8557,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="164" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>48</v>
       </c>
@@ -8799,7 +8823,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="171" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>48</v>
       </c>
@@ -9597,7 +9621,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="192" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>48</v>
       </c>
@@ -9825,7 +9849,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="198" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>48</v>
       </c>
@@ -10091,7 +10115,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="205" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>237</v>
       </c>
@@ -10129,7 +10153,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="206" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>48</v>
       </c>
@@ -10167,7 +10191,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="207" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>48</v>
       </c>
@@ -10243,7 +10267,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="209" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>45</v>
       </c>
@@ -10281,7 +10305,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="210" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>3</v>
       </c>
@@ -10319,7 +10343,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="211" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>3</v>
       </c>
@@ -10357,7 +10381,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="212" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>244</v>
       </c>
@@ -10395,7 +10419,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="213" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>244</v>
       </c>
@@ -10433,7 +10457,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="214" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>244</v>
       </c>
@@ -10471,7 +10495,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="215" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>374</v>
       </c>
@@ -10509,7 +10533,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="216" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>526</v>
       </c>
@@ -10547,7 +10571,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="217" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>526</v>
       </c>
@@ -10585,7 +10609,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="218" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>374</v>
       </c>
@@ -10623,7 +10647,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="219" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>69</v>
       </c>
@@ -10661,7 +10685,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="220" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>244</v>
       </c>
@@ -10698,8 +10722,11 @@
       <c r="L220" t="s">
         <v>602</v>
       </c>
-    </row>
-    <row r="221" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+      <c r="M220" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="221" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>244</v>
       </c>
@@ -10737,7 +10764,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="222" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>69</v>
       </c>
@@ -10775,7 +10802,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="223" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>69</v>
       </c>
@@ -10813,7 +10840,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="224" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>69</v>
       </c>
@@ -12219,7 +12246,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="261" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
         <v>237</v>
       </c>
@@ -12485,7 +12512,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="268" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
         <v>237</v>
       </c>
@@ -12599,7 +12626,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="271" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
         <v>48</v>
       </c>
@@ -12869,12 +12896,17 @@
   <autoFilter ref="A1:L277">
     <filterColumn colId="0">
       <filters>
-        <filter val="Libellen"/>
+        <filter val="Sprinkhanen"/>
       </filters>
     </filterColumn>
-    <filterColumn colId="9">
+    <filterColumn colId="3">
       <filters>
-        <filter val="1"/>
+        <filter val="ja"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="4">
+      <filters>
+        <filter val="nee"/>
       </filters>
     </filterColumn>
   </autoFilter>

--- a/data/input/Excel_files/Soortenlijst_Maatwerkgebieden.xlsx
+++ b/data/input/Excel_files/Soortenlijst_Maatwerkgebieden.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4807" uniqueCount="608">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4801" uniqueCount="605">
   <si>
     <t>Taxonomische groep</t>
   </si>
@@ -1849,15 +1849,6 @@
   </si>
   <si>
     <t>Gedaan</t>
-  </si>
-  <si>
-    <t>niet nuttig voor Turnhout</t>
-  </si>
-  <si>
-    <t>Wel meenemen voor Heesbossen</t>
-  </si>
-  <si>
-    <t>nergens relevant</t>
   </si>
 </sst>
 </file>
@@ -2333,7 +2324,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:M277"/>
+  <dimension ref="A1:L277"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.109375" bestFit="1" customWidth="1"/>
@@ -2725,7 +2716,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="11" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -2956,7 +2947,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="17" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>374</v>
       </c>
@@ -2994,7 +2985,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="18" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>374</v>
       </c>
@@ -3032,7 +3023,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="19" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>526</v>
       </c>
@@ -3070,7 +3061,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="20" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>244</v>
       </c>
@@ -3108,7 +3099,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="21" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>20</v>
       </c>
@@ -3146,7 +3137,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="22" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>374</v>
       </c>
@@ -3184,7 +3175,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="23" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>20</v>
       </c>
@@ -3222,7 +3213,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="24" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>374</v>
       </c>
@@ -3260,7 +3251,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="25" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>244</v>
       </c>
@@ -3298,7 +3289,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="26" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>244</v>
       </c>
@@ -3336,7 +3327,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="27" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>244</v>
       </c>
@@ -3374,7 +3365,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="28" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>244</v>
       </c>
@@ -3412,7 +3403,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="29" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>244</v>
       </c>
@@ -3450,7 +3441,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="30" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>20</v>
       </c>
@@ -3488,7 +3479,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="31" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>244</v>
       </c>
@@ -3526,7 +3517,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="32" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>244</v>
       </c>
@@ -3537,10 +3528,10 @@
         <v>270</v>
       </c>
       <c r="D32" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="E32" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="F32">
         <v>1</v>
@@ -3561,10 +3552,7 @@
         <v>0</v>
       </c>
       <c r="L32" t="s">
-        <v>602</v>
-      </c>
-      <c r="M32" t="s">
-        <v>607</v>
+        <v>601</v>
       </c>
     </row>
     <row r="33" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -4175,7 +4163,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="49" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>69</v>
       </c>
@@ -4213,7 +4201,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="50" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>69</v>
       </c>
@@ -4251,7 +4239,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="51" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>453</v>
       </c>
@@ -4289,7 +4277,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="52" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>453</v>
       </c>
@@ -4327,7 +4315,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="53" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>69</v>
       </c>
@@ -4365,7 +4353,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="54" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>69</v>
       </c>
@@ -4403,7 +4391,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="55" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>526</v>
       </c>
@@ -4441,7 +4429,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="56" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>69</v>
       </c>
@@ -4479,7 +4467,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="57" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>69</v>
       </c>
@@ -4517,7 +4505,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="58" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>453</v>
       </c>
@@ -4555,7 +4543,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="59" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>244</v>
       </c>
@@ -4566,10 +4554,10 @@
         <v>272</v>
       </c>
       <c r="D59" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="E59" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="F59">
         <v>0</v>
@@ -4590,13 +4578,10 @@
         <v>1</v>
       </c>
       <c r="L59" t="s">
-        <v>602</v>
-      </c>
-      <c r="M59" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="60" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>69</v>
       </c>
@@ -4634,7 +4619,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="61" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>69</v>
       </c>
@@ -4672,7 +4657,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="62" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>69</v>
       </c>
@@ -4710,7 +4695,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="63" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>69</v>
       </c>
@@ -4748,7 +4733,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="64" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>69</v>
       </c>
@@ -6610,7 +6595,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="113" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>3</v>
       </c>
@@ -6648,7 +6633,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="114" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>244</v>
       </c>
@@ -6686,7 +6671,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="115" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>244</v>
       </c>
@@ -6724,7 +6709,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="116" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>244</v>
       </c>
@@ -6762,7 +6747,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="117" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>374</v>
       </c>
@@ -6797,10 +6782,10 @@
         <v>0</v>
       </c>
       <c r="L117" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="118" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="118" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>374</v>
       </c>
@@ -6838,7 +6823,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="119" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>374</v>
       </c>
@@ -6876,7 +6861,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="120" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>244</v>
       </c>
@@ -6887,10 +6872,10 @@
         <v>284</v>
       </c>
       <c r="D120" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="E120" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="F120">
         <v>0</v>
@@ -6911,13 +6896,10 @@
         <v>1</v>
       </c>
       <c r="L120" t="s">
-        <v>602</v>
-      </c>
-      <c r="M120" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="121" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="121" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>526</v>
       </c>
@@ -6955,7 +6937,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="122" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>20</v>
       </c>
@@ -6993,7 +6975,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="123" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>244</v>
       </c>
@@ -7031,7 +7013,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="124" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>3</v>
       </c>
@@ -7069,7 +7051,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="125" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>20</v>
       </c>
@@ -7107,7 +7089,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="126" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>244</v>
       </c>
@@ -7145,7 +7127,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="127" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>48</v>
       </c>
@@ -7183,7 +7165,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="128" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>374</v>
       </c>
@@ -7221,7 +7203,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="129" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>3</v>
       </c>
@@ -7259,7 +7241,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="130" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>244</v>
       </c>
@@ -7270,10 +7252,10 @@
         <v>290</v>
       </c>
       <c r="D130" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="E130" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="F130">
         <v>0</v>
@@ -7294,13 +7276,10 @@
         <v>1</v>
       </c>
       <c r="L130" t="s">
-        <v>602</v>
-      </c>
-      <c r="M130" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="131" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="131" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>69</v>
       </c>
@@ -7338,7 +7317,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="132" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>453</v>
       </c>
@@ -7376,7 +7355,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="133" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>374</v>
       </c>
@@ -7414,7 +7393,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="134" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>244</v>
       </c>
@@ -7452,7 +7431,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="135" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>20</v>
       </c>
@@ -7490,7 +7469,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="136" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>244</v>
       </c>
@@ -7528,7 +7507,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="137" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>244</v>
       </c>
@@ -7539,10 +7518,10 @@
         <v>296</v>
       </c>
       <c r="D137" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="E137" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="F137">
         <v>1</v>
@@ -7563,13 +7542,10 @@
         <v>0</v>
       </c>
       <c r="L137" t="s">
-        <v>602</v>
-      </c>
-      <c r="M137" t="s">
-        <v>606</v>
-      </c>
-    </row>
-    <row r="138" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="138" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>69</v>
       </c>
@@ -7607,7 +7583,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="139" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>244</v>
       </c>
@@ -7645,7 +7621,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="140" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>526</v>
       </c>
@@ -7683,7 +7659,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="141" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>453</v>
       </c>
@@ -7721,7 +7697,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="142" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>363</v>
       </c>
@@ -7759,7 +7735,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="143" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>244</v>
       </c>
@@ -7797,7 +7773,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="144" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>453</v>
       </c>
@@ -8101,7 +8077,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="152" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>374</v>
       </c>
@@ -8177,7 +8153,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="154" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>374</v>
       </c>
@@ -8937,7 +8913,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="174" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>374</v>
       </c>
@@ -9127,7 +9103,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="179" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>374</v>
       </c>
@@ -9735,7 +9711,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="195" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>374</v>
       </c>
@@ -9773,7 +9749,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="196" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>374</v>
       </c>
@@ -9822,10 +9798,10 @@
         <v>340</v>
       </c>
       <c r="D197" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="E197" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="F197">
         <v>0</v>
@@ -9846,7 +9822,7 @@
         <v>1</v>
       </c>
       <c r="L197" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="198" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -9887,7 +9863,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="199" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>374</v>
       </c>
@@ -10115,7 +10091,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="205" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>237</v>
       </c>
@@ -10267,7 +10243,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="209" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>45</v>
       </c>
@@ -10305,7 +10281,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="210" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>3</v>
       </c>
@@ -10343,7 +10319,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="211" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>3</v>
       </c>
@@ -10381,7 +10357,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="212" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>244</v>
       </c>
@@ -10419,7 +10395,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="213" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>244</v>
       </c>
@@ -10457,7 +10433,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="214" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>244</v>
       </c>
@@ -10495,7 +10471,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="215" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>374</v>
       </c>
@@ -10533,7 +10509,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="216" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>526</v>
       </c>
@@ -10571,7 +10547,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="217" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>526</v>
       </c>
@@ -10609,7 +10585,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="218" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>374</v>
       </c>
@@ -10647,7 +10623,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="219" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>69</v>
       </c>
@@ -10685,7 +10661,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="220" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>244</v>
       </c>
@@ -10696,10 +10672,10 @@
         <v>356</v>
       </c>
       <c r="D220" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="E220" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="F220">
         <v>0</v>
@@ -10720,13 +10696,10 @@
         <v>1</v>
       </c>
       <c r="L220" t="s">
-        <v>602</v>
-      </c>
-      <c r="M220" t="s">
-        <v>607</v>
-      </c>
-    </row>
-    <row r="221" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="221" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>244</v>
       </c>
@@ -10764,7 +10737,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="222" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>69</v>
       </c>
@@ -10802,7 +10775,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="223" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>69</v>
       </c>
@@ -10840,7 +10813,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="224" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>69</v>
       </c>
@@ -11296,7 +11269,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="236" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
         <v>374</v>
       </c>
@@ -12246,7 +12219,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="261" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
         <v>237</v>
       </c>
@@ -12512,7 +12485,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="268" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
         <v>237</v>
       </c>
@@ -12894,17 +12867,22 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:L277">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="Sprinkhanen"/>
-      </filters>
-    </filterColumn>
     <filterColumn colId="3">
       <filters>
         <filter val="ja"/>
       </filters>
     </filterColumn>
     <filterColumn colId="4">
+      <filters>
+        <filter val="nee"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="9">
+      <filters>
+        <filter val="1"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="11">
       <filters>
         <filter val="nee"/>
       </filters>

--- a/data/input/Excel_files/Soortenlijst_Maatwerkgebieden.xlsx
+++ b/data/input/Excel_files/Soortenlijst_Maatwerkgebieden.xlsx
@@ -1737,9 +1737,6 @@
     <t>Myotis daubentonii</t>
   </si>
   <si>
-    <t>Model?</t>
-  </si>
-  <si>
     <t>TurnhoutsVennegebied</t>
   </si>
   <si>
@@ -1836,9 +1833,6 @@
     <t>zomertortel</t>
   </si>
   <si>
-    <t>Automatisch?</t>
-  </si>
-  <si>
     <t>ja</t>
   </si>
   <si>
@@ -1849,6 +1843,12 @@
   </si>
   <si>
     <t>Gedaan</t>
+  </si>
+  <si>
+    <t>Automatisch</t>
+  </si>
+  <si>
+    <t>Model</t>
   </si>
 </sst>
 </file>
@@ -2341,7 +2341,7 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
@@ -2350,31 +2350,31 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
+        <v>604</v>
+      </c>
+      <c r="E1" t="s">
+        <v>603</v>
+      </c>
+      <c r="F1" t="s">
+        <v>570</v>
+      </c>
+      <c r="G1" t="s">
+        <v>571</v>
+      </c>
+      <c r="H1" t="s">
+        <v>568</v>
+      </c>
+      <c r="I1" t="s">
+        <v>572</v>
+      </c>
+      <c r="J1" t="s">
         <v>567</v>
       </c>
-      <c r="E1" t="s">
-        <v>600</v>
-      </c>
-      <c r="F1" t="s">
-        <v>571</v>
-      </c>
-      <c r="G1" t="s">
-        <v>572</v>
-      </c>
-      <c r="H1" t="s">
+      <c r="K1" t="s">
         <v>569</v>
       </c>
-      <c r="I1" t="s">
-        <v>573</v>
-      </c>
-      <c r="J1" t="s">
-        <v>568</v>
-      </c>
-      <c r="K1" t="s">
-        <v>570</v>
-      </c>
       <c r="L1" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
     </row>
     <row r="2" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -2388,10 +2388,10 @@
         <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E2" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="F2">
         <v>1</v>
@@ -2412,7 +2412,7 @@
         <v>1</v>
       </c>
       <c r="L2" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="3" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -2426,10 +2426,10 @@
         <v>232</v>
       </c>
       <c r="D3" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E3" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F3">
         <v>1</v>
@@ -2450,7 +2450,7 @@
         <v>0</v>
       </c>
       <c r="L3" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="4" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -2464,10 +2464,10 @@
         <v>246</v>
       </c>
       <c r="D4" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E4" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -2488,7 +2488,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="5" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -2502,10 +2502,10 @@
         <v>248</v>
       </c>
       <c r="D5" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E5" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -2526,7 +2526,7 @@
         <v>0</v>
       </c>
       <c r="L5" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="6" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -2540,10 +2540,10 @@
         <v>528</v>
       </c>
       <c r="D6" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E6" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -2564,7 +2564,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="7" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -2578,10 +2578,10 @@
         <v>365</v>
       </c>
       <c r="D7" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E7" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -2602,7 +2602,7 @@
         <v>1</v>
       </c>
       <c r="L7" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="8" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -2616,10 +2616,10 @@
         <v>50</v>
       </c>
       <c r="D8" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E8" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -2640,7 +2640,7 @@
         <v>1</v>
       </c>
       <c r="L8" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="9" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -2654,10 +2654,10 @@
         <v>250</v>
       </c>
       <c r="D9" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E9" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="F9">
         <v>1</v>
@@ -2678,7 +2678,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="10" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -2692,10 +2692,10 @@
         <v>376</v>
       </c>
       <c r="D10" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E10" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -2716,7 +2716,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="11" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -2730,10 +2730,10 @@
         <v>252</v>
       </c>
       <c r="D11" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E11" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -2754,7 +2754,7 @@
         <v>1</v>
       </c>
       <c r="L11" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="12" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -2768,10 +2768,10 @@
         <v>378</v>
       </c>
       <c r="D12" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E12" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F12">
         <v>1</v>
@@ -2792,10 +2792,10 @@
         <v>0</v>
       </c>
       <c r="L12" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>374</v>
       </c>
@@ -2806,10 +2806,10 @@
         <v>380</v>
       </c>
       <c r="D13" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E13" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F13">
         <v>0</v>
@@ -2830,7 +2830,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="14" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -2844,10 +2844,10 @@
         <v>254</v>
       </c>
       <c r="D14" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E14" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -2868,7 +2868,7 @@
         <v>1</v>
       </c>
       <c r="L14" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="15" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -2882,10 +2882,10 @@
         <v>24</v>
       </c>
       <c r="D15" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E15" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F15">
         <v>1</v>
@@ -2906,7 +2906,7 @@
         <v>1</v>
       </c>
       <c r="L15" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="16" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -2920,10 +2920,10 @@
         <v>7</v>
       </c>
       <c r="D16" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E16" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F16">
         <v>1</v>
@@ -2944,7 +2944,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="17" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -2958,10 +2958,10 @@
         <v>382</v>
       </c>
       <c r="D17" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E17" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="F17">
         <v>0</v>
@@ -2982,7 +2982,7 @@
         <v>0</v>
       </c>
       <c r="L17" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="18" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -2996,10 +2996,10 @@
         <v>384</v>
       </c>
       <c r="D18" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E18" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -3020,7 +3020,7 @@
         <v>0</v>
       </c>
       <c r="L18" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="19" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -3034,10 +3034,10 @@
         <v>532</v>
       </c>
       <c r="D19" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E19" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F19">
         <v>0</v>
@@ -3058,7 +3058,7 @@
         <v>0</v>
       </c>
       <c r="L19" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="20" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -3072,10 +3072,10 @@
         <v>256</v>
       </c>
       <c r="D20" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E20" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="F20">
         <v>0</v>
@@ -3096,7 +3096,7 @@
         <v>0</v>
       </c>
       <c r="L20" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="21" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -3110,10 +3110,10 @@
         <v>26</v>
       </c>
       <c r="D21" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E21" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="F21">
         <v>1</v>
@@ -3134,7 +3134,7 @@
         <v>1</v>
       </c>
       <c r="L21" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="22" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -3148,10 +3148,10 @@
         <v>390</v>
       </c>
       <c r="D22" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E22" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F22">
         <v>0</v>
@@ -3172,7 +3172,7 @@
         <v>1</v>
       </c>
       <c r="L22" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
     </row>
     <row r="23" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -3186,10 +3186,10 @@
         <v>28</v>
       </c>
       <c r="D23" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E23" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F23">
         <v>1</v>
@@ -3210,7 +3210,7 @@
         <v>1</v>
       </c>
       <c r="L23" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="24" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -3224,10 +3224,10 @@
         <v>386</v>
       </c>
       <c r="D24" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E24" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F24">
         <v>1</v>
@@ -3248,7 +3248,7 @@
         <v>0</v>
       </c>
       <c r="L24" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="25" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -3262,10 +3262,10 @@
         <v>258</v>
       </c>
       <c r="D25" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E25" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="F25">
         <v>1</v>
@@ -3286,7 +3286,7 @@
         <v>0</v>
       </c>
       <c r="L25" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="26" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -3300,10 +3300,10 @@
         <v>260</v>
       </c>
       <c r="D26" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E26" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="F26">
         <v>0</v>
@@ -3324,7 +3324,7 @@
         <v>1</v>
       </c>
       <c r="L26" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="27" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -3338,10 +3338,10 @@
         <v>262</v>
       </c>
       <c r="D27" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E27" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="F27">
         <v>1</v>
@@ -3362,7 +3362,7 @@
         <v>0</v>
       </c>
       <c r="L27" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="28" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -3376,10 +3376,10 @@
         <v>264</v>
       </c>
       <c r="D28" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E28" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="F28">
         <v>1</v>
@@ -3400,7 +3400,7 @@
         <v>0</v>
       </c>
       <c r="L28" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="29" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -3414,10 +3414,10 @@
         <v>266</v>
       </c>
       <c r="D29" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E29" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F29">
         <v>1</v>
@@ -3438,7 +3438,7 @@
         <v>0</v>
       </c>
       <c r="L29" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="30" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -3452,10 +3452,10 @@
         <v>30</v>
       </c>
       <c r="D30" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E30" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="F30">
         <v>0</v>
@@ -3476,7 +3476,7 @@
         <v>1</v>
       </c>
       <c r="L30" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="31" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -3490,10 +3490,10 @@
         <v>268</v>
       </c>
       <c r="D31" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E31" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="F31">
         <v>1</v>
@@ -3514,7 +3514,7 @@
         <v>0</v>
       </c>
       <c r="L31" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="32" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -3528,10 +3528,10 @@
         <v>270</v>
       </c>
       <c r="D32" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E32" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="F32">
         <v>1</v>
@@ -3552,7 +3552,7 @@
         <v>0</v>
       </c>
       <c r="L32" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="33" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -3566,10 +3566,10 @@
         <v>71</v>
       </c>
       <c r="D33" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E33" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F33">
         <v>0</v>
@@ -3590,7 +3590,7 @@
         <v>1</v>
       </c>
       <c r="L33" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="34" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -3604,10 +3604,10 @@
         <v>73</v>
       </c>
       <c r="D34" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E34" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F34">
         <v>1</v>
@@ -3628,7 +3628,7 @@
         <v>1</v>
       </c>
       <c r="L34" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="35" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -3642,10 +3642,10 @@
         <v>534</v>
       </c>
       <c r="D35" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E35" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F35">
         <v>0</v>
@@ -3666,7 +3666,7 @@
         <v>1</v>
       </c>
       <c r="L35" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="36" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -3680,10 +3680,10 @@
         <v>455</v>
       </c>
       <c r="D36" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E36" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F36">
         <v>1</v>
@@ -3704,7 +3704,7 @@
         <v>1</v>
       </c>
       <c r="L36" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="37" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -3718,10 +3718,10 @@
         <v>75</v>
       </c>
       <c r="D37" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E37" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F37">
         <v>1</v>
@@ -3742,7 +3742,7 @@
         <v>1</v>
       </c>
       <c r="L37" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="38" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -3756,10 +3756,10 @@
         <v>77</v>
       </c>
       <c r="D38" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E38" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F38">
         <v>1</v>
@@ -3780,7 +3780,7 @@
         <v>1</v>
       </c>
       <c r="L38" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="39" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -3794,10 +3794,10 @@
         <v>79</v>
       </c>
       <c r="D39" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E39" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F39">
         <v>1</v>
@@ -3818,7 +3818,7 @@
         <v>1</v>
       </c>
       <c r="L39" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="40" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -3832,10 +3832,10 @@
         <v>457</v>
       </c>
       <c r="D40" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E40" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F40">
         <v>0</v>
@@ -3856,7 +3856,7 @@
         <v>1</v>
       </c>
       <c r="L40" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="41" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -3870,10 +3870,10 @@
         <v>81</v>
       </c>
       <c r="D41" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E41" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F41">
         <v>0</v>
@@ -3894,7 +3894,7 @@
         <v>0</v>
       </c>
       <c r="L41" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="42" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -3908,10 +3908,10 @@
         <v>83</v>
       </c>
       <c r="D42" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E42" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F42">
         <v>0</v>
@@ -3932,7 +3932,7 @@
         <v>0</v>
       </c>
       <c r="L42" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="43" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -3946,10 +3946,10 @@
         <v>530</v>
       </c>
       <c r="D43" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E43" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F43">
         <v>0</v>
@@ -3970,7 +3970,7 @@
         <v>1</v>
       </c>
       <c r="L43" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="44" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -3984,10 +3984,10 @@
         <v>388</v>
       </c>
       <c r="D44" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E44" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="F44">
         <v>0</v>
@@ -4008,7 +4008,7 @@
         <v>1</v>
       </c>
       <c r="L44" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="45" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -4022,10 +4022,10 @@
         <v>85</v>
       </c>
       <c r="D45" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E45" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F45">
         <v>0</v>
@@ -4046,7 +4046,7 @@
         <v>1</v>
       </c>
       <c r="L45" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="46" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -4060,10 +4060,10 @@
         <v>87</v>
       </c>
       <c r="D46" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E46" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F46">
         <v>1</v>
@@ -4084,7 +4084,7 @@
         <v>1</v>
       </c>
       <c r="L46" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="47" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -4098,10 +4098,10 @@
         <v>89</v>
       </c>
       <c r="D47" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E47" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F47">
         <v>1</v>
@@ -4122,7 +4122,7 @@
         <v>1</v>
       </c>
       <c r="L47" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="48" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -4136,10 +4136,10 @@
         <v>91</v>
       </c>
       <c r="D48" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E48" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F48">
         <v>1</v>
@@ -4160,7 +4160,7 @@
         <v>1</v>
       </c>
       <c r="L48" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="49" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -4174,10 +4174,10 @@
         <v>93</v>
       </c>
       <c r="D49" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E49" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F49">
         <v>1</v>
@@ -4198,7 +4198,7 @@
         <v>1</v>
       </c>
       <c r="L49" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="50" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -4212,10 +4212,10 @@
         <v>95</v>
       </c>
       <c r="D50" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E50" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F50">
         <v>1</v>
@@ -4236,7 +4236,7 @@
         <v>1</v>
       </c>
       <c r="L50" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="51" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -4250,10 +4250,10 @@
         <v>459</v>
       </c>
       <c r="D51" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E51" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F51">
         <v>0</v>
@@ -4274,7 +4274,7 @@
         <v>1</v>
       </c>
       <c r="L51" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="52" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -4288,10 +4288,10 @@
         <v>461</v>
       </c>
       <c r="D52" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E52" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F52">
         <v>1</v>
@@ -4312,7 +4312,7 @@
         <v>1</v>
       </c>
       <c r="L52" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="53" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -4326,10 +4326,10 @@
         <v>97</v>
       </c>
       <c r="D53" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E53" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F53">
         <v>1</v>
@@ -4350,7 +4350,7 @@
         <v>1</v>
       </c>
       <c r="L53" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="54" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -4364,10 +4364,10 @@
         <v>99</v>
       </c>
       <c r="D54" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E54" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F54">
         <v>1</v>
@@ -4388,7 +4388,7 @@
         <v>0</v>
       </c>
       <c r="L54" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="55" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -4402,10 +4402,10 @@
         <v>536</v>
       </c>
       <c r="D55" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E55" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F55">
         <v>0</v>
@@ -4426,7 +4426,7 @@
         <v>0</v>
       </c>
       <c r="L55" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="56" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -4440,10 +4440,10 @@
         <v>101</v>
       </c>
       <c r="D56" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E56" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F56">
         <v>1</v>
@@ -4464,7 +4464,7 @@
         <v>1</v>
       </c>
       <c r="L56" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="57" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -4478,10 +4478,10 @@
         <v>103</v>
       </c>
       <c r="D57" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E57" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F57">
         <v>1</v>
@@ -4502,7 +4502,7 @@
         <v>1</v>
       </c>
       <c r="L57" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="58" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -4516,10 +4516,10 @@
         <v>463</v>
       </c>
       <c r="D58" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E58" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F58">
         <v>1</v>
@@ -4540,7 +4540,7 @@
         <v>0</v>
       </c>
       <c r="L58" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="59" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -4554,10 +4554,10 @@
         <v>272</v>
       </c>
       <c r="D59" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E59" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="F59">
         <v>0</v>
@@ -4578,7 +4578,7 @@
         <v>1</v>
       </c>
       <c r="L59" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="60" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -4592,10 +4592,10 @@
         <v>105</v>
       </c>
       <c r="D60" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E60" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F60">
         <v>1</v>
@@ -4616,7 +4616,7 @@
         <v>0</v>
       </c>
       <c r="L60" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="61" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -4630,10 +4630,10 @@
         <v>107</v>
       </c>
       <c r="D61" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E61" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F61">
         <v>1</v>
@@ -4654,7 +4654,7 @@
         <v>1</v>
       </c>
       <c r="L61" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="62" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -4668,10 +4668,10 @@
         <v>109</v>
       </c>
       <c r="D62" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E62" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F62">
         <v>1</v>
@@ -4692,7 +4692,7 @@
         <v>0</v>
       </c>
       <c r="L62" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="63" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -4706,10 +4706,10 @@
         <v>111</v>
       </c>
       <c r="D63" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E63" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F63">
         <v>1</v>
@@ -4730,7 +4730,7 @@
         <v>1</v>
       </c>
       <c r="L63" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="64" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -4744,10 +4744,10 @@
         <v>113</v>
       </c>
       <c r="D64" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E64" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F64">
         <v>0</v>
@@ -4768,7 +4768,7 @@
         <v>1</v>
       </c>
       <c r="L64" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="65" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -4782,10 +4782,10 @@
         <v>32</v>
       </c>
       <c r="D65" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E65" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="F65">
         <v>0</v>
@@ -4806,7 +4806,7 @@
         <v>1</v>
       </c>
       <c r="L65" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="66" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -4820,10 +4820,10 @@
         <v>115</v>
       </c>
       <c r="D66" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E66" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F66">
         <v>0</v>
@@ -4844,7 +4844,7 @@
         <v>1</v>
       </c>
       <c r="L66" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="67" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -4858,10 +4858,10 @@
         <v>34</v>
       </c>
       <c r="D67" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E67" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="F67">
         <v>1</v>
@@ -4882,7 +4882,7 @@
         <v>0</v>
       </c>
       <c r="L67" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="68" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -4896,10 +4896,10 @@
         <v>117</v>
       </c>
       <c r="D68" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E68" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F68">
         <v>1</v>
@@ -4920,7 +4920,7 @@
         <v>1</v>
       </c>
       <c r="L68" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="69" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -4934,10 +4934,10 @@
         <v>465</v>
       </c>
       <c r="D69" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E69" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F69">
         <v>0</v>
@@ -4958,7 +4958,7 @@
         <v>1</v>
       </c>
       <c r="L69" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="70" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -4972,10 +4972,10 @@
         <v>119</v>
       </c>
       <c r="D70" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E70" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F70">
         <v>1</v>
@@ -4996,7 +4996,7 @@
         <v>0</v>
       </c>
       <c r="L70" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="71" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -5010,10 +5010,10 @@
         <v>121</v>
       </c>
       <c r="D71" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E71" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F71">
         <v>1</v>
@@ -5034,7 +5034,7 @@
         <v>1</v>
       </c>
       <c r="L71" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="72" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -5048,10 +5048,10 @@
         <v>123</v>
       </c>
       <c r="D72" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E72" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F72">
         <v>1</v>
@@ -5072,7 +5072,7 @@
         <v>1</v>
       </c>
       <c r="L72" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="73" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -5086,10 +5086,10 @@
         <v>125</v>
       </c>
       <c r="D73" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E73" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F73">
         <v>1</v>
@@ -5110,7 +5110,7 @@
         <v>1</v>
       </c>
       <c r="L73" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="74" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -5124,10 +5124,10 @@
         <v>127</v>
       </c>
       <c r="D74" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E74" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F74">
         <v>0</v>
@@ -5148,7 +5148,7 @@
         <v>0</v>
       </c>
       <c r="L74" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="75" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -5162,10 +5162,10 @@
         <v>52</v>
       </c>
       <c r="D75" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E75" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F75">
         <v>1</v>
@@ -5186,7 +5186,7 @@
         <v>0</v>
       </c>
       <c r="L75" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="76" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -5200,10 +5200,10 @@
         <v>538</v>
       </c>
       <c r="D76" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E76" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F76">
         <v>1</v>
@@ -5224,7 +5224,7 @@
         <v>0</v>
       </c>
       <c r="L76" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="77" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -5238,10 +5238,10 @@
         <v>467</v>
       </c>
       <c r="D77" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E77" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F77">
         <v>0</v>
@@ -5262,7 +5262,7 @@
         <v>1</v>
       </c>
       <c r="L77" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="78" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -5276,10 +5276,10 @@
         <v>129</v>
       </c>
       <c r="D78" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E78" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F78">
         <v>1</v>
@@ -5300,7 +5300,7 @@
         <v>1</v>
       </c>
       <c r="L78" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="79" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -5314,10 +5314,10 @@
         <v>131</v>
       </c>
       <c r="D79" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E79" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F79">
         <v>1</v>
@@ -5338,7 +5338,7 @@
         <v>1</v>
       </c>
       <c r="L79" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="80" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -5352,10 +5352,10 @@
         <v>469</v>
       </c>
       <c r="D80" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E80" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F80">
         <v>0</v>
@@ -5376,7 +5376,7 @@
         <v>1</v>
       </c>
       <c r="L80" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="81" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -5390,10 +5390,10 @@
         <v>133</v>
       </c>
       <c r="D81" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E81" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F81">
         <v>1</v>
@@ -5414,7 +5414,7 @@
         <v>1</v>
       </c>
       <c r="L81" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="82" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -5428,10 +5428,10 @@
         <v>135</v>
       </c>
       <c r="D82" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E82" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F82">
         <v>1</v>
@@ -5452,7 +5452,7 @@
         <v>1</v>
       </c>
       <c r="L82" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="83" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -5466,10 +5466,10 @@
         <v>137</v>
       </c>
       <c r="D83" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E83" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F83">
         <v>1</v>
@@ -5490,7 +5490,7 @@
         <v>0</v>
       </c>
       <c r="L83" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="84" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -5504,10 +5504,10 @@
         <v>540</v>
       </c>
       <c r="D84" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E84" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F84">
         <v>0</v>
@@ -5528,7 +5528,7 @@
         <v>0</v>
       </c>
       <c r="L84" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="85" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -5542,10 +5542,10 @@
         <v>139</v>
       </c>
       <c r="D85" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E85" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F85">
         <v>1</v>
@@ -5566,7 +5566,7 @@
         <v>0</v>
       </c>
       <c r="L85" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="86" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -5580,10 +5580,10 @@
         <v>141</v>
       </c>
       <c r="D86" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E86" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F86">
         <v>1</v>
@@ -5604,7 +5604,7 @@
         <v>1</v>
       </c>
       <c r="L86" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="87" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -5618,10 +5618,10 @@
         <v>544</v>
       </c>
       <c r="D87" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E87" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F87">
         <v>0</v>
@@ -5642,7 +5642,7 @@
         <v>1</v>
       </c>
       <c r="L87" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="88" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -5656,10 +5656,10 @@
         <v>471</v>
       </c>
       <c r="D88" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E88" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F88">
         <v>1</v>
@@ -5680,7 +5680,7 @@
         <v>1</v>
       </c>
       <c r="L88" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="89" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -5694,10 +5694,10 @@
         <v>473</v>
       </c>
       <c r="D89" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E89" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F89">
         <v>0</v>
@@ -5718,7 +5718,7 @@
         <v>1</v>
       </c>
       <c r="L89" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="90" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -5732,10 +5732,10 @@
         <v>234</v>
       </c>
       <c r="D90" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E90" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F90">
         <v>1</v>
@@ -5756,7 +5756,7 @@
         <v>1</v>
       </c>
       <c r="L90" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="91" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -5770,10 +5770,10 @@
         <v>475</v>
       </c>
       <c r="D91" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E91" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F91">
         <v>1</v>
@@ -5794,7 +5794,7 @@
         <v>1</v>
       </c>
       <c r="L91" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="92" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -5808,10 +5808,10 @@
         <v>143</v>
       </c>
       <c r="D92" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E92" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F92">
         <v>1</v>
@@ -5832,7 +5832,7 @@
         <v>1</v>
       </c>
       <c r="L92" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="93" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -5846,10 +5846,10 @@
         <v>145</v>
       </c>
       <c r="D93" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E93" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F93">
         <v>1</v>
@@ -5870,7 +5870,7 @@
         <v>0</v>
       </c>
       <c r="L93" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="94" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -5884,10 +5884,10 @@
         <v>274</v>
       </c>
       <c r="D94" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E94" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="F94">
         <v>1</v>
@@ -5908,7 +5908,7 @@
         <v>0</v>
       </c>
       <c r="L94" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="95" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -5922,10 +5922,10 @@
         <v>147</v>
       </c>
       <c r="D95" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E95" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F95">
         <v>1</v>
@@ -5946,7 +5946,7 @@
         <v>1</v>
       </c>
       <c r="L95" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="96" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -5960,10 +5960,10 @@
         <v>477</v>
       </c>
       <c r="D96" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E96" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F96">
         <v>1</v>
@@ -5984,7 +5984,7 @@
         <v>1</v>
       </c>
       <c r="L96" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="97" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -5998,10 +5998,10 @@
         <v>149</v>
       </c>
       <c r="D97" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E97" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F97">
         <v>1</v>
@@ -6022,7 +6022,7 @@
         <v>0</v>
       </c>
       <c r="L97" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="98" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -6036,10 +6036,10 @@
         <v>151</v>
       </c>
       <c r="D98" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E98" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F98">
         <v>1</v>
@@ -6060,7 +6060,7 @@
         <v>1</v>
       </c>
       <c r="L98" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="99" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -6074,10 +6074,10 @@
         <v>479</v>
       </c>
       <c r="D99" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E99" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F99">
         <v>1</v>
@@ -6098,7 +6098,7 @@
         <v>1</v>
       </c>
       <c r="L99" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="100" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -6112,10 +6112,10 @@
         <v>481</v>
       </c>
       <c r="D100" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E100" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F100">
         <v>1</v>
@@ -6136,7 +6136,7 @@
         <v>1</v>
       </c>
       <c r="L100" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="101" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -6150,10 +6150,10 @@
         <v>153</v>
       </c>
       <c r="D101" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E101" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F101">
         <v>0</v>
@@ -6174,7 +6174,7 @@
         <v>0</v>
       </c>
       <c r="L101" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="102" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -6188,10 +6188,10 @@
         <v>155</v>
       </c>
       <c r="D102" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E102" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F102">
         <v>1</v>
@@ -6212,7 +6212,7 @@
         <v>1</v>
       </c>
       <c r="L102" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="103" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -6226,10 +6226,10 @@
         <v>157</v>
       </c>
       <c r="D103" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E103" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F103">
         <v>0</v>
@@ -6250,7 +6250,7 @@
         <v>1</v>
       </c>
       <c r="L103" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="104" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -6264,10 +6264,10 @@
         <v>159</v>
       </c>
       <c r="D104" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E104" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F104">
         <v>1</v>
@@ -6288,7 +6288,7 @@
         <v>1</v>
       </c>
       <c r="L104" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="105" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -6302,10 +6302,10 @@
         <v>548</v>
       </c>
       <c r="D105" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E105" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F105">
         <v>0</v>
@@ -6326,7 +6326,7 @@
         <v>1</v>
       </c>
       <c r="L105" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="106" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -6340,10 +6340,10 @@
         <v>542</v>
       </c>
       <c r="D106" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E106" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F106">
         <v>0</v>
@@ -6364,7 +6364,7 @@
         <v>0</v>
       </c>
       <c r="L106" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="107" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -6378,10 +6378,10 @@
         <v>483</v>
       </c>
       <c r="D107" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E107" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F107">
         <v>0</v>
@@ -6402,7 +6402,7 @@
         <v>1</v>
       </c>
       <c r="L107" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="108" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -6416,10 +6416,10 @@
         <v>276</v>
       </c>
       <c r="D108" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E108" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="F108">
         <v>0</v>
@@ -6440,7 +6440,7 @@
         <v>0</v>
       </c>
       <c r="L108" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="109" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -6454,10 +6454,10 @@
         <v>485</v>
       </c>
       <c r="D109" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E109" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F109">
         <v>1</v>
@@ -6478,7 +6478,7 @@
         <v>1</v>
       </c>
       <c r="L109" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="110" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -6492,10 +6492,10 @@
         <v>36</v>
       </c>
       <c r="D110" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E110" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="F110">
         <v>1</v>
@@ -6516,7 +6516,7 @@
         <v>1</v>
       </c>
       <c r="L110" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="111" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -6530,10 +6530,10 @@
         <v>161</v>
       </c>
       <c r="D111" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E111" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F111">
         <v>1</v>
@@ -6554,7 +6554,7 @@
         <v>1</v>
       </c>
       <c r="L111" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="112" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -6568,10 +6568,10 @@
         <v>367</v>
       </c>
       <c r="D112" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E112" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F112">
         <v>1</v>
@@ -6592,7 +6592,7 @@
         <v>0</v>
       </c>
       <c r="L112" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="113" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -6606,10 +6606,10 @@
         <v>13</v>
       </c>
       <c r="D113" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E113" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F113">
         <v>1</v>
@@ -6630,7 +6630,7 @@
         <v>0</v>
       </c>
       <c r="L113" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="114" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -6644,10 +6644,10 @@
         <v>278</v>
       </c>
       <c r="D114" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E114" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="F114">
         <v>0</v>
@@ -6668,7 +6668,7 @@
         <v>1</v>
       </c>
       <c r="L114" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="115" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -6682,10 +6682,10 @@
         <v>280</v>
       </c>
       <c r="D115" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E115" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="F115">
         <v>0</v>
@@ -6706,7 +6706,7 @@
         <v>1</v>
       </c>
       <c r="L115" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="116" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -6720,10 +6720,10 @@
         <v>282</v>
       </c>
       <c r="D116" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E116" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="F116">
         <v>1</v>
@@ -6744,7 +6744,7 @@
         <v>1</v>
       </c>
       <c r="L116" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="117" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -6758,10 +6758,10 @@
         <v>392</v>
       </c>
       <c r="D117" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E117" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F117">
         <v>1</v>
@@ -6782,7 +6782,7 @@
         <v>0</v>
       </c>
       <c r="L117" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="118" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -6796,10 +6796,10 @@
         <v>406</v>
       </c>
       <c r="D118" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E118" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F118">
         <v>1</v>
@@ -6820,7 +6820,7 @@
         <v>0</v>
       </c>
       <c r="L118" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="119" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -6834,10 +6834,10 @@
         <v>394</v>
       </c>
       <c r="D119" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E119" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F119">
         <v>0</v>
@@ -6858,7 +6858,7 @@
         <v>0</v>
       </c>
       <c r="L119" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="120" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -6872,10 +6872,10 @@
         <v>284</v>
       </c>
       <c r="D120" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E120" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="F120">
         <v>0</v>
@@ -6896,7 +6896,7 @@
         <v>1</v>
       </c>
       <c r="L120" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="121" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -6910,10 +6910,10 @@
         <v>546</v>
       </c>
       <c r="D121" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E121" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F121">
         <v>0</v>
@@ -6934,7 +6934,7 @@
         <v>1</v>
       </c>
       <c r="L121" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="122" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -6948,10 +6948,10 @@
         <v>38</v>
       </c>
       <c r="D122" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E122" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="F122">
         <v>1</v>
@@ -6972,7 +6972,7 @@
         <v>1</v>
       </c>
       <c r="L122" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="123" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -6986,10 +6986,10 @@
         <v>286</v>
       </c>
       <c r="D123" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E123" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="F123">
         <v>1</v>
@@ -7010,7 +7010,7 @@
         <v>1</v>
       </c>
       <c r="L123" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="124" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -7024,10 +7024,10 @@
         <v>9</v>
       </c>
       <c r="D124" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E124" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F124">
         <v>1</v>
@@ -7048,7 +7048,7 @@
         <v>0</v>
       </c>
       <c r="L124" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="125" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -7062,10 +7062,10 @@
         <v>40</v>
       </c>
       <c r="D125" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E125" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F125">
         <v>1</v>
@@ -7086,7 +7086,7 @@
         <v>1</v>
       </c>
       <c r="L125" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="126" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -7100,10 +7100,10 @@
         <v>288</v>
       </c>
       <c r="D126" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E126" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="F126">
         <v>1</v>
@@ -7124,7 +7124,7 @@
         <v>1</v>
       </c>
       <c r="L126" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="127" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -7138,10 +7138,10 @@
         <v>54</v>
       </c>
       <c r="D127" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E127" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F127">
         <v>1</v>
@@ -7162,7 +7162,7 @@
         <v>0</v>
       </c>
       <c r="L127" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="128" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -7176,10 +7176,10 @@
         <v>396</v>
       </c>
       <c r="D128" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E128" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F128">
         <v>1</v>
@@ -7200,7 +7200,7 @@
         <v>0</v>
       </c>
       <c r="L128" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="129" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -7214,10 +7214,10 @@
         <v>11</v>
       </c>
       <c r="D129" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E129" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F129">
         <v>0</v>
@@ -7238,7 +7238,7 @@
         <v>1</v>
       </c>
       <c r="L129" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="130" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -7252,10 +7252,10 @@
         <v>290</v>
       </c>
       <c r="D130" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E130" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="F130">
         <v>0</v>
@@ -7276,7 +7276,7 @@
         <v>1</v>
       </c>
       <c r="L130" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="131" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -7290,10 +7290,10 @@
         <v>163</v>
       </c>
       <c r="D131" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E131" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F131">
         <v>0</v>
@@ -7314,7 +7314,7 @@
         <v>1</v>
       </c>
       <c r="L131" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="132" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -7328,10 +7328,10 @@
         <v>487</v>
       </c>
       <c r="D132" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E132" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F132">
         <v>0</v>
@@ -7352,10 +7352,10 @@
         <v>1</v>
       </c>
       <c r="L132" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="133" spans="1:12" x14ac:dyDescent="0.3">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="133" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>374</v>
       </c>
@@ -7366,10 +7366,10 @@
         <v>398</v>
       </c>
       <c r="D133" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E133" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F133">
         <v>0</v>
@@ -7390,7 +7390,7 @@
         <v>0</v>
       </c>
       <c r="L133" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
     </row>
     <row r="134" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -7404,10 +7404,10 @@
         <v>292</v>
       </c>
       <c r="D134" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E134" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="F134">
         <v>1</v>
@@ -7428,7 +7428,7 @@
         <v>0</v>
       </c>
       <c r="L134" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="135" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -7442,10 +7442,10 @@
         <v>42</v>
       </c>
       <c r="D135" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E135" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="F135">
         <v>0</v>
@@ -7466,7 +7466,7 @@
         <v>1</v>
       </c>
       <c r="L135" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="136" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -7480,10 +7480,10 @@
         <v>294</v>
       </c>
       <c r="D136" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E136" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="F136">
         <v>0</v>
@@ -7504,7 +7504,7 @@
         <v>0</v>
       </c>
       <c r="L136" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="137" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -7518,10 +7518,10 @@
         <v>296</v>
       </c>
       <c r="D137" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E137" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="F137">
         <v>1</v>
@@ -7542,7 +7542,7 @@
         <v>0</v>
       </c>
       <c r="L137" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="138" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -7556,10 +7556,10 @@
         <v>165</v>
       </c>
       <c r="D138" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E138" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F138">
         <v>1</v>
@@ -7580,7 +7580,7 @@
         <v>1</v>
       </c>
       <c r="L138" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="139" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -7594,10 +7594,10 @@
         <v>298</v>
       </c>
       <c r="D139" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E139" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="F139">
         <v>1</v>
@@ -7618,7 +7618,7 @@
         <v>1</v>
       </c>
       <c r="L139" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="140" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -7632,10 +7632,10 @@
         <v>550</v>
       </c>
       <c r="D140" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E140" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F140">
         <v>1</v>
@@ -7656,7 +7656,7 @@
         <v>0</v>
       </c>
       <c r="L140" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="141" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -7670,10 +7670,10 @@
         <v>489</v>
       </c>
       <c r="D141" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E141" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F141">
         <v>1</v>
@@ -7694,7 +7694,7 @@
         <v>0</v>
       </c>
       <c r="L141" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="142" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -7708,10 +7708,10 @@
         <v>369</v>
       </c>
       <c r="D142" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E142" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F142">
         <v>0</v>
@@ -7732,7 +7732,7 @@
         <v>0</v>
       </c>
       <c r="L142" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="143" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -7746,10 +7746,10 @@
         <v>300</v>
       </c>
       <c r="D143" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E143" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="F143">
         <v>0</v>
@@ -7770,7 +7770,7 @@
         <v>1</v>
       </c>
       <c r="L143" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="144" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -7784,10 +7784,10 @@
         <v>491</v>
       </c>
       <c r="D144" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E144" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F144">
         <v>0</v>
@@ -7808,7 +7808,7 @@
         <v>1</v>
       </c>
       <c r="L144" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="145" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -7822,10 +7822,10 @@
         <v>302</v>
       </c>
       <c r="D145" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E145" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="F145">
         <v>0</v>
@@ -7846,7 +7846,7 @@
         <v>1</v>
       </c>
       <c r="L145" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="146" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -7860,10 +7860,10 @@
         <v>304</v>
       </c>
       <c r="D146" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E146" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="F146">
         <v>1</v>
@@ -7884,7 +7884,7 @@
         <v>1</v>
       </c>
       <c r="L146" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="147" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -7898,10 +7898,10 @@
         <v>306</v>
       </c>
       <c r="D147" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E147" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="F147">
         <v>1</v>
@@ -7922,7 +7922,7 @@
         <v>0</v>
       </c>
       <c r="L147" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="148" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -7936,10 +7936,10 @@
         <v>308</v>
       </c>
       <c r="D148" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E148" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="F148">
         <v>0</v>
@@ -7960,7 +7960,7 @@
         <v>0</v>
       </c>
       <c r="L148" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="149" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -7974,10 +7974,10 @@
         <v>44</v>
       </c>
       <c r="D149" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E149" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F149">
         <v>1</v>
@@ -7998,7 +7998,7 @@
         <v>1</v>
       </c>
       <c r="L149" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="150" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -8012,10 +8012,10 @@
         <v>400</v>
       </c>
       <c r="D150" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E150" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="F150">
         <v>0</v>
@@ -8036,7 +8036,7 @@
         <v>0</v>
       </c>
       <c r="L150" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="151" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -8050,10 +8050,10 @@
         <v>310</v>
       </c>
       <c r="D151" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E151" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="F151">
         <v>1</v>
@@ -8074,10 +8074,10 @@
         <v>0</v>
       </c>
       <c r="L151" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="152" spans="1:12" x14ac:dyDescent="0.3">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="152" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>374</v>
       </c>
@@ -8088,10 +8088,10 @@
         <v>402</v>
       </c>
       <c r="D152" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E152" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F152">
         <v>1</v>
@@ -8112,7 +8112,7 @@
         <v>0</v>
       </c>
       <c r="L152" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
     </row>
     <row r="153" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -8126,10 +8126,10 @@
         <v>312</v>
       </c>
       <c r="D153" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E153" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="F153">
         <v>1</v>
@@ -8150,10 +8150,10 @@
         <v>1</v>
       </c>
       <c r="L153" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="154" spans="1:12" x14ac:dyDescent="0.3">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="154" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>374</v>
       </c>
@@ -8164,10 +8164,10 @@
         <v>404</v>
       </c>
       <c r="D154" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E154" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F154">
         <v>0</v>
@@ -8188,7 +8188,7 @@
         <v>0</v>
       </c>
       <c r="L154" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
     </row>
     <row r="155" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -8202,10 +8202,10 @@
         <v>408</v>
       </c>
       <c r="D155" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E155" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F155">
         <v>0</v>
@@ -8226,7 +8226,7 @@
         <v>1</v>
       </c>
       <c r="L155" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="156" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -8240,10 +8240,10 @@
         <v>320</v>
       </c>
       <c r="D156" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E156" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="F156">
         <v>0</v>
@@ -8264,7 +8264,7 @@
         <v>1</v>
       </c>
       <c r="L156" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="157" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -8278,10 +8278,10 @@
         <v>552</v>
       </c>
       <c r="D157" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E157" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F157">
         <v>1</v>
@@ -8302,7 +8302,7 @@
         <v>1</v>
       </c>
       <c r="L157" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="158" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -8316,10 +8316,10 @@
         <v>314</v>
       </c>
       <c r="D158" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E158" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="F158">
         <v>1</v>
@@ -8340,7 +8340,7 @@
         <v>0</v>
       </c>
       <c r="L158" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="159" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -8354,10 +8354,10 @@
         <v>236</v>
       </c>
       <c r="D159" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E159" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="F159">
         <v>1</v>
@@ -8378,7 +8378,7 @@
         <v>1</v>
       </c>
       <c r="L159" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="160" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -8392,10 +8392,10 @@
         <v>328</v>
       </c>
       <c r="D160" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E160" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="F160">
         <v>0</v>
@@ -8416,7 +8416,7 @@
         <v>1</v>
       </c>
       <c r="L160" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="161" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -8430,10 +8430,10 @@
         <v>316</v>
       </c>
       <c r="D161" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E161" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="F161">
         <v>1</v>
@@ -8454,7 +8454,7 @@
         <v>1</v>
       </c>
       <c r="L161" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="162" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -8468,10 +8468,10 @@
         <v>318</v>
       </c>
       <c r="D162" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E162" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="F162">
         <v>1</v>
@@ -8492,7 +8492,7 @@
         <v>0</v>
       </c>
       <c r="L162" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="163" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -8506,10 +8506,10 @@
         <v>334</v>
       </c>
       <c r="D163" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E163" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="F163">
         <v>0</v>
@@ -8530,7 +8530,7 @@
         <v>1</v>
       </c>
       <c r="L163" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="164" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -8544,10 +8544,10 @@
         <v>56</v>
       </c>
       <c r="D164" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E164" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F164">
         <v>1</v>
@@ -8568,7 +8568,7 @@
         <v>0</v>
       </c>
       <c r="L164" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="165" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -8582,10 +8582,10 @@
         <v>410</v>
       </c>
       <c r="D165" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E165" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="F165">
         <v>1</v>
@@ -8606,7 +8606,7 @@
         <v>1</v>
       </c>
       <c r="L165" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="166" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -8620,10 +8620,10 @@
         <v>554</v>
       </c>
       <c r="D166" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E166" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F166">
         <v>0</v>
@@ -8644,7 +8644,7 @@
         <v>0</v>
       </c>
       <c r="L166" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="167" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -8658,10 +8658,10 @@
         <v>412</v>
       </c>
       <c r="D167" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E167" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F167">
         <v>0</v>
@@ -8682,7 +8682,7 @@
         <v>0</v>
       </c>
       <c r="L167" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="168" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -8696,10 +8696,10 @@
         <v>322</v>
       </c>
       <c r="D168" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E168" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="F168">
         <v>1</v>
@@ -8720,7 +8720,7 @@
         <v>0</v>
       </c>
       <c r="L168" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="169" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -8734,10 +8734,10 @@
         <v>414</v>
       </c>
       <c r="D169" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E169" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="F169">
         <v>1</v>
@@ -8758,7 +8758,7 @@
         <v>1</v>
       </c>
       <c r="L169" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="170" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -8772,10 +8772,10 @@
         <v>416</v>
       </c>
       <c r="D170" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E170" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F170">
         <v>0</v>
@@ -8796,7 +8796,7 @@
         <v>0</v>
       </c>
       <c r="L170" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="171" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -8810,10 +8810,10 @@
         <v>58</v>
       </c>
       <c r="D171" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E171" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F171">
         <v>0</v>
@@ -8834,7 +8834,7 @@
         <v>0</v>
       </c>
       <c r="L171" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="172" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -8848,10 +8848,10 @@
         <v>324</v>
       </c>
       <c r="D172" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E172" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="F172">
         <v>1</v>
@@ -8872,7 +8872,7 @@
         <v>0</v>
       </c>
       <c r="L172" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="173" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -8886,10 +8886,10 @@
         <v>418</v>
       </c>
       <c r="D173" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E173" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F173">
         <v>0</v>
@@ -8910,10 +8910,10 @@
         <v>1</v>
       </c>
       <c r="L173" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="174" spans="1:12" x14ac:dyDescent="0.3">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="174" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>374</v>
       </c>
@@ -8924,10 +8924,10 @@
         <v>420</v>
       </c>
       <c r="D174" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E174" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F174">
         <v>0</v>
@@ -8948,7 +8948,7 @@
         <v>0</v>
       </c>
       <c r="L174" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
     </row>
     <row r="175" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -8962,10 +8962,10 @@
         <v>326</v>
       </c>
       <c r="D175" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E175" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="F175">
         <v>1</v>
@@ -8986,7 +8986,7 @@
         <v>0</v>
       </c>
       <c r="L175" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="176" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -9000,10 +9000,10 @@
         <v>15</v>
       </c>
       <c r="D176" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E176" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F176">
         <v>1</v>
@@ -9024,7 +9024,7 @@
         <v>0</v>
       </c>
       <c r="L176" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="177" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -9038,10 +9038,10 @@
         <v>422</v>
       </c>
       <c r="D177" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E177" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F177">
         <v>0</v>
@@ -9062,7 +9062,7 @@
         <v>0</v>
       </c>
       <c r="L177" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="178" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -9076,10 +9076,10 @@
         <v>167</v>
       </c>
       <c r="D178" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E178" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F178">
         <v>1</v>
@@ -9100,10 +9100,10 @@
         <v>0</v>
       </c>
       <c r="L178" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="179" spans="1:12" x14ac:dyDescent="0.3">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="179" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>374</v>
       </c>
@@ -9114,10 +9114,10 @@
         <v>424</v>
       </c>
       <c r="D179" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E179" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F179">
         <v>0</v>
@@ -9138,7 +9138,7 @@
         <v>0</v>
       </c>
       <c r="L179" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
     </row>
     <row r="180" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -9152,10 +9152,10 @@
         <v>169</v>
       </c>
       <c r="D180" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E180" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F180">
         <v>1</v>
@@ -9176,7 +9176,7 @@
         <v>0</v>
       </c>
       <c r="L180" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="181" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -9190,10 +9190,10 @@
         <v>171</v>
       </c>
       <c r="D181" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E181" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F181">
         <v>0</v>
@@ -9214,7 +9214,7 @@
         <v>0</v>
       </c>
       <c r="L181" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="182" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -9228,10 +9228,10 @@
         <v>173</v>
       </c>
       <c r="D182" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E182" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F182">
         <v>1</v>
@@ -9252,7 +9252,7 @@
         <v>1</v>
       </c>
       <c r="L182" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="183" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -9266,10 +9266,10 @@
         <v>330</v>
       </c>
       <c r="D183" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E183" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="F183">
         <v>1</v>
@@ -9290,7 +9290,7 @@
         <v>1</v>
       </c>
       <c r="L183" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="184" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -9304,10 +9304,10 @@
         <v>426</v>
       </c>
       <c r="D184" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E184" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F184">
         <v>1</v>
@@ -9328,7 +9328,7 @@
         <v>0</v>
       </c>
       <c r="L184" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="185" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -9342,10 +9342,10 @@
         <v>493</v>
       </c>
       <c r="D185" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E185" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F185">
         <v>0</v>
@@ -9366,7 +9366,7 @@
         <v>1</v>
       </c>
       <c r="L185" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="186" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -9380,10 +9380,10 @@
         <v>332</v>
       </c>
       <c r="D186" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E186" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="F186">
         <v>1</v>
@@ -9404,7 +9404,7 @@
         <v>0</v>
       </c>
       <c r="L186" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="187" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -9418,10 +9418,10 @@
         <v>558</v>
       </c>
       <c r="D187" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E187" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F187">
         <v>1</v>
@@ -9442,7 +9442,7 @@
         <v>1</v>
       </c>
       <c r="L187" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="188" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -9456,10 +9456,10 @@
         <v>556</v>
       </c>
       <c r="D188" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E188" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F188">
         <v>0</v>
@@ -9480,7 +9480,7 @@
         <v>0</v>
       </c>
       <c r="L188" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="189" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -9494,10 +9494,10 @@
         <v>17</v>
       </c>
       <c r="D189" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E189" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F189">
         <v>1</v>
@@ -9518,7 +9518,7 @@
         <v>0</v>
       </c>
       <c r="L189" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="190" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -9532,10 +9532,10 @@
         <v>560</v>
       </c>
       <c r="D190" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E190" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F190">
         <v>1</v>
@@ -9556,7 +9556,7 @@
         <v>0</v>
       </c>
       <c r="L190" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="191" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -9570,10 +9570,10 @@
         <v>373</v>
       </c>
       <c r="D191" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E191" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F191">
         <v>0</v>
@@ -9594,7 +9594,7 @@
         <v>1</v>
       </c>
       <c r="L191" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="192" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -9608,10 +9608,10 @@
         <v>60</v>
       </c>
       <c r="D192" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E192" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F192">
         <v>1</v>
@@ -9632,7 +9632,7 @@
         <v>0</v>
       </c>
       <c r="L192" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="193" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -9646,10 +9646,10 @@
         <v>336</v>
       </c>
       <c r="D193" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E193" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="F193">
         <v>0</v>
@@ -9670,7 +9670,7 @@
         <v>0</v>
       </c>
       <c r="L193" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="194" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -9684,10 +9684,10 @@
         <v>338</v>
       </c>
       <c r="D194" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E194" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="F194">
         <v>0</v>
@@ -9708,10 +9708,10 @@
         <v>0</v>
       </c>
       <c r="L194" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="195" spans="1:12" x14ac:dyDescent="0.3">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="195" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>374</v>
       </c>
@@ -9722,10 +9722,10 @@
         <v>428</v>
       </c>
       <c r="D195" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E195" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F195">
         <v>0</v>
@@ -9746,10 +9746,10 @@
         <v>0</v>
       </c>
       <c r="L195" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="196" spans="1:12" x14ac:dyDescent="0.3">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="196" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>374</v>
       </c>
@@ -9760,10 +9760,10 @@
         <v>430</v>
       </c>
       <c r="D196" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E196" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F196">
         <v>0</v>
@@ -9784,7 +9784,7 @@
         <v>0</v>
       </c>
       <c r="L196" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
     </row>
     <row r="197" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -9798,10 +9798,10 @@
         <v>340</v>
       </c>
       <c r="D197" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E197" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="F197">
         <v>0</v>
@@ -9822,7 +9822,7 @@
         <v>1</v>
       </c>
       <c r="L197" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="198" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -9836,10 +9836,10 @@
         <v>62</v>
       </c>
       <c r="D198" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E198" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F198">
         <v>1</v>
@@ -9860,10 +9860,10 @@
         <v>0</v>
       </c>
       <c r="L198" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="199" spans="1:12" x14ac:dyDescent="0.3">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="199" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>374</v>
       </c>
@@ -9874,10 +9874,10 @@
         <v>432</v>
       </c>
       <c r="D199" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E199" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F199">
         <v>0</v>
@@ -9898,7 +9898,7 @@
         <v>0</v>
       </c>
       <c r="L199" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
     </row>
     <row r="200" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -9912,10 +9912,10 @@
         <v>434</v>
       </c>
       <c r="D200" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E200" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="F200">
         <v>1</v>
@@ -9936,7 +9936,7 @@
         <v>0</v>
       </c>
       <c r="L200" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="201" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -9950,10 +9950,10 @@
         <v>342</v>
       </c>
       <c r="D201" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E201" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="F201">
         <v>0</v>
@@ -9974,7 +9974,7 @@
         <v>0</v>
       </c>
       <c r="L201" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="202" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -9988,10 +9988,10 @@
         <v>344</v>
       </c>
       <c r="D202" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E202" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="F202">
         <v>1</v>
@@ -10012,7 +10012,7 @@
         <v>0</v>
       </c>
       <c r="L202" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="203" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -10026,10 +10026,10 @@
         <v>193</v>
       </c>
       <c r="D203" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E203" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F203">
         <v>1</v>
@@ -10050,7 +10050,7 @@
         <v>1</v>
       </c>
       <c r="L203" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="204" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -10064,10 +10064,10 @@
         <v>346</v>
       </c>
       <c r="D204" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E204" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="F204">
         <v>1</v>
@@ -10088,7 +10088,7 @@
         <v>0</v>
       </c>
       <c r="L204" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="205" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -10102,10 +10102,10 @@
         <v>239</v>
       </c>
       <c r="D205" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E205" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F205">
         <v>1</v>
@@ -10126,7 +10126,7 @@
         <v>1</v>
       </c>
       <c r="L205" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="206" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -10140,10 +10140,10 @@
         <v>64</v>
       </c>
       <c r="D206" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E206" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F206">
         <v>1</v>
@@ -10164,7 +10164,7 @@
         <v>0</v>
       </c>
       <c r="L206" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="207" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -10178,10 +10178,10 @@
         <v>66</v>
       </c>
       <c r="D207" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E207" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F207">
         <v>1</v>
@@ -10202,7 +10202,7 @@
         <v>0</v>
       </c>
       <c r="L207" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="208" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -10216,10 +10216,10 @@
         <v>348</v>
       </c>
       <c r="D208" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E208" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="F208">
         <v>0</v>
@@ -10240,7 +10240,7 @@
         <v>1</v>
       </c>
       <c r="L208" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="209" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -10254,10 +10254,10 @@
         <v>47</v>
       </c>
       <c r="D209" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E209" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F209">
         <v>0</v>
@@ -10278,7 +10278,7 @@
         <v>1</v>
       </c>
       <c r="L209" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="210" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -10292,10 +10292,10 @@
         <v>5</v>
       </c>
       <c r="D210" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E210" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F210">
         <v>0</v>
@@ -10316,7 +10316,7 @@
         <v>1</v>
       </c>
       <c r="L210" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="211" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -10330,10 +10330,10 @@
         <v>19</v>
       </c>
       <c r="D211" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E211" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F211">
         <v>1</v>
@@ -10354,7 +10354,7 @@
         <v>1</v>
       </c>
       <c r="L211" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="212" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -10368,10 +10368,10 @@
         <v>350</v>
       </c>
       <c r="D212" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E212" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="F212">
         <v>1</v>
@@ -10392,7 +10392,7 @@
         <v>0</v>
       </c>
       <c r="L212" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="213" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -10406,10 +10406,10 @@
         <v>352</v>
       </c>
       <c r="D213" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E213" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="F213">
         <v>1</v>
@@ -10430,7 +10430,7 @@
         <v>0</v>
       </c>
       <c r="L213" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="214" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -10444,10 +10444,10 @@
         <v>354</v>
       </c>
       <c r="D214" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E214" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="F214">
         <v>1</v>
@@ -10468,7 +10468,7 @@
         <v>0</v>
       </c>
       <c r="L214" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="215" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -10482,10 +10482,10 @@
         <v>436</v>
       </c>
       <c r="D215" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E215" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F215">
         <v>1</v>
@@ -10506,7 +10506,7 @@
         <v>1</v>
       </c>
       <c r="L215" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="216" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -10520,10 +10520,10 @@
         <v>564</v>
       </c>
       <c r="D216" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E216" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F216">
         <v>1</v>
@@ -10544,7 +10544,7 @@
         <v>1</v>
       </c>
       <c r="L216" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="217" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -10558,10 +10558,10 @@
         <v>566</v>
       </c>
       <c r="D217" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E217" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F217">
         <v>1</v>
@@ -10582,7 +10582,7 @@
         <v>0</v>
       </c>
       <c r="L217" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="218" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -10596,10 +10596,10 @@
         <v>444</v>
       </c>
       <c r="D218" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E218" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F218">
         <v>1</v>
@@ -10620,7 +10620,7 @@
         <v>0</v>
       </c>
       <c r="L218" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="219" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -10634,10 +10634,10 @@
         <v>175</v>
       </c>
       <c r="D219" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E219" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F219">
         <v>1</v>
@@ -10658,7 +10658,7 @@
         <v>1</v>
       </c>
       <c r="L219" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="220" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -10672,10 +10672,10 @@
         <v>356</v>
       </c>
       <c r="D220" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E220" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="F220">
         <v>0</v>
@@ -10696,7 +10696,7 @@
         <v>1</v>
       </c>
       <c r="L220" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="221" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -10710,10 +10710,10 @@
         <v>358</v>
       </c>
       <c r="D221" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E221" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="F221">
         <v>1</v>
@@ -10734,7 +10734,7 @@
         <v>1</v>
       </c>
       <c r="L221" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="222" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -10748,10 +10748,10 @@
         <v>177</v>
       </c>
       <c r="D222" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E222" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F222">
         <v>1</v>
@@ -10772,7 +10772,7 @@
         <v>1</v>
       </c>
       <c r="L222" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="223" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -10786,10 +10786,10 @@
         <v>179</v>
       </c>
       <c r="D223" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E223" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F223">
         <v>1</v>
@@ -10810,7 +10810,7 @@
         <v>1</v>
       </c>
       <c r="L223" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="224" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -10824,10 +10824,10 @@
         <v>181</v>
       </c>
       <c r="D224" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E224" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F224">
         <v>0</v>
@@ -10848,7 +10848,7 @@
         <v>1</v>
       </c>
       <c r="L224" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="225" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -10862,10 +10862,10 @@
         <v>183</v>
       </c>
       <c r="D225" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E225" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F225">
         <v>1</v>
@@ -10886,7 +10886,7 @@
         <v>1</v>
       </c>
       <c r="L225" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="226" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -10900,10 +10900,10 @@
         <v>185</v>
       </c>
       <c r="D226" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E226" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F226">
         <v>1</v>
@@ -10924,7 +10924,7 @@
         <v>1</v>
       </c>
       <c r="L226" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="227" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -10938,10 +10938,10 @@
         <v>187</v>
       </c>
       <c r="D227" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E227" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F227">
         <v>1</v>
@@ -10962,7 +10962,7 @@
         <v>1</v>
       </c>
       <c r="L227" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="228" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -10976,10 +10976,10 @@
         <v>495</v>
       </c>
       <c r="D228" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E228" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F228">
         <v>1</v>
@@ -11000,7 +11000,7 @@
         <v>0</v>
       </c>
       <c r="L228" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="229" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -11014,10 +11014,10 @@
         <v>497</v>
       </c>
       <c r="D229" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E229" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F229">
         <v>1</v>
@@ -11038,7 +11038,7 @@
         <v>1</v>
       </c>
       <c r="L229" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="230" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -11052,10 +11052,10 @@
         <v>371</v>
       </c>
       <c r="D230" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E230" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F230">
         <v>0</v>
@@ -11076,7 +11076,7 @@
         <v>1</v>
       </c>
       <c r="L230" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="231" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -11090,10 +11090,10 @@
         <v>189</v>
       </c>
       <c r="D231" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E231" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F231">
         <v>1</v>
@@ -11114,7 +11114,7 @@
         <v>0</v>
       </c>
       <c r="L231" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="232" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -11128,10 +11128,10 @@
         <v>499</v>
       </c>
       <c r="D232" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E232" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F232">
         <v>0</v>
@@ -11152,7 +11152,7 @@
         <v>1</v>
       </c>
       <c r="L232" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="233" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -11166,10 +11166,10 @@
         <v>501</v>
       </c>
       <c r="D233" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E233" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F233">
         <v>0</v>
@@ -11190,7 +11190,7 @@
         <v>0</v>
       </c>
       <c r="L233" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="234" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -11204,10 +11204,10 @@
         <v>438</v>
       </c>
       <c r="D234" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E234" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F234">
         <v>0</v>
@@ -11228,7 +11228,7 @@
         <v>1</v>
       </c>
       <c r="L234" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="235" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -11242,10 +11242,10 @@
         <v>440</v>
       </c>
       <c r="D235" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E235" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="F235">
         <v>1</v>
@@ -11266,10 +11266,10 @@
         <v>1</v>
       </c>
       <c r="L235" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="236" spans="1:12" x14ac:dyDescent="0.3">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="236" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
         <v>374</v>
       </c>
@@ -11280,10 +11280,10 @@
         <v>442</v>
       </c>
       <c r="D236" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E236" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F236">
         <v>0</v>
@@ -11304,7 +11304,7 @@
         <v>0</v>
       </c>
       <c r="L236" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
     </row>
     <row r="237" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -11318,10 +11318,10 @@
         <v>191</v>
       </c>
       <c r="D237" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E237" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F237">
         <v>1</v>
@@ -11342,7 +11342,7 @@
         <v>0</v>
       </c>
       <c r="L237" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="238" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -11356,10 +11356,10 @@
         <v>360</v>
       </c>
       <c r="D238" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E238" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="F238">
         <v>1</v>
@@ -11380,7 +11380,7 @@
         <v>0</v>
       </c>
       <c r="L238" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="239" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -11394,10 +11394,10 @@
         <v>195</v>
       </c>
       <c r="D239" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E239" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F239">
         <v>0</v>
@@ -11418,7 +11418,7 @@
         <v>0</v>
       </c>
       <c r="L239" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="240" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -11432,10 +11432,10 @@
         <v>503</v>
       </c>
       <c r="D240" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E240" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F240">
         <v>0</v>
@@ -11456,7 +11456,7 @@
         <v>1</v>
       </c>
       <c r="L240" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="241" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -11470,10 +11470,10 @@
         <v>197</v>
       </c>
       <c r="D241" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E241" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F241">
         <v>1</v>
@@ -11494,7 +11494,7 @@
         <v>1</v>
       </c>
       <c r="L241" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="242" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -11508,10 +11508,10 @@
         <v>199</v>
       </c>
       <c r="D242" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E242" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F242">
         <v>1</v>
@@ -11532,7 +11532,7 @@
         <v>1</v>
       </c>
       <c r="L242" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="243" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -11546,10 +11546,10 @@
         <v>505</v>
       </c>
       <c r="D243" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E243" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F243">
         <v>0</v>
@@ -11570,7 +11570,7 @@
         <v>1</v>
       </c>
       <c r="L243" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="244" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -11584,10 +11584,10 @@
         <v>201</v>
       </c>
       <c r="D244" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E244" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F244">
         <v>1</v>
@@ -11608,7 +11608,7 @@
         <v>1</v>
       </c>
       <c r="L244" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="245" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -11622,10 +11622,10 @@
         <v>203</v>
       </c>
       <c r="D245" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E245" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F245">
         <v>1</v>
@@ -11646,7 +11646,7 @@
         <v>1</v>
       </c>
       <c r="L245" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="246" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -11660,10 +11660,10 @@
         <v>507</v>
       </c>
       <c r="D246" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E246" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F246">
         <v>0</v>
@@ -11684,7 +11684,7 @@
         <v>1</v>
       </c>
       <c r="L246" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="247" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -11698,10 +11698,10 @@
         <v>205</v>
       </c>
       <c r="D247" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E247" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F247">
         <v>1</v>
@@ -11722,7 +11722,7 @@
         <v>1</v>
       </c>
       <c r="L247" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="248" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -11736,10 +11736,10 @@
         <v>562</v>
       </c>
       <c r="D248" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E248" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F248">
         <v>0</v>
@@ -11760,7 +11760,7 @@
         <v>1</v>
       </c>
       <c r="L248" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="249" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -11774,10 +11774,10 @@
         <v>207</v>
       </c>
       <c r="D249" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E249" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F249">
         <v>0</v>
@@ -11798,7 +11798,7 @@
         <v>1</v>
       </c>
       <c r="L249" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="250" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -11812,10 +11812,10 @@
         <v>209</v>
       </c>
       <c r="D250" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E250" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F250">
         <v>1</v>
@@ -11836,7 +11836,7 @@
         <v>1</v>
       </c>
       <c r="L250" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="251" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -11850,10 +11850,10 @@
         <v>211</v>
       </c>
       <c r="D251" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E251" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F251">
         <v>1</v>
@@ -11874,7 +11874,7 @@
         <v>0</v>
       </c>
       <c r="L251" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="252" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -11888,10 +11888,10 @@
         <v>509</v>
       </c>
       <c r="D252" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E252" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F252">
         <v>1</v>
@@ -11912,7 +11912,7 @@
         <v>1</v>
       </c>
       <c r="L252" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="253" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -11926,10 +11926,10 @@
         <v>511</v>
       </c>
       <c r="D253" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E253" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F253">
         <v>1</v>
@@ -11950,7 +11950,7 @@
         <v>1</v>
       </c>
       <c r="L253" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="254" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -11964,10 +11964,10 @@
         <v>513</v>
       </c>
       <c r="D254" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E254" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F254">
         <v>1</v>
@@ -11988,7 +11988,7 @@
         <v>0</v>
       </c>
       <c r="L254" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="255" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -12002,10 +12002,10 @@
         <v>213</v>
       </c>
       <c r="D255" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E255" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F255">
         <v>1</v>
@@ -12026,7 +12026,7 @@
         <v>1</v>
       </c>
       <c r="L255" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="256" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -12040,10 +12040,10 @@
         <v>215</v>
       </c>
       <c r="D256" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E256" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F256">
         <v>1</v>
@@ -12064,7 +12064,7 @@
         <v>1</v>
       </c>
       <c r="L256" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="257" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -12078,10 +12078,10 @@
         <v>362</v>
       </c>
       <c r="D257" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E257" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="F257">
         <v>1</v>
@@ -12102,7 +12102,7 @@
         <v>0</v>
       </c>
       <c r="L257" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="258" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -12116,10 +12116,10 @@
         <v>446</v>
       </c>
       <c r="D258" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E258" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F258">
         <v>0</v>
@@ -12140,7 +12140,7 @@
         <v>0</v>
       </c>
       <c r="L258" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="259" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -12154,10 +12154,10 @@
         <v>217</v>
       </c>
       <c r="D259" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E259" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F259">
         <v>1</v>
@@ -12178,7 +12178,7 @@
         <v>1</v>
       </c>
       <c r="L259" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="260" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -12192,10 +12192,10 @@
         <v>219</v>
       </c>
       <c r="D260" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E260" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F260">
         <v>1</v>
@@ -12216,7 +12216,7 @@
         <v>1</v>
       </c>
       <c r="L260" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="261" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -12230,10 +12230,10 @@
         <v>241</v>
       </c>
       <c r="D261" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E261" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F261">
         <v>1</v>
@@ -12254,7 +12254,7 @@
         <v>1</v>
       </c>
       <c r="L261" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="262" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -12268,10 +12268,10 @@
         <v>515</v>
       </c>
       <c r="D262" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E262" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F262">
         <v>1</v>
@@ -12292,7 +12292,7 @@
         <v>1</v>
       </c>
       <c r="L262" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="263" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -12306,10 +12306,10 @@
         <v>517</v>
       </c>
       <c r="D263" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E263" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F263">
         <v>0</v>
@@ -12330,7 +12330,7 @@
         <v>1</v>
       </c>
       <c r="L263" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="264" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -12344,10 +12344,10 @@
         <v>221</v>
       </c>
       <c r="D264" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E264" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F264">
         <v>1</v>
@@ -12368,7 +12368,7 @@
         <v>0</v>
       </c>
       <c r="L264" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="265" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -12382,10 +12382,10 @@
         <v>519</v>
       </c>
       <c r="D265" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E265" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F265">
         <v>1</v>
@@ -12406,7 +12406,7 @@
         <v>1</v>
       </c>
       <c r="L265" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="266" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -12420,10 +12420,10 @@
         <v>223</v>
       </c>
       <c r="D266" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E266" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F266">
         <v>1</v>
@@ -12444,10 +12444,10 @@
         <v>1</v>
       </c>
       <c r="L266" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="267" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="267" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
         <v>374</v>
       </c>
@@ -12458,10 +12458,10 @@
         <v>448</v>
       </c>
       <c r="D267" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E267" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F267">
         <v>0</v>
@@ -12482,7 +12482,7 @@
         <v>1</v>
       </c>
       <c r="L267" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="268" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -12496,10 +12496,10 @@
         <v>243</v>
       </c>
       <c r="D268" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E268" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F268">
         <v>0</v>
@@ -12520,7 +12520,7 @@
         <v>1</v>
       </c>
       <c r="L268" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="269" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -12534,10 +12534,10 @@
         <v>521</v>
       </c>
       <c r="D269" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E269" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F269">
         <v>1</v>
@@ -12558,7 +12558,7 @@
         <v>1</v>
       </c>
       <c r="L269" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="270" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -12572,10 +12572,10 @@
         <v>523</v>
       </c>
       <c r="D270" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E270" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F270">
         <v>0</v>
@@ -12596,10 +12596,10 @@
         <v>1</v>
       </c>
       <c r="L270" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="271" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="271" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
         <v>48</v>
       </c>
@@ -12610,10 +12610,10 @@
         <v>68</v>
       </c>
       <c r="D271" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E271" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F271">
         <v>0</v>
@@ -12634,7 +12634,7 @@
         <v>0</v>
       </c>
       <c r="L271" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="272" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -12648,10 +12648,10 @@
         <v>450</v>
       </c>
       <c r="D272" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E272" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F272">
         <v>1</v>
@@ -12672,7 +12672,7 @@
         <v>0</v>
       </c>
       <c r="L272" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="273" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -12686,10 +12686,10 @@
         <v>525</v>
       </c>
       <c r="D273" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E273" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F273">
         <v>0</v>
@@ -12710,7 +12710,7 @@
         <v>1</v>
       </c>
       <c r="L273" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="274" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -12724,10 +12724,10 @@
         <v>225</v>
       </c>
       <c r="D274" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E274" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F274">
         <v>0</v>
@@ -12748,7 +12748,7 @@
         <v>1</v>
       </c>
       <c r="L274" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="275" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -12762,10 +12762,10 @@
         <v>227</v>
       </c>
       <c r="D275" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E275" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F275">
         <v>1</v>
@@ -12786,7 +12786,7 @@
         <v>1</v>
       </c>
       <c r="L275" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="276" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -12800,10 +12800,10 @@
         <v>452</v>
       </c>
       <c r="D276" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E276" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F276">
         <v>0</v>
@@ -12824,7 +12824,7 @@
         <v>0</v>
       </c>
       <c r="L276" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="277" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -12838,10 +12838,10 @@
         <v>229</v>
       </c>
       <c r="D277" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="E277" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F277">
         <v>1</v>
@@ -12862,19 +12862,15 @@
         <v>1</v>
       </c>
       <c r="L277" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:L277">
-    <filterColumn colId="3">
+    <filterColumn colId="0">
       <filters>
-        <filter val="ja"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="4">
-      <filters>
-        <filter val="nee"/>
+        <filter val="Libellen"/>
+        <filter val="Vogels"/>
       </filters>
     </filterColumn>
     <filterColumn colId="9">
@@ -12985,7 +12981,7 @@
     </row>
     <row r="9" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>409</v>
@@ -12996,7 +12992,7 @@
     </row>
     <row r="10" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>413</v>
@@ -13007,7 +13003,7 @@
     </row>
     <row r="11" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>433</v>
@@ -13018,7 +13014,7 @@
     </row>
     <row r="12" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>435</v>
@@ -13029,7 +13025,7 @@
     </row>
     <row r="13" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>439</v>
@@ -14446,7 +14442,7 @@
     </row>
     <row r="144" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A144" s="2" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B144" s="2" t="s">
         <v>401</v>
@@ -18887,7 +18883,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="42" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -18898,7 +18894,7 @@
     </row>
     <row r="2" spans="1:3" ht="55.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>18</v>
@@ -18936,7 +18932,7 @@
     </row>
     <row r="6" spans="1:3" ht="42" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>387</v>
@@ -18947,7 +18943,7 @@
     </row>
     <row r="7" spans="1:3" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>407</v>
@@ -18958,7 +18954,7 @@
     </row>
     <row r="8" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>409</v>
@@ -18969,7 +18965,7 @@
     </row>
     <row r="9" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>413</v>
@@ -18980,7 +18976,7 @@
     </row>
     <row r="10" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>417</v>
@@ -18991,7 +18987,7 @@
     </row>
     <row r="11" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>435</v>
@@ -19002,7 +18998,7 @@
     </row>
     <row r="12" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>439</v>
@@ -19148,7 +19144,7 @@
         <v>48</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="C25" s="9"/>
     </row>
@@ -20656,7 +20652,7 @@
         <v>526</v>
       </c>
       <c r="B163" s="6" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="C163" s="9"/>
     </row>
@@ -20665,7 +20661,7 @@
         <v>526</v>
       </c>
       <c r="B164" s="6" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="C164" s="9"/>
     </row>
@@ -20674,7 +20670,7 @@
         <v>526</v>
       </c>
       <c r="B165" s="6" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C165" s="9"/>
     </row>
@@ -20683,7 +20679,7 @@
         <v>526</v>
       </c>
       <c r="B166" s="6" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="C166" s="9"/>
     </row>
@@ -20692,7 +20688,7 @@
         <v>526</v>
       </c>
       <c r="B167" s="6" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="C167" s="9"/>
     </row>
@@ -20701,7 +20697,7 @@
         <v>526</v>
       </c>
       <c r="B168" s="6" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="C168" s="9"/>
     </row>
@@ -20710,7 +20706,7 @@
         <v>526</v>
       </c>
       <c r="B169" s="6" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="C169" s="9"/>
     </row>
@@ -24892,10 +24888,10 @@
   <sheetData>
     <row r="1" spans="1:3" ht="42" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -24988,7 +24984,7 @@
         <v>20</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>24</v>
@@ -26343,7 +26339,7 @@
         <v>526</v>
       </c>
       <c r="B135" s="6" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="C135" s="9"/>
     </row>
@@ -26352,7 +26348,7 @@
         <v>526</v>
       </c>
       <c r="B136" s="6" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="C136" s="9"/>
     </row>
@@ -26361,7 +26357,7 @@
         <v>526</v>
       </c>
       <c r="B137" s="6" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="C137" s="9"/>
     </row>
@@ -26370,7 +26366,7 @@
         <v>526</v>
       </c>
       <c r="B138" s="6" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="C138" s="9"/>
     </row>
@@ -26379,7 +26375,7 @@
         <v>526</v>
       </c>
       <c r="B139" s="6" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="C139" s="9"/>
     </row>
@@ -26388,7 +26384,7 @@
         <v>526</v>
       </c>
       <c r="B140" s="6" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="C140" s="9"/>
     </row>
@@ -30709,10 +30705,10 @@
   <sheetData>
     <row r="1" spans="1:3" ht="42" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="10" t="s">
+        <v>589</v>
+      </c>
+      <c r="B1" s="11" t="s">
         <v>590</v>
-      </c>
-      <c r="B1" s="11" t="s">
-        <v>591</v>
       </c>
       <c r="C1" s="11" t="s">
         <v>2</v>
@@ -30720,7 +30716,7 @@
     </row>
     <row r="2" spans="1:3" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>8</v>
@@ -30731,7 +30727,7 @@
     </row>
     <row r="3" spans="1:3" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>10</v>
@@ -30740,7 +30736,7 @@
     </row>
     <row r="4" spans="1:3" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>12</v>
@@ -30749,7 +30745,7 @@
     </row>
     <row r="5" spans="1:3" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="5" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>14</v>
@@ -30760,7 +30756,7 @@
     </row>
     <row r="6" spans="1:3" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="5" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>16</v>
@@ -30769,7 +30765,7 @@
     </row>
     <row r="7" spans="1:3" ht="55.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="5" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>18</v>
@@ -30780,7 +30776,7 @@
     </row>
     <row r="8" spans="1:3" ht="42" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="5" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>387</v>
@@ -30791,7 +30787,7 @@
     </row>
     <row r="9" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="5" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>407</v>
@@ -30802,7 +30798,7 @@
     </row>
     <row r="10" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="5" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>409</v>
@@ -30813,7 +30809,7 @@
     </row>
     <row r="11" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="5" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>413</v>
@@ -30824,7 +30820,7 @@
     </row>
     <row r="12" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="5" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>417</v>
@@ -30835,7 +30831,7 @@
     </row>
     <row r="13" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="5" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>433</v>
@@ -30846,7 +30842,7 @@
     </row>
     <row r="14" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="5" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>435</v>
@@ -30857,7 +30853,7 @@
     </row>
     <row r="15" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="5" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>439</v>
@@ -32013,7 +32009,7 @@
         <v>244</v>
       </c>
       <c r="B120" s="6" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="C120" s="6" t="s">
         <v>266</v>
@@ -32387,7 +32383,7 @@
         <v>363</v>
       </c>
       <c r="B154" s="6" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="C154" s="9"/>
     </row>
@@ -36868,7 +36864,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="10" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="B1" s="11" t="s">
         <v>1</v>
@@ -36926,7 +36922,7 @@
         <v>526</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="C6" s="9"/>
     </row>
@@ -37025,7 +37021,7 @@
     </row>
     <row r="16" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="5" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>6</v>
@@ -37055,7 +37051,7 @@
         <v>526</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="C19" s="9"/>
     </row>
@@ -38255,7 +38251,7 @@
     </row>
     <row r="130" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A130" s="5" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B130" s="6" t="s">
         <v>8</v>
@@ -38302,13 +38298,13 @@
         <v>374</v>
       </c>
       <c r="B134" s="6" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="C134" s="9"/>
     </row>
     <row r="135" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A135" s="5" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B135" s="6" t="s">
         <v>10</v>
@@ -38713,7 +38709,7 @@
     </row>
     <row r="174" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A174" s="5" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B174" s="6" t="s">
         <v>14</v>
@@ -38782,7 +38778,7 @@
     </row>
     <row r="181" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A181" s="5" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B181" s="6" t="s">
         <v>16</v>
@@ -38981,7 +38977,7 @@
     </row>
     <row r="200" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A200" s="5" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B200" s="6" t="s">
         <v>18</v>
@@ -43323,7 +43319,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="42" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="10" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="B1" s="11" t="s">
         <v>1</v>
@@ -44731,7 +44727,7 @@
     </row>
     <row r="129" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A129" s="12" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B129" s="7" t="s">
         <v>18</v>
@@ -44929,7 +44925,7 @@
     </row>
     <row r="147" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A147" s="3" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B147" s="3" t="s">
         <v>10</v>
@@ -44938,7 +44934,7 @@
     </row>
     <row r="148" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A148" s="3" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B148" s="3" t="s">
         <v>4</v>
@@ -45031,7 +45027,7 @@
         <v>526</v>
       </c>
       <c r="B158" s="3" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="C158" s="8"/>
     </row>
@@ -45040,7 +45036,7 @@
         <v>526</v>
       </c>
       <c r="B159" s="3" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="C159" s="8"/>
     </row>
@@ -45049,7 +45045,7 @@
         <v>526</v>
       </c>
       <c r="B160" s="3" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="C160" s="8"/>
     </row>
@@ -45058,7 +45054,7 @@
         <v>526</v>
       </c>
       <c r="B161" s="3" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C161" s="8"/>
     </row>
@@ -45067,7 +45063,7 @@
         <v>374</v>
       </c>
       <c r="B162" s="3" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C162" s="8"/>
     </row>

--- a/data/input/Excel_files/Soortenlijst_Maatwerkgebieden.xlsx
+++ b/data/input/Excel_files/Soortenlijst_Maatwerkgebieden.xlsx
@@ -6595,7 +6595,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="113" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>3</v>
       </c>
@@ -6785,7 +6785,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="118" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>374</v>
       </c>
@@ -10243,7 +10243,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="209" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>45</v>
       </c>
@@ -10281,7 +10281,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="210" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>3</v>
       </c>
@@ -10585,7 +10585,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="218" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>374</v>
       </c>
@@ -12869,13 +12869,10 @@
   <autoFilter ref="A1:L277">
     <filterColumn colId="0">
       <filters>
+        <filter val="Amfibieën"/>
+        <filter val="Kevers"/>
         <filter val="Libellen"/>
         <filter val="Vogels"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="9">
-      <filters>
-        <filter val="1"/>
       </filters>
     </filterColumn>
     <filterColumn colId="11">

--- a/data/input/Excel_files/Soortenlijst_Maatwerkgebieden.xlsx
+++ b/data/input/Excel_files/Soortenlijst_Maatwerkgebieden.xlsx
@@ -2379,19 +2379,19 @@
     </row>
     <row r="2" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="D2" t="s">
         <v>599</v>
       </c>
       <c r="E2" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="F2">
         <v>1</v>
@@ -2400,30 +2400,30 @@
         <v>1</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J2">
         <v>1</v>
       </c>
       <c r="K2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L2" t="s">
         <v>599</v>
       </c>
     </row>
-    <row r="3" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>230</v>
+        <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>231</v>
+        <v>12</v>
       </c>
       <c r="C3" t="s">
-        <v>232</v>
+        <v>13</v>
       </c>
       <c r="D3" t="s">
         <v>599</v>
@@ -2435,7 +2435,7 @@
         <v>1</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H3">
         <v>1</v>
@@ -2444,42 +2444,42 @@
         <v>1</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3">
         <v>0</v>
       </c>
       <c r="L3" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="4" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>244</v>
+        <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>245</v>
+        <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>246</v>
+        <v>9</v>
       </c>
       <c r="D4" t="s">
         <v>599</v>
       </c>
       <c r="E4" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4">
         <v>0</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4">
         <v>1</v>
@@ -2493,37 +2493,37 @@
     </row>
     <row r="5" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>244</v>
+        <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>247</v>
+        <v>10</v>
       </c>
       <c r="C5" t="s">
-        <v>248</v>
+        <v>11</v>
       </c>
       <c r="D5" t="s">
         <v>599</v>
       </c>
       <c r="E5" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="F5">
         <v>0</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5">
         <v>1</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" t="s">
         <v>599</v>
@@ -2531,31 +2531,31 @@
     </row>
     <row r="6" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>526</v>
+        <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>527</v>
+        <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>528</v>
+        <v>15</v>
       </c>
       <c r="D6" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="E6" t="s">
         <v>600</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6">
         <v>1</v>
@@ -2564,33 +2564,33 @@
         <v>0</v>
       </c>
       <c r="L6" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="7" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>363</v>
+        <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>364</v>
+        <v>16</v>
       </c>
       <c r="C7" t="s">
-        <v>365</v>
+        <v>17</v>
       </c>
       <c r="D7" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="E7" t="s">
         <v>600</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7">
         <v>1</v>
@@ -2599,21 +2599,21 @@
         <v>1</v>
       </c>
       <c r="K7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L7" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>48</v>
+        <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>49</v>
+        <v>4</v>
       </c>
       <c r="C8" t="s">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="D8" t="s">
         <v>599</v>
@@ -2625,7 +2625,7 @@
         <v>0</v>
       </c>
       <c r="G8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H8">
         <v>0</v>
@@ -2634,30 +2634,30 @@
         <v>0</v>
       </c>
       <c r="J8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8">
         <v>1</v>
       </c>
       <c r="L8" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="9" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>244</v>
+        <v>3</v>
       </c>
       <c r="B9" t="s">
-        <v>249</v>
+        <v>18</v>
       </c>
       <c r="C9" t="s">
-        <v>250</v>
+        <v>19</v>
       </c>
       <c r="D9" t="s">
         <v>599</v>
       </c>
       <c r="E9" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="F9">
         <v>1</v>
@@ -2666,7 +2666,7 @@
         <v>1</v>
       </c>
       <c r="H9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I9">
         <v>1</v>
@@ -2675,7 +2675,7 @@
         <v>1</v>
       </c>
       <c r="K9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" t="s">
         <v>599</v>
@@ -2683,37 +2683,37 @@
     </row>
     <row r="10" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>374</v>
+        <v>20</v>
       </c>
       <c r="B10" t="s">
-        <v>375</v>
+        <v>21</v>
       </c>
       <c r="C10" t="s">
-        <v>376</v>
+        <v>22</v>
       </c>
       <c r="D10" t="s">
         <v>599</v>
       </c>
       <c r="E10" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10">
         <v>1</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" t="s">
         <v>599</v>
@@ -2721,28 +2721,28 @@
     </row>
     <row r="11" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>244</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s">
-        <v>251</v>
+        <v>23</v>
       </c>
       <c r="C11" t="s">
-        <v>252</v>
+        <v>24</v>
       </c>
       <c r="D11" t="s">
         <v>599</v>
       </c>
       <c r="E11" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11">
         <v>1</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11">
         <v>1</v>
@@ -2759,28 +2759,28 @@
     </row>
     <row r="12" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>374</v>
+        <v>20</v>
       </c>
       <c r="B12" t="s">
-        <v>377</v>
+        <v>25</v>
       </c>
       <c r="C12" t="s">
-        <v>378</v>
+        <v>26</v>
       </c>
       <c r="D12" t="s">
         <v>599</v>
       </c>
       <c r="E12" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="F12">
         <v>1</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I12">
         <v>1</v>
@@ -2789,36 +2789,36 @@
         <v>1</v>
       </c>
       <c r="K12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" t="s">
         <v>599</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>374</v>
+        <v>20</v>
       </c>
       <c r="B13" t="s">
-        <v>379</v>
+        <v>27</v>
       </c>
       <c r="C13" t="s">
-        <v>380</v>
+        <v>28</v>
       </c>
       <c r="D13" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="E13" t="s">
         <v>600</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13">
         <v>1</v>
@@ -2827,21 +2827,21 @@
         <v>1</v>
       </c>
       <c r="K13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="14" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>244</v>
+        <v>20</v>
       </c>
       <c r="B14" t="s">
-        <v>253</v>
+        <v>29</v>
       </c>
       <c r="C14" t="s">
-        <v>254</v>
+        <v>30</v>
       </c>
       <c r="D14" t="s">
         <v>599</v>
@@ -2859,7 +2859,7 @@
         <v>0</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14">
         <v>1</v>
@@ -2876,25 +2876,25 @@
         <v>20</v>
       </c>
       <c r="B15" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="C15" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="D15" t="s">
         <v>599</v>
       </c>
       <c r="E15" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="F15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G15">
         <v>1</v>
       </c>
       <c r="H15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I15">
         <v>1</v>
@@ -2911,19 +2911,19 @@
     </row>
     <row r="16" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="B16" t="s">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="C16" t="s">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="D16" t="s">
         <v>599</v>
       </c>
       <c r="E16" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="F16">
         <v>1</v>
@@ -2932,10 +2932,10 @@
         <v>1</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16">
         <v>1</v>
@@ -2949,13 +2949,13 @@
     </row>
     <row r="17" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>374</v>
+        <v>20</v>
       </c>
       <c r="B17" t="s">
-        <v>381</v>
+        <v>35</v>
       </c>
       <c r="C17" t="s">
-        <v>382</v>
+        <v>36</v>
       </c>
       <c r="D17" t="s">
         <v>599</v>
@@ -2964,10 +2964,10 @@
         <v>599</v>
       </c>
       <c r="F17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17">
         <v>1</v>
@@ -2979,7 +2979,7 @@
         <v>1</v>
       </c>
       <c r="K17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" t="s">
         <v>599</v>
@@ -2987,37 +2987,37 @@
     </row>
     <row r="18" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>374</v>
+        <v>20</v>
       </c>
       <c r="B18" t="s">
-        <v>383</v>
+        <v>37</v>
       </c>
       <c r="C18" t="s">
-        <v>384</v>
+        <v>38</v>
       </c>
       <c r="D18" t="s">
         <v>599</v>
       </c>
       <c r="E18" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="F18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J18">
         <v>1</v>
       </c>
       <c r="K18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" t="s">
         <v>599</v>
@@ -3025,51 +3025,51 @@
     </row>
     <row r="19" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>526</v>
+        <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>531</v>
+        <v>39</v>
       </c>
       <c r="C19" t="s">
-        <v>532</v>
+        <v>40</v>
       </c>
       <c r="D19" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="E19" t="s">
         <v>600</v>
       </c>
       <c r="F19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19">
         <v>1</v>
       </c>
       <c r="K19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="20" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>244</v>
+        <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>255</v>
+        <v>41</v>
       </c>
       <c r="C20" t="s">
-        <v>256</v>
+        <v>42</v>
       </c>
       <c r="D20" t="s">
         <v>599</v>
@@ -3081,19 +3081,19 @@
         <v>0</v>
       </c>
       <c r="G20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H20">
         <v>0</v>
       </c>
       <c r="I20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J20">
         <v>1</v>
       </c>
       <c r="K20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L20" t="s">
         <v>599</v>
@@ -3104,16 +3104,16 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="C21" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="D21" t="s">
         <v>599</v>
       </c>
       <c r="E21" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="F21">
         <v>1</v>
@@ -3122,7 +3122,7 @@
         <v>1</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21">
         <v>1</v>
@@ -3137,15 +3137,15 @@
         <v>599</v>
       </c>
     </row>
-    <row r="22" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>374</v>
+        <v>45</v>
       </c>
       <c r="B22" t="s">
-        <v>389</v>
+        <v>46</v>
       </c>
       <c r="C22" t="s">
-        <v>390</v>
+        <v>47</v>
       </c>
       <c r="D22" t="s">
         <v>599</v>
@@ -3172,18 +3172,18 @@
         <v>1</v>
       </c>
       <c r="L22" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="23" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="B23" t="s">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="C23" t="s">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="D23" t="s">
         <v>599</v>
@@ -3192,16 +3192,16 @@
         <v>600</v>
       </c>
       <c r="F23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G23">
         <v>1</v>
       </c>
       <c r="H23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J23">
         <v>1</v>
@@ -3215,13 +3215,13 @@
     </row>
     <row r="24" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>374</v>
+        <v>48</v>
       </c>
       <c r="B24" t="s">
-        <v>385</v>
+        <v>51</v>
       </c>
       <c r="C24" t="s">
-        <v>386</v>
+        <v>52</v>
       </c>
       <c r="D24" t="s">
         <v>599</v>
@@ -3233,13 +3233,13 @@
         <v>1</v>
       </c>
       <c r="G24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H24">
         <v>1</v>
       </c>
       <c r="I24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J24">
         <v>1</v>
@@ -3253,19 +3253,19 @@
     </row>
     <row r="25" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>244</v>
+        <v>48</v>
       </c>
       <c r="B25" t="s">
-        <v>257</v>
+        <v>53</v>
       </c>
       <c r="C25" t="s">
-        <v>258</v>
+        <v>54</v>
       </c>
       <c r="D25" t="s">
         <v>599</v>
       </c>
       <c r="E25" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="F25">
         <v>1</v>
@@ -3291,37 +3291,37 @@
     </row>
     <row r="26" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>244</v>
+        <v>48</v>
       </c>
       <c r="B26" t="s">
-        <v>259</v>
+        <v>55</v>
       </c>
       <c r="C26" t="s">
-        <v>260</v>
+        <v>56</v>
       </c>
       <c r="D26" t="s">
         <v>599</v>
       </c>
       <c r="E26" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="F26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J26">
         <v>1</v>
       </c>
       <c r="K26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L26" t="s">
         <v>599</v>
@@ -3329,22 +3329,22 @@
     </row>
     <row r="27" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>244</v>
+        <v>48</v>
       </c>
       <c r="B27" t="s">
-        <v>261</v>
+        <v>57</v>
       </c>
       <c r="C27" t="s">
-        <v>262</v>
+        <v>58</v>
       </c>
       <c r="D27" t="s">
         <v>599</v>
       </c>
       <c r="E27" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="F27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -3367,19 +3367,19 @@
     </row>
     <row r="28" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>244</v>
+        <v>48</v>
       </c>
       <c r="B28" t="s">
-        <v>263</v>
+        <v>59</v>
       </c>
       <c r="C28" t="s">
-        <v>264</v>
+        <v>60</v>
       </c>
       <c r="D28" t="s">
         <v>599</v>
       </c>
       <c r="E28" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="F28">
         <v>1</v>
@@ -3388,10 +3388,10 @@
         <v>0</v>
       </c>
       <c r="H28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J28">
         <v>1</v>
@@ -3405,13 +3405,13 @@
     </row>
     <row r="29" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>244</v>
+        <v>48</v>
       </c>
       <c r="B29" t="s">
-        <v>265</v>
+        <v>61</v>
       </c>
       <c r="C29" t="s">
-        <v>266</v>
+        <v>62</v>
       </c>
       <c r="D29" t="s">
         <v>599</v>
@@ -3443,28 +3443,28 @@
     </row>
     <row r="30" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="B30" t="s">
-        <v>29</v>
+        <v>63</v>
       </c>
       <c r="C30" t="s">
-        <v>30</v>
+        <v>64</v>
       </c>
       <c r="D30" t="s">
         <v>599</v>
       </c>
       <c r="E30" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="F30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G30">
         <v>1</v>
       </c>
       <c r="H30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I30">
         <v>1</v>
@@ -3473,7 +3473,7 @@
         <v>1</v>
       </c>
       <c r="K30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L30" t="s">
         <v>599</v>
@@ -3481,25 +3481,25 @@
     </row>
     <row r="31" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>244</v>
+        <v>48</v>
       </c>
       <c r="B31" t="s">
-        <v>267</v>
+        <v>65</v>
       </c>
       <c r="C31" t="s">
-        <v>268</v>
+        <v>66</v>
       </c>
       <c r="D31" t="s">
         <v>599</v>
       </c>
       <c r="E31" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="F31">
         <v>1</v>
       </c>
       <c r="G31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H31">
         <v>1</v>
@@ -3519,25 +3519,25 @@
     </row>
     <row r="32" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>244</v>
+        <v>48</v>
       </c>
       <c r="B32" t="s">
-        <v>269</v>
+        <v>67</v>
       </c>
       <c r="C32" t="s">
-        <v>270</v>
+        <v>68</v>
       </c>
       <c r="D32" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="E32" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="F32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H32">
         <v>1</v>
@@ -3552,7 +3552,7 @@
         <v>0</v>
       </c>
       <c r="L32" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="33" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -3633,31 +3633,31 @@
     </row>
     <row r="35" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>526</v>
+        <v>69</v>
       </c>
       <c r="B35" t="s">
-        <v>533</v>
+        <v>74</v>
       </c>
       <c r="C35" t="s">
-        <v>534</v>
+        <v>75</v>
       </c>
       <c r="D35" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="E35" t="s">
         <v>600</v>
       </c>
       <c r="F35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H35">
         <v>0</v>
       </c>
       <c r="I35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J35">
         <v>1</v>
@@ -3666,18 +3666,18 @@
         <v>1</v>
       </c>
       <c r="L35" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="36" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>453</v>
+        <v>69</v>
       </c>
       <c r="B36" t="s">
-        <v>454</v>
+        <v>76</v>
       </c>
       <c r="C36" t="s">
-        <v>455</v>
+        <v>77</v>
       </c>
       <c r="D36" t="s">
         <v>600</v>
@@ -3692,7 +3692,7 @@
         <v>1</v>
       </c>
       <c r="H36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I36">
         <v>1</v>
@@ -3712,10 +3712,10 @@
         <v>69</v>
       </c>
       <c r="B37" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C37" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D37" t="s">
         <v>600</v>
@@ -3750,10 +3750,10 @@
         <v>69</v>
       </c>
       <c r="B38" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C38" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="D38" t="s">
         <v>600</v>
@@ -3762,7 +3762,7 @@
         <v>600</v>
       </c>
       <c r="F38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G38">
         <v>1</v>
@@ -3777,7 +3777,7 @@
         <v>1</v>
       </c>
       <c r="K38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L38" t="s">
         <v>600</v>
@@ -3788,10 +3788,10 @@
         <v>69</v>
       </c>
       <c r="B39" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C39" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="D39" t="s">
         <v>600</v>
@@ -3800,13 +3800,13 @@
         <v>600</v>
       </c>
       <c r="F39">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G39">
         <v>1</v>
       </c>
       <c r="H39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I39">
         <v>1</v>
@@ -3815,7 +3815,7 @@
         <v>1</v>
       </c>
       <c r="K39">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L39" t="s">
         <v>600</v>
@@ -3823,13 +3823,13 @@
     </row>
     <row r="40" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>453</v>
+        <v>69</v>
       </c>
       <c r="B40" t="s">
-        <v>456</v>
+        <v>84</v>
       </c>
       <c r="C40" t="s">
-        <v>457</v>
+        <v>85</v>
       </c>
       <c r="D40" t="s">
         <v>600</v>
@@ -3844,7 +3844,7 @@
         <v>1</v>
       </c>
       <c r="H40">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I40">
         <v>1</v>
@@ -3864,10 +3864,10 @@
         <v>69</v>
       </c>
       <c r="B41" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="C41" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="D41" t="s">
         <v>600</v>
@@ -3876,13 +3876,13 @@
         <v>600</v>
       </c>
       <c r="F41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G41">
         <v>1</v>
       </c>
       <c r="H41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I41">
         <v>1</v>
@@ -3891,7 +3891,7 @@
         <v>1</v>
       </c>
       <c r="K41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L41" t="s">
         <v>600</v>
@@ -3902,10 +3902,10 @@
         <v>69</v>
       </c>
       <c r="B42" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="C42" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="D42" t="s">
         <v>600</v>
@@ -3914,7 +3914,7 @@
         <v>600</v>
       </c>
       <c r="F42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G42">
         <v>1</v>
@@ -3929,7 +3929,7 @@
         <v>1</v>
       </c>
       <c r="K42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L42" t="s">
         <v>600</v>
@@ -3937,13 +3937,13 @@
     </row>
     <row r="43" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>526</v>
+        <v>69</v>
       </c>
       <c r="B43" t="s">
-        <v>529</v>
+        <v>90</v>
       </c>
       <c r="C43" t="s">
-        <v>530</v>
+        <v>91</v>
       </c>
       <c r="D43" t="s">
         <v>600</v>
@@ -3952,19 +3952,19 @@
         <v>600</v>
       </c>
       <c r="F43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K43">
         <v>1</v>
@@ -3975,22 +3975,22 @@
     </row>
     <row r="44" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>374</v>
+        <v>69</v>
       </c>
       <c r="B44" t="s">
-        <v>387</v>
+        <v>92</v>
       </c>
       <c r="C44" t="s">
-        <v>388</v>
+        <v>93</v>
       </c>
       <c r="D44" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="E44" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="F44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G44">
         <v>1</v>
@@ -4008,7 +4008,7 @@
         <v>1</v>
       </c>
       <c r="L44" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="45" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -4016,10 +4016,10 @@
         <v>69</v>
       </c>
       <c r="B45" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="C45" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="D45" t="s">
         <v>600</v>
@@ -4028,13 +4028,13 @@
         <v>600</v>
       </c>
       <c r="F45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G45">
         <v>1</v>
       </c>
       <c r="H45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I45">
         <v>1</v>
@@ -4054,10 +4054,10 @@
         <v>69</v>
       </c>
       <c r="B46" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="C46" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="D46" t="s">
         <v>600</v>
@@ -4092,10 +4092,10 @@
         <v>69</v>
       </c>
       <c r="B47" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="C47" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="D47" t="s">
         <v>600</v>
@@ -4119,7 +4119,7 @@
         <v>1</v>
       </c>
       <c r="K47">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L47" t="s">
         <v>600</v>
@@ -4130,10 +4130,10 @@
         <v>69</v>
       </c>
       <c r="B48" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="C48" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="D48" t="s">
         <v>600</v>
@@ -4145,10 +4145,10 @@
         <v>1</v>
       </c>
       <c r="G48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I48">
         <v>1</v>
@@ -4168,10 +4168,10 @@
         <v>69</v>
       </c>
       <c r="B49" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C49" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="D49" t="s">
         <v>600</v>
@@ -4186,7 +4186,7 @@
         <v>1</v>
       </c>
       <c r="H49">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I49">
         <v>1</v>
@@ -4206,10 +4206,10 @@
         <v>69</v>
       </c>
       <c r="B50" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="C50" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="D50" t="s">
         <v>600</v>
@@ -4233,7 +4233,7 @@
         <v>1</v>
       </c>
       <c r="K50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L50" t="s">
         <v>600</v>
@@ -4241,13 +4241,13 @@
     </row>
     <row r="51" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>453</v>
+        <v>69</v>
       </c>
       <c r="B51" t="s">
-        <v>458</v>
+        <v>106</v>
       </c>
       <c r="C51" t="s">
-        <v>459</v>
+        <v>107</v>
       </c>
       <c r="D51" t="s">
         <v>600</v>
@@ -4256,13 +4256,13 @@
         <v>600</v>
       </c>
       <c r="F51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G51">
         <v>1</v>
       </c>
       <c r="H51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I51">
         <v>1</v>
@@ -4279,13 +4279,13 @@
     </row>
     <row r="52" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>453</v>
+        <v>69</v>
       </c>
       <c r="B52" t="s">
-        <v>460</v>
+        <v>108</v>
       </c>
       <c r="C52" t="s">
-        <v>461</v>
+        <v>109</v>
       </c>
       <c r="D52" t="s">
         <v>600</v>
@@ -4300,7 +4300,7 @@
         <v>0</v>
       </c>
       <c r="H52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I52">
         <v>1</v>
@@ -4309,7 +4309,7 @@
         <v>1</v>
       </c>
       <c r="K52">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L52" t="s">
         <v>600</v>
@@ -4320,10 +4320,10 @@
         <v>69</v>
       </c>
       <c r="B53" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="C53" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="D53" t="s">
         <v>600</v>
@@ -4358,10 +4358,10 @@
         <v>69</v>
       </c>
       <c r="B54" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="C54" t="s">
-        <v>99</v>
+        <v>113</v>
       </c>
       <c r="D54" t="s">
         <v>600</v>
@@ -4370,7 +4370,7 @@
         <v>600</v>
       </c>
       <c r="F54">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G54">
         <v>1</v>
@@ -4385,7 +4385,7 @@
         <v>1</v>
       </c>
       <c r="K54">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L54" t="s">
         <v>600</v>
@@ -4393,13 +4393,13 @@
     </row>
     <row r="55" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>526</v>
+        <v>69</v>
       </c>
       <c r="B55" t="s">
-        <v>535</v>
+        <v>114</v>
       </c>
       <c r="C55" t="s">
-        <v>536</v>
+        <v>115</v>
       </c>
       <c r="D55" t="s">
         <v>600</v>
@@ -4411,7 +4411,7 @@
         <v>0</v>
       </c>
       <c r="G55">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H55">
         <v>0</v>
@@ -4420,10 +4420,10 @@
         <v>0</v>
       </c>
       <c r="J55">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K55">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L55" t="s">
         <v>600</v>
@@ -4434,10 +4434,10 @@
         <v>69</v>
       </c>
       <c r="B56" t="s">
-        <v>100</v>
+        <v>116</v>
       </c>
       <c r="C56" t="s">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="D56" t="s">
         <v>600</v>
@@ -4449,7 +4449,7 @@
         <v>1</v>
       </c>
       <c r="G56">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H56">
         <v>0</v>
@@ -4472,10 +4472,10 @@
         <v>69</v>
       </c>
       <c r="B57" t="s">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="C57" t="s">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="D57" t="s">
         <v>600</v>
@@ -4490,7 +4490,7 @@
         <v>1</v>
       </c>
       <c r="H57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I57">
         <v>1</v>
@@ -4499,7 +4499,7 @@
         <v>1</v>
       </c>
       <c r="K57">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L57" t="s">
         <v>600</v>
@@ -4507,13 +4507,13 @@
     </row>
     <row r="58" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>453</v>
+        <v>69</v>
       </c>
       <c r="B58" t="s">
-        <v>462</v>
+        <v>120</v>
       </c>
       <c r="C58" t="s">
-        <v>463</v>
+        <v>121</v>
       </c>
       <c r="D58" t="s">
         <v>600</v>
@@ -4537,7 +4537,7 @@
         <v>1</v>
       </c>
       <c r="K58">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L58" t="s">
         <v>600</v>
@@ -4545,31 +4545,31 @@
     </row>
     <row r="59" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>244</v>
+        <v>69</v>
       </c>
       <c r="B59" t="s">
-        <v>271</v>
+        <v>122</v>
       </c>
       <c r="C59" t="s">
-        <v>272</v>
+        <v>123</v>
       </c>
       <c r="D59" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="E59" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="F59">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G59">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H59">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I59">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J59">
         <v>1</v>
@@ -4578,7 +4578,7 @@
         <v>1</v>
       </c>
       <c r="L59" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="60" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -4586,10 +4586,10 @@
         <v>69</v>
       </c>
       <c r="B60" t="s">
-        <v>104</v>
+        <v>124</v>
       </c>
       <c r="C60" t="s">
-        <v>105</v>
+        <v>125</v>
       </c>
       <c r="D60" t="s">
         <v>600</v>
@@ -4613,7 +4613,7 @@
         <v>1</v>
       </c>
       <c r="K60">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L60" t="s">
         <v>600</v>
@@ -4624,10 +4624,10 @@
         <v>69</v>
       </c>
       <c r="B61" t="s">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="C61" t="s">
-        <v>107</v>
+        <v>127</v>
       </c>
       <c r="D61" t="s">
         <v>600</v>
@@ -4636,7 +4636,7 @@
         <v>600</v>
       </c>
       <c r="F61">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G61">
         <v>1</v>
@@ -4651,7 +4651,7 @@
         <v>1</v>
       </c>
       <c r="K61">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L61" t="s">
         <v>600</v>
@@ -4662,10 +4662,10 @@
         <v>69</v>
       </c>
       <c r="B62" t="s">
-        <v>108</v>
+        <v>128</v>
       </c>
       <c r="C62" t="s">
-        <v>109</v>
+        <v>129</v>
       </c>
       <c r="D62" t="s">
         <v>600</v>
@@ -4677,7 +4677,7 @@
         <v>1</v>
       </c>
       <c r="G62">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H62">
         <v>1</v>
@@ -4689,7 +4689,7 @@
         <v>1</v>
       </c>
       <c r="K62">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L62" t="s">
         <v>600</v>
@@ -4700,10 +4700,10 @@
         <v>69</v>
       </c>
       <c r="B63" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="C63" t="s">
-        <v>111</v>
+        <v>131</v>
       </c>
       <c r="D63" t="s">
         <v>600</v>
@@ -4718,7 +4718,7 @@
         <v>1</v>
       </c>
       <c r="H63">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I63">
         <v>1</v>
@@ -4738,10 +4738,10 @@
         <v>69</v>
       </c>
       <c r="B64" t="s">
-        <v>112</v>
+        <v>132</v>
       </c>
       <c r="C64" t="s">
-        <v>113</v>
+        <v>133</v>
       </c>
       <c r="D64" t="s">
         <v>600</v>
@@ -4750,7 +4750,7 @@
         <v>600</v>
       </c>
       <c r="F64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G64">
         <v>1</v>
@@ -4773,28 +4773,28 @@
     </row>
     <row r="65" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>20</v>
+        <v>69</v>
       </c>
       <c r="B65" t="s">
-        <v>31</v>
+        <v>134</v>
       </c>
       <c r="C65" t="s">
-        <v>32</v>
+        <v>135</v>
       </c>
       <c r="D65" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="E65" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="F65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G65">
         <v>1</v>
       </c>
       <c r="H65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I65">
         <v>1</v>
@@ -4806,7 +4806,7 @@
         <v>1</v>
       </c>
       <c r="L65" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="66" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -4814,10 +4814,10 @@
         <v>69</v>
       </c>
       <c r="B66" t="s">
-        <v>114</v>
+        <v>136</v>
       </c>
       <c r="C66" t="s">
-        <v>115</v>
+        <v>137</v>
       </c>
       <c r="D66" t="s">
         <v>600</v>
@@ -4826,22 +4826,22 @@
         <v>600</v>
       </c>
       <c r="F66">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G66">
         <v>1</v>
       </c>
       <c r="H66">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I66">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J66">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K66">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L66" t="s">
         <v>600</v>
@@ -4849,19 +4849,19 @@
     </row>
     <row r="67" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>20</v>
+        <v>69</v>
       </c>
       <c r="B67" t="s">
-        <v>33</v>
+        <v>138</v>
       </c>
       <c r="C67" t="s">
-        <v>34</v>
+        <v>139</v>
       </c>
       <c r="D67" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="E67" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="F67">
         <v>1</v>
@@ -4882,7 +4882,7 @@
         <v>0</v>
       </c>
       <c r="L67" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="68" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -4890,10 +4890,10 @@
         <v>69</v>
       </c>
       <c r="B68" t="s">
-        <v>116</v>
+        <v>140</v>
       </c>
       <c r="C68" t="s">
-        <v>117</v>
+        <v>141</v>
       </c>
       <c r="D68" t="s">
         <v>600</v>
@@ -4905,7 +4905,7 @@
         <v>1</v>
       </c>
       <c r="G68">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H68">
         <v>0</v>
@@ -4925,13 +4925,13 @@
     </row>
     <row r="69" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>453</v>
+        <v>69</v>
       </c>
       <c r="B69" t="s">
-        <v>464</v>
+        <v>142</v>
       </c>
       <c r="C69" t="s">
-        <v>465</v>
+        <v>143</v>
       </c>
       <c r="D69" t="s">
         <v>600</v>
@@ -4940,13 +4940,13 @@
         <v>600</v>
       </c>
       <c r="F69">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G69">
         <v>1</v>
       </c>
       <c r="H69">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I69">
         <v>1</v>
@@ -4966,10 +4966,10 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>118</v>
+        <v>144</v>
       </c>
       <c r="C70" t="s">
-        <v>119</v>
+        <v>145</v>
       </c>
       <c r="D70" t="s">
         <v>600</v>
@@ -5004,10 +5004,10 @@
         <v>69</v>
       </c>
       <c r="B71" t="s">
-        <v>120</v>
+        <v>146</v>
       </c>
       <c r="C71" t="s">
-        <v>121</v>
+        <v>147</v>
       </c>
       <c r="D71" t="s">
         <v>600</v>
@@ -5042,10 +5042,10 @@
         <v>69</v>
       </c>
       <c r="B72" t="s">
-        <v>122</v>
+        <v>148</v>
       </c>
       <c r="C72" t="s">
-        <v>123</v>
+        <v>149</v>
       </c>
       <c r="D72" t="s">
         <v>600</v>
@@ -5069,7 +5069,7 @@
         <v>1</v>
       </c>
       <c r="K72">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L72" t="s">
         <v>600</v>
@@ -5080,10 +5080,10 @@
         <v>69</v>
       </c>
       <c r="B73" t="s">
-        <v>124</v>
+        <v>150</v>
       </c>
       <c r="C73" t="s">
-        <v>125</v>
+        <v>151</v>
       </c>
       <c r="D73" t="s">
         <v>600</v>
@@ -5118,10 +5118,10 @@
         <v>69</v>
       </c>
       <c r="B74" t="s">
-        <v>126</v>
+        <v>152</v>
       </c>
       <c r="C74" t="s">
-        <v>127</v>
+        <v>153</v>
       </c>
       <c r="D74" t="s">
         <v>600</v>
@@ -5153,16 +5153,16 @@
     </row>
     <row r="75" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="B75" t="s">
-        <v>51</v>
+        <v>154</v>
       </c>
       <c r="C75" t="s">
-        <v>52</v>
+        <v>155</v>
       </c>
       <c r="D75" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="E75" t="s">
         <v>600</v>
@@ -5174,7 +5174,7 @@
         <v>1</v>
       </c>
       <c r="H75">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I75">
         <v>1</v>
@@ -5183,21 +5183,21 @@
         <v>1</v>
       </c>
       <c r="K75">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L75" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="76" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>526</v>
+        <v>69</v>
       </c>
       <c r="B76" t="s">
-        <v>537</v>
+        <v>156</v>
       </c>
       <c r="C76" t="s">
-        <v>538</v>
+        <v>157</v>
       </c>
       <c r="D76" t="s">
         <v>600</v>
@@ -5206,22 +5206,22 @@
         <v>600</v>
       </c>
       <c r="F76">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G76">
         <v>1</v>
       </c>
       <c r="H76">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I76">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J76">
         <v>1</v>
       </c>
       <c r="K76">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L76" t="s">
         <v>600</v>
@@ -5229,13 +5229,13 @@
     </row>
     <row r="77" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>453</v>
+        <v>69</v>
       </c>
       <c r="B77" t="s">
-        <v>466</v>
+        <v>158</v>
       </c>
       <c r="C77" t="s">
-        <v>467</v>
+        <v>159</v>
       </c>
       <c r="D77" t="s">
         <v>600</v>
@@ -5244,19 +5244,19 @@
         <v>600</v>
       </c>
       <c r="F77">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G77">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H77">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I77">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J77">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K77">
         <v>1</v>
@@ -5270,10 +5270,10 @@
         <v>69</v>
       </c>
       <c r="B78" t="s">
-        <v>128</v>
+        <v>160</v>
       </c>
       <c r="C78" t="s">
-        <v>129</v>
+        <v>161</v>
       </c>
       <c r="D78" t="s">
         <v>600</v>
@@ -5308,10 +5308,10 @@
         <v>69</v>
       </c>
       <c r="B79" t="s">
-        <v>130</v>
+        <v>162</v>
       </c>
       <c r="C79" t="s">
-        <v>131</v>
+        <v>163</v>
       </c>
       <c r="D79" t="s">
         <v>600</v>
@@ -5320,19 +5320,19 @@
         <v>600</v>
       </c>
       <c r="F79">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G79">
         <v>1</v>
       </c>
       <c r="H79">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I79">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J79">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K79">
         <v>1</v>
@@ -5343,13 +5343,13 @@
     </row>
     <row r="80" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>453</v>
+        <v>69</v>
       </c>
       <c r="B80" t="s">
-        <v>468</v>
+        <v>164</v>
       </c>
       <c r="C80" t="s">
-        <v>469</v>
+        <v>165</v>
       </c>
       <c r="D80" t="s">
         <v>600</v>
@@ -5358,7 +5358,7 @@
         <v>600</v>
       </c>
       <c r="F80">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G80">
         <v>1</v>
@@ -5384,10 +5384,10 @@
         <v>69</v>
       </c>
       <c r="B81" t="s">
-        <v>132</v>
+        <v>166</v>
       </c>
       <c r="C81" t="s">
-        <v>133</v>
+        <v>167</v>
       </c>
       <c r="D81" t="s">
         <v>600</v>
@@ -5411,7 +5411,7 @@
         <v>1</v>
       </c>
       <c r="K81">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L81" t="s">
         <v>600</v>
@@ -5422,10 +5422,10 @@
         <v>69</v>
       </c>
       <c r="B82" t="s">
-        <v>134</v>
+        <v>168</v>
       </c>
       <c r="C82" t="s">
-        <v>135</v>
+        <v>169</v>
       </c>
       <c r="D82" t="s">
         <v>600</v>
@@ -5449,7 +5449,7 @@
         <v>1</v>
       </c>
       <c r="K82">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L82" t="s">
         <v>600</v>
@@ -5460,10 +5460,10 @@
         <v>69</v>
       </c>
       <c r="B83" t="s">
-        <v>136</v>
+        <v>170</v>
       </c>
       <c r="C83" t="s">
-        <v>137</v>
+        <v>171</v>
       </c>
       <c r="D83" t="s">
         <v>600</v>
@@ -5472,16 +5472,16 @@
         <v>600</v>
       </c>
       <c r="F83">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G83">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H83">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I83">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J83">
         <v>1</v>
@@ -5495,13 +5495,13 @@
     </row>
     <row r="84" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>526</v>
+        <v>69</v>
       </c>
       <c r="B84" t="s">
-        <v>539</v>
+        <v>172</v>
       </c>
       <c r="C84" t="s">
-        <v>540</v>
+        <v>173</v>
       </c>
       <c r="D84" t="s">
         <v>600</v>
@@ -5510,39 +5510,39 @@
         <v>600</v>
       </c>
       <c r="F84">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G84">
         <v>1</v>
       </c>
       <c r="H84">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I84">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J84">
         <v>1</v>
       </c>
       <c r="K84">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L84" t="s">
         <v>600</v>
       </c>
     </row>
-    <row r="85" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>69</v>
       </c>
       <c r="B85" t="s">
-        <v>138</v>
+        <v>192</v>
       </c>
       <c r="C85" t="s">
-        <v>139</v>
+        <v>193</v>
       </c>
       <c r="D85" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="E85" t="s">
         <v>600</v>
@@ -5551,19 +5551,19 @@
         <v>1</v>
       </c>
       <c r="G85">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H85">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I85">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J85">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L85" t="s">
         <v>600</v>
@@ -5574,10 +5574,10 @@
         <v>69</v>
       </c>
       <c r="B86" t="s">
-        <v>140</v>
+        <v>174</v>
       </c>
       <c r="C86" t="s">
-        <v>141</v>
+        <v>175</v>
       </c>
       <c r="D86" t="s">
         <v>600</v>
@@ -5589,10 +5589,10 @@
         <v>1</v>
       </c>
       <c r="G86">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H86">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I86">
         <v>1</v>
@@ -5609,13 +5609,13 @@
     </row>
     <row r="87" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>526</v>
+        <v>69</v>
       </c>
       <c r="B87" t="s">
-        <v>543</v>
+        <v>176</v>
       </c>
       <c r="C87" t="s">
-        <v>544</v>
+        <v>177</v>
       </c>
       <c r="D87" t="s">
         <v>600</v>
@@ -5624,19 +5624,19 @@
         <v>600</v>
       </c>
       <c r="F87">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G87">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H87">
         <v>0</v>
       </c>
       <c r="I87">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J87">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K87">
         <v>1</v>
@@ -5647,13 +5647,13 @@
     </row>
     <row r="88" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>453</v>
+        <v>69</v>
       </c>
       <c r="B88" t="s">
-        <v>470</v>
+        <v>178</v>
       </c>
       <c r="C88" t="s">
-        <v>471</v>
+        <v>179</v>
       </c>
       <c r="D88" t="s">
         <v>600</v>
@@ -5685,13 +5685,13 @@
     </row>
     <row r="89" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>453</v>
+        <v>69</v>
       </c>
       <c r="B89" t="s">
-        <v>472</v>
+        <v>180</v>
       </c>
       <c r="C89" t="s">
-        <v>473</v>
+        <v>181</v>
       </c>
       <c r="D89" t="s">
         <v>600</v>
@@ -5709,10 +5709,10 @@
         <v>0</v>
       </c>
       <c r="I89">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J89">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K89">
         <v>1</v>
@@ -5723,16 +5723,16 @@
     </row>
     <row r="90" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>230</v>
+        <v>69</v>
       </c>
       <c r="B90" t="s">
-        <v>233</v>
+        <v>182</v>
       </c>
       <c r="C90" t="s">
-        <v>234</v>
+        <v>183</v>
       </c>
       <c r="D90" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="E90" t="s">
         <v>600</v>
@@ -5741,10 +5741,10 @@
         <v>1</v>
       </c>
       <c r="G90">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H90">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I90">
         <v>1</v>
@@ -5756,18 +5756,18 @@
         <v>1</v>
       </c>
       <c r="L90" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="91" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>453</v>
+        <v>69</v>
       </c>
       <c r="B91" t="s">
-        <v>474</v>
+        <v>184</v>
       </c>
       <c r="C91" t="s">
-        <v>475</v>
+        <v>185</v>
       </c>
       <c r="D91" t="s">
         <v>600</v>
@@ -5779,10 +5779,10 @@
         <v>1</v>
       </c>
       <c r="G91">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H91">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I91">
         <v>1</v>
@@ -5802,10 +5802,10 @@
         <v>69</v>
       </c>
       <c r="B92" t="s">
-        <v>142</v>
+        <v>186</v>
       </c>
       <c r="C92" t="s">
-        <v>143</v>
+        <v>187</v>
       </c>
       <c r="D92" t="s">
         <v>600</v>
@@ -5820,7 +5820,7 @@
         <v>1</v>
       </c>
       <c r="H92">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I92">
         <v>1</v>
@@ -5840,10 +5840,10 @@
         <v>69</v>
       </c>
       <c r="B93" t="s">
-        <v>144</v>
+        <v>188</v>
       </c>
       <c r="C93" t="s">
-        <v>145</v>
+        <v>189</v>
       </c>
       <c r="D93" t="s">
         <v>600</v>
@@ -5875,31 +5875,31 @@
     </row>
     <row r="94" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>244</v>
+        <v>69</v>
       </c>
       <c r="B94" t="s">
-        <v>273</v>
+        <v>190</v>
       </c>
       <c r="C94" t="s">
-        <v>274</v>
+        <v>191</v>
       </c>
       <c r="D94" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="E94" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="F94">
         <v>1</v>
       </c>
       <c r="G94">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H94">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I94">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J94">
         <v>1</v>
@@ -5908,7 +5908,7 @@
         <v>0</v>
       </c>
       <c r="L94" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="95" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -5916,10 +5916,10 @@
         <v>69</v>
       </c>
       <c r="B95" t="s">
-        <v>146</v>
+        <v>194</v>
       </c>
       <c r="C95" t="s">
-        <v>147</v>
+        <v>195</v>
       </c>
       <c r="D95" t="s">
         <v>600</v>
@@ -5928,7 +5928,7 @@
         <v>600</v>
       </c>
       <c r="F95">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G95">
         <v>1</v>
@@ -5943,7 +5943,7 @@
         <v>1</v>
       </c>
       <c r="K95">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L95" t="s">
         <v>600</v>
@@ -5951,13 +5951,13 @@
     </row>
     <row r="96" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>453</v>
+        <v>69</v>
       </c>
       <c r="B96" t="s">
-        <v>476</v>
+        <v>196</v>
       </c>
       <c r="C96" t="s">
-        <v>477</v>
+        <v>197</v>
       </c>
       <c r="D96" t="s">
         <v>600</v>
@@ -5992,10 +5992,10 @@
         <v>69</v>
       </c>
       <c r="B97" t="s">
-        <v>148</v>
+        <v>198</v>
       </c>
       <c r="C97" t="s">
-        <v>149</v>
+        <v>199</v>
       </c>
       <c r="D97" t="s">
         <v>600</v>
@@ -6007,10 +6007,10 @@
         <v>1</v>
       </c>
       <c r="G97">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H97">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I97">
         <v>1</v>
@@ -6019,7 +6019,7 @@
         <v>1</v>
       </c>
       <c r="K97">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L97" t="s">
         <v>600</v>
@@ -6030,10 +6030,10 @@
         <v>69</v>
       </c>
       <c r="B98" t="s">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="C98" t="s">
-        <v>151</v>
+        <v>201</v>
       </c>
       <c r="D98" t="s">
         <v>600</v>
@@ -6065,13 +6065,13 @@
     </row>
     <row r="99" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>453</v>
+        <v>69</v>
       </c>
       <c r="B99" t="s">
-        <v>478</v>
+        <v>202</v>
       </c>
       <c r="C99" t="s">
-        <v>479</v>
+        <v>203</v>
       </c>
       <c r="D99" t="s">
         <v>600</v>
@@ -6103,13 +6103,13 @@
     </row>
     <row r="100" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>453</v>
+        <v>69</v>
       </c>
       <c r="B100" t="s">
-        <v>480</v>
+        <v>204</v>
       </c>
       <c r="C100" t="s">
-        <v>481</v>
+        <v>205</v>
       </c>
       <c r="D100" t="s">
         <v>600</v>
@@ -6144,10 +6144,10 @@
         <v>69</v>
       </c>
       <c r="B101" t="s">
-        <v>152</v>
+        <v>206</v>
       </c>
       <c r="C101" t="s">
-        <v>153</v>
+        <v>207</v>
       </c>
       <c r="D101" t="s">
         <v>600</v>
@@ -6162,16 +6162,16 @@
         <v>1</v>
       </c>
       <c r="H101">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I101">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J101">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K101">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L101" t="s">
         <v>600</v>
@@ -6182,10 +6182,10 @@
         <v>69</v>
       </c>
       <c r="B102" t="s">
-        <v>154</v>
+        <v>208</v>
       </c>
       <c r="C102" t="s">
-        <v>155</v>
+        <v>209</v>
       </c>
       <c r="D102" t="s">
         <v>600</v>
@@ -6200,7 +6200,7 @@
         <v>1</v>
       </c>
       <c r="H102">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I102">
         <v>1</v>
@@ -6220,10 +6220,10 @@
         <v>69</v>
       </c>
       <c r="B103" t="s">
-        <v>156</v>
+        <v>210</v>
       </c>
       <c r="C103" t="s">
-        <v>157</v>
+        <v>211</v>
       </c>
       <c r="D103" t="s">
         <v>600</v>
@@ -6232,13 +6232,13 @@
         <v>600</v>
       </c>
       <c r="F103">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G103">
         <v>1</v>
       </c>
       <c r="H103">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I103">
         <v>1</v>
@@ -6247,7 +6247,7 @@
         <v>1</v>
       </c>
       <c r="K103">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L103" t="s">
         <v>600</v>
@@ -6258,10 +6258,10 @@
         <v>69</v>
       </c>
       <c r="B104" t="s">
-        <v>158</v>
+        <v>212</v>
       </c>
       <c r="C104" t="s">
-        <v>159</v>
+        <v>213</v>
       </c>
       <c r="D104" t="s">
         <v>600</v>
@@ -6293,13 +6293,13 @@
     </row>
     <row r="105" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>526</v>
+        <v>69</v>
       </c>
       <c r="B105" t="s">
-        <v>547</v>
+        <v>214</v>
       </c>
       <c r="C105" t="s">
-        <v>548</v>
+        <v>215</v>
       </c>
       <c r="D105" t="s">
         <v>600</v>
@@ -6308,19 +6308,19 @@
         <v>600</v>
       </c>
       <c r="F105">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G105">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H105">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I105">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J105">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K105">
         <v>1</v>
@@ -6331,13 +6331,13 @@
     </row>
     <row r="106" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>526</v>
+        <v>69</v>
       </c>
       <c r="B106" t="s">
-        <v>541</v>
+        <v>216</v>
       </c>
       <c r="C106" t="s">
-        <v>542</v>
+        <v>217</v>
       </c>
       <c r="D106" t="s">
         <v>600</v>
@@ -6346,22 +6346,22 @@
         <v>600</v>
       </c>
       <c r="F106">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G106">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H106">
         <v>0</v>
       </c>
       <c r="I106">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J106">
         <v>1</v>
       </c>
       <c r="K106">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L106" t="s">
         <v>600</v>
@@ -6369,13 +6369,13 @@
     </row>
     <row r="107" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>453</v>
+        <v>69</v>
       </c>
       <c r="B107" t="s">
-        <v>482</v>
+        <v>218</v>
       </c>
       <c r="C107" t="s">
-        <v>483</v>
+        <v>219</v>
       </c>
       <c r="D107" t="s">
         <v>600</v>
@@ -6384,19 +6384,19 @@
         <v>600</v>
       </c>
       <c r="F107">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G107">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H107">
         <v>0</v>
       </c>
       <c r="I107">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J107">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K107">
         <v>1</v>
@@ -6407,31 +6407,31 @@
     </row>
     <row r="108" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>244</v>
+        <v>69</v>
       </c>
       <c r="B108" t="s">
-        <v>275</v>
+        <v>220</v>
       </c>
       <c r="C108" t="s">
-        <v>276</v>
+        <v>221</v>
       </c>
       <c r="D108" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="E108" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="F108">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G108">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H108">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I108">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J108">
         <v>1</v>
@@ -6440,18 +6440,18 @@
         <v>0</v>
       </c>
       <c r="L108" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="109" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>453</v>
+        <v>69</v>
       </c>
       <c r="B109" t="s">
-        <v>484</v>
+        <v>222</v>
       </c>
       <c r="C109" t="s">
-        <v>485</v>
+        <v>223</v>
       </c>
       <c r="D109" t="s">
         <v>600</v>
@@ -6466,7 +6466,7 @@
         <v>1</v>
       </c>
       <c r="H109">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I109">
         <v>1</v>
@@ -6483,40 +6483,40 @@
     </row>
     <row r="110" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>20</v>
+        <v>69</v>
       </c>
       <c r="B110" t="s">
-        <v>35</v>
+        <v>224</v>
       </c>
       <c r="C110" t="s">
-        <v>36</v>
+        <v>225</v>
       </c>
       <c r="D110" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="E110" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="F110">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G110">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H110">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I110">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J110">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K110">
         <v>1</v>
       </c>
       <c r="L110" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="111" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -6524,10 +6524,10 @@
         <v>69</v>
       </c>
       <c r="B111" t="s">
-        <v>160</v>
+        <v>226</v>
       </c>
       <c r="C111" t="s">
-        <v>161</v>
+        <v>227</v>
       </c>
       <c r="D111" t="s">
         <v>600</v>
@@ -6542,7 +6542,7 @@
         <v>1</v>
       </c>
       <c r="H111">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I111">
         <v>1</v>
@@ -6559,16 +6559,16 @@
     </row>
     <row r="112" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>363</v>
+        <v>69</v>
       </c>
       <c r="B112" t="s">
-        <v>366</v>
+        <v>228</v>
       </c>
       <c r="C112" t="s">
-        <v>367</v>
+        <v>229</v>
       </c>
       <c r="D112" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="E112" t="s">
         <v>600</v>
@@ -6577,33 +6577,33 @@
         <v>1</v>
       </c>
       <c r="G112">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H112">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I112">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J112">
         <v>1</v>
       </c>
       <c r="K112">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L112" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="113" spans="1:12" x14ac:dyDescent="0.3">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="113" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>3</v>
+        <v>230</v>
       </c>
       <c r="B113" t="s">
-        <v>12</v>
+        <v>231</v>
       </c>
       <c r="C113" t="s">
-        <v>13</v>
+        <v>232</v>
       </c>
       <c r="D113" t="s">
         <v>599</v>
@@ -6615,7 +6615,7 @@
         <v>1</v>
       </c>
       <c r="G113">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H113">
         <v>1</v>
@@ -6624,42 +6624,42 @@
         <v>1</v>
       </c>
       <c r="J113">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K113">
         <v>0</v>
       </c>
       <c r="L113" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="114" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>244</v>
+        <v>230</v>
       </c>
       <c r="B114" t="s">
-        <v>277</v>
+        <v>233</v>
       </c>
       <c r="C114" t="s">
-        <v>278</v>
+        <v>234</v>
       </c>
       <c r="D114" t="s">
         <v>599</v>
       </c>
       <c r="E114" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="F114">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G114">
         <v>1</v>
       </c>
       <c r="H114">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I114">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J114">
         <v>1</v>
@@ -6673,13 +6673,13 @@
     </row>
     <row r="115" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>244</v>
+        <v>230</v>
       </c>
       <c r="B115" t="s">
-        <v>279</v>
+        <v>235</v>
       </c>
       <c r="C115" t="s">
-        <v>280</v>
+        <v>236</v>
       </c>
       <c r="D115" t="s">
         <v>599</v>
@@ -6688,13 +6688,13 @@
         <v>599</v>
       </c>
       <c r="F115">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G115">
         <v>1</v>
       </c>
       <c r="H115">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I115">
         <v>1</v>
@@ -6711,19 +6711,19 @@
     </row>
     <row r="116" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="B116" t="s">
-        <v>281</v>
+        <v>238</v>
       </c>
       <c r="C116" t="s">
-        <v>282</v>
+        <v>239</v>
       </c>
       <c r="D116" t="s">
         <v>599</v>
       </c>
       <c r="E116" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="F116">
         <v>1</v>
@@ -6732,7 +6732,7 @@
         <v>0</v>
       </c>
       <c r="H116">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I116">
         <v>1</v>
@@ -6749,13 +6749,13 @@
     </row>
     <row r="117" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>374</v>
+        <v>237</v>
       </c>
       <c r="B117" t="s">
-        <v>391</v>
+        <v>240</v>
       </c>
       <c r="C117" t="s">
-        <v>392</v>
+        <v>241</v>
       </c>
       <c r="D117" t="s">
         <v>599</v>
@@ -6767,33 +6767,33 @@
         <v>1</v>
       </c>
       <c r="G117">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H117">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I117">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J117">
         <v>1</v>
       </c>
       <c r="K117">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L117" t="s">
         <v>599</v>
       </c>
     </row>
-    <row r="118" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>374</v>
+        <v>237</v>
       </c>
       <c r="B118" t="s">
-        <v>405</v>
+        <v>242</v>
       </c>
       <c r="C118" t="s">
-        <v>406</v>
+        <v>243</v>
       </c>
       <c r="D118" t="s">
         <v>599</v>
@@ -6802,10 +6802,10 @@
         <v>600</v>
       </c>
       <c r="F118">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G118">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H118">
         <v>0</v>
@@ -6814,39 +6814,39 @@
         <v>0</v>
       </c>
       <c r="J118">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K118">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L118" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="119" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>374</v>
+        <v>244</v>
       </c>
       <c r="B119" t="s">
-        <v>393</v>
+        <v>245</v>
       </c>
       <c r="C119" t="s">
-        <v>394</v>
+        <v>246</v>
       </c>
       <c r="D119" t="s">
         <v>599</v>
       </c>
       <c r="E119" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="F119">
         <v>0</v>
       </c>
       <c r="G119">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H119">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I119">
         <v>0</v>
@@ -6866,10 +6866,10 @@
         <v>244</v>
       </c>
       <c r="B120" t="s">
-        <v>283</v>
+        <v>247</v>
       </c>
       <c r="C120" t="s">
-        <v>284</v>
+        <v>248</v>
       </c>
       <c r="D120" t="s">
         <v>599</v>
@@ -6881,19 +6881,19 @@
         <v>0</v>
       </c>
       <c r="G120">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H120">
         <v>0</v>
       </c>
       <c r="I120">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J120">
         <v>1</v>
       </c>
       <c r="K120">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L120" t="s">
         <v>599</v>
@@ -6901,37 +6901,37 @@
     </row>
     <row r="121" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>526</v>
+        <v>244</v>
       </c>
       <c r="B121" t="s">
-        <v>545</v>
+        <v>249</v>
       </c>
       <c r="C121" t="s">
-        <v>546</v>
+        <v>250</v>
       </c>
       <c r="D121" t="s">
         <v>599</v>
       </c>
       <c r="E121" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="F121">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G121">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H121">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I121">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J121">
         <v>1</v>
       </c>
       <c r="K121">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L121" t="s">
         <v>599</v>
@@ -6939,13 +6939,13 @@
     </row>
     <row r="122" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>20</v>
+        <v>244</v>
       </c>
       <c r="B122" t="s">
-        <v>37</v>
+        <v>251</v>
       </c>
       <c r="C122" t="s">
-        <v>38</v>
+        <v>252</v>
       </c>
       <c r="D122" t="s">
         <v>599</v>
@@ -6954,13 +6954,13 @@
         <v>599</v>
       </c>
       <c r="F122">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G122">
         <v>1</v>
       </c>
       <c r="H122">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I122">
         <v>1</v>
@@ -6980,10 +6980,10 @@
         <v>244</v>
       </c>
       <c r="B123" t="s">
-        <v>285</v>
+        <v>253</v>
       </c>
       <c r="C123" t="s">
-        <v>286</v>
+        <v>254</v>
       </c>
       <c r="D123" t="s">
         <v>599</v>
@@ -6992,16 +6992,16 @@
         <v>599</v>
       </c>
       <c r="F123">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G123">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H123">
         <v>0</v>
       </c>
       <c r="I123">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J123">
         <v>1</v>
@@ -7015,31 +7015,31 @@
     </row>
     <row r="124" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>3</v>
+        <v>244</v>
       </c>
       <c r="B124" t="s">
-        <v>8</v>
+        <v>255</v>
       </c>
       <c r="C124" t="s">
-        <v>9</v>
+        <v>256</v>
       </c>
       <c r="D124" t="s">
         <v>599</v>
       </c>
       <c r="E124" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="F124">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G124">
         <v>0</v>
       </c>
       <c r="H124">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I124">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J124">
         <v>1</v>
@@ -7053,19 +7053,19 @@
     </row>
     <row r="125" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>20</v>
+        <v>244</v>
       </c>
       <c r="B125" t="s">
-        <v>39</v>
+        <v>257</v>
       </c>
       <c r="C125" t="s">
-        <v>40</v>
+        <v>258</v>
       </c>
       <c r="D125" t="s">
         <v>599</v>
       </c>
       <c r="E125" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="F125">
         <v>1</v>
@@ -7083,7 +7083,7 @@
         <v>1</v>
       </c>
       <c r="K125">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L125" t="s">
         <v>599</v>
@@ -7094,10 +7094,10 @@
         <v>244</v>
       </c>
       <c r="B126" t="s">
-        <v>287</v>
+        <v>259</v>
       </c>
       <c r="C126" t="s">
-        <v>288</v>
+        <v>260</v>
       </c>
       <c r="D126" t="s">
         <v>599</v>
@@ -7106,16 +7106,16 @@
         <v>599</v>
       </c>
       <c r="F126">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G126">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H126">
         <v>0</v>
       </c>
       <c r="I126">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J126">
         <v>1</v>
@@ -7129,25 +7129,25 @@
     </row>
     <row r="127" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>48</v>
+        <v>244</v>
       </c>
       <c r="B127" t="s">
-        <v>53</v>
+        <v>261</v>
       </c>
       <c r="C127" t="s">
-        <v>54</v>
+        <v>262</v>
       </c>
       <c r="D127" t="s">
         <v>599</v>
       </c>
       <c r="E127" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="F127">
         <v>1</v>
       </c>
       <c r="G127">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H127">
         <v>1</v>
@@ -7167,19 +7167,19 @@
     </row>
     <row r="128" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>374</v>
+        <v>244</v>
       </c>
       <c r="B128" t="s">
-        <v>395</v>
+        <v>263</v>
       </c>
       <c r="C128" t="s">
-        <v>396</v>
+        <v>264</v>
       </c>
       <c r="D128" t="s">
         <v>599</v>
       </c>
       <c r="E128" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="F128">
         <v>1</v>
@@ -7188,10 +7188,10 @@
         <v>0</v>
       </c>
       <c r="H128">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I128">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J128">
         <v>1</v>
@@ -7205,13 +7205,13 @@
     </row>
     <row r="129" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>3</v>
+        <v>244</v>
       </c>
       <c r="B129" t="s">
-        <v>10</v>
+        <v>265</v>
       </c>
       <c r="C129" t="s">
-        <v>11</v>
+        <v>266</v>
       </c>
       <c r="D129" t="s">
         <v>599</v>
@@ -7220,10 +7220,10 @@
         <v>600</v>
       </c>
       <c r="F129">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G129">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H129">
         <v>1</v>
@@ -7235,7 +7235,7 @@
         <v>1</v>
       </c>
       <c r="K129">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L129" t="s">
         <v>599</v>
@@ -7246,10 +7246,10 @@
         <v>244</v>
       </c>
       <c r="B130" t="s">
-        <v>289</v>
+        <v>267</v>
       </c>
       <c r="C130" t="s">
-        <v>290</v>
+        <v>268</v>
       </c>
       <c r="D130" t="s">
         <v>599</v>
@@ -7258,13 +7258,13 @@
         <v>599</v>
       </c>
       <c r="F130">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G130">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H130">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I130">
         <v>1</v>
@@ -7273,7 +7273,7 @@
         <v>1</v>
       </c>
       <c r="K130">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L130" t="s">
         <v>599</v>
@@ -7281,69 +7281,69 @@
     </row>
     <row r="131" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>69</v>
+        <v>244</v>
       </c>
       <c r="B131" t="s">
-        <v>162</v>
+        <v>269</v>
       </c>
       <c r="C131" t="s">
-        <v>163</v>
+        <v>270</v>
       </c>
       <c r="D131" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="E131" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="F131">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G131">
         <v>1</v>
       </c>
       <c r="H131">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I131">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J131">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K131">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L131" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="132" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>453</v>
+        <v>244</v>
       </c>
       <c r="B132" t="s">
-        <v>486</v>
+        <v>271</v>
       </c>
       <c r="C132" t="s">
-        <v>487</v>
+        <v>272</v>
       </c>
       <c r="D132" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="E132" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="F132">
         <v>0</v>
       </c>
       <c r="G132">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H132">
         <v>0</v>
       </c>
       <c r="I132">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J132">
         <v>1</v>
@@ -7352,27 +7352,27 @@
         <v>1</v>
       </c>
       <c r="L132" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="133" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>374</v>
+        <v>244</v>
       </c>
       <c r="B133" t="s">
-        <v>397</v>
+        <v>273</v>
       </c>
       <c r="C133" t="s">
-        <v>398</v>
+        <v>274</v>
       </c>
       <c r="D133" t="s">
         <v>599</v>
       </c>
       <c r="E133" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="F133">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G133">
         <v>0</v>
@@ -7398,10 +7398,10 @@
         <v>244</v>
       </c>
       <c r="B134" t="s">
-        <v>291</v>
+        <v>275</v>
       </c>
       <c r="C134" t="s">
-        <v>292</v>
+        <v>276</v>
       </c>
       <c r="D134" t="s">
         <v>599</v>
@@ -7410,7 +7410,7 @@
         <v>599</v>
       </c>
       <c r="F134">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G134">
         <v>0</v>
@@ -7433,13 +7433,13 @@
     </row>
     <row r="135" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>20</v>
+        <v>244</v>
       </c>
       <c r="B135" t="s">
-        <v>41</v>
+        <v>277</v>
       </c>
       <c r="C135" t="s">
-        <v>42</v>
+        <v>278</v>
       </c>
       <c r="D135" t="s">
         <v>599</v>
@@ -7457,7 +7457,7 @@
         <v>0</v>
       </c>
       <c r="I135">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J135">
         <v>1</v>
@@ -7474,10 +7474,10 @@
         <v>244</v>
       </c>
       <c r="B136" t="s">
-        <v>293</v>
+        <v>279</v>
       </c>
       <c r="C136" t="s">
-        <v>294</v>
+        <v>280</v>
       </c>
       <c r="D136" t="s">
         <v>599</v>
@@ -7489,10 +7489,10 @@
         <v>0</v>
       </c>
       <c r="G136">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H136">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I136">
         <v>1</v>
@@ -7501,7 +7501,7 @@
         <v>1</v>
       </c>
       <c r="K136">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L136" t="s">
         <v>599</v>
@@ -7512,10 +7512,10 @@
         <v>244</v>
       </c>
       <c r="B137" t="s">
-        <v>295</v>
+        <v>281</v>
       </c>
       <c r="C137" t="s">
-        <v>296</v>
+        <v>282</v>
       </c>
       <c r="D137" t="s">
         <v>599</v>
@@ -7530,7 +7530,7 @@
         <v>0</v>
       </c>
       <c r="H137">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I137">
         <v>1</v>
@@ -7539,7 +7539,7 @@
         <v>1</v>
       </c>
       <c r="K137">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L137" t="s">
         <v>599</v>
@@ -7547,22 +7547,22 @@
     </row>
     <row r="138" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>69</v>
+        <v>244</v>
       </c>
       <c r="B138" t="s">
-        <v>164</v>
+        <v>283</v>
       </c>
       <c r="C138" t="s">
-        <v>165</v>
+        <v>284</v>
       </c>
       <c r="D138" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="E138" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="F138">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G138">
         <v>1</v>
@@ -7580,7 +7580,7 @@
         <v>1</v>
       </c>
       <c r="L138" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="139" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -7588,10 +7588,10 @@
         <v>244</v>
       </c>
       <c r="B139" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
       <c r="C139" t="s">
-        <v>298</v>
+        <v>286</v>
       </c>
       <c r="D139" t="s">
         <v>599</v>
@@ -7603,10 +7603,10 @@
         <v>1</v>
       </c>
       <c r="G139">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H139">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I139">
         <v>1</v>
@@ -7623,19 +7623,19 @@
     </row>
     <row r="140" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>526</v>
+        <v>244</v>
       </c>
       <c r="B140" t="s">
-        <v>549</v>
+        <v>287</v>
       </c>
       <c r="C140" t="s">
-        <v>550</v>
+        <v>288</v>
       </c>
       <c r="D140" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="E140" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="F140">
         <v>1</v>
@@ -7644,45 +7644,45 @@
         <v>0</v>
       </c>
       <c r="H140">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I140">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J140">
         <v>1</v>
       </c>
       <c r="K140">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L140" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="141" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>453</v>
+        <v>244</v>
       </c>
       <c r="B141" t="s">
-        <v>488</v>
+        <v>289</v>
       </c>
       <c r="C141" t="s">
-        <v>489</v>
+        <v>290</v>
       </c>
       <c r="D141" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="E141" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="F141">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G141">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H141">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I141">
         <v>1</v>
@@ -7691,33 +7691,33 @@
         <v>1</v>
       </c>
       <c r="K141">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L141" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="142" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>363</v>
+        <v>244</v>
       </c>
       <c r="B142" t="s">
-        <v>368</v>
+        <v>291</v>
       </c>
       <c r="C142" t="s">
-        <v>369</v>
+        <v>292</v>
       </c>
       <c r="D142" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="E142" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="F142">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G142">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H142">
         <v>0</v>
@@ -7732,7 +7732,7 @@
         <v>0</v>
       </c>
       <c r="L142" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="143" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -7740,10 +7740,10 @@
         <v>244</v>
       </c>
       <c r="B143" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="C143" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="D143" t="s">
         <v>599</v>
@@ -7755,10 +7755,10 @@
         <v>0</v>
       </c>
       <c r="G143">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H143">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I143">
         <v>1</v>
@@ -7767,7 +7767,7 @@
         <v>1</v>
       </c>
       <c r="K143">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L143" t="s">
         <v>599</v>
@@ -7775,28 +7775,28 @@
     </row>
     <row r="144" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>453</v>
+        <v>244</v>
       </c>
       <c r="B144" t="s">
-        <v>490</v>
+        <v>295</v>
       </c>
       <c r="C144" t="s">
-        <v>491</v>
+        <v>296</v>
       </c>
       <c r="D144" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="E144" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="F144">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G144">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H144">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I144">
         <v>1</v>
@@ -7805,10 +7805,10 @@
         <v>1</v>
       </c>
       <c r="K144">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L144" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="145" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -7816,10 +7816,10 @@
         <v>244</v>
       </c>
       <c r="B145" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="C145" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="D145" t="s">
         <v>599</v>
@@ -7828,16 +7828,16 @@
         <v>599</v>
       </c>
       <c r="F145">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G145">
         <v>1</v>
       </c>
       <c r="H145">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I145">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J145">
         <v>1</v>
@@ -7854,10 +7854,10 @@
         <v>244</v>
       </c>
       <c r="B146" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C146" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="D146" t="s">
         <v>599</v>
@@ -7866,13 +7866,13 @@
         <v>599</v>
       </c>
       <c r="F146">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G146">
         <v>1</v>
       </c>
       <c r="H146">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I146">
         <v>1</v>
@@ -7892,10 +7892,10 @@
         <v>244</v>
       </c>
       <c r="B147" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="C147" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="D147" t="s">
         <v>599</v>
@@ -7904,22 +7904,22 @@
         <v>599</v>
       </c>
       <c r="F147">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G147">
         <v>1</v>
       </c>
       <c r="H147">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I147">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J147">
         <v>1</v>
       </c>
       <c r="K147">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L147" t="s">
         <v>599</v>
@@ -7930,10 +7930,10 @@
         <v>244</v>
       </c>
       <c r="B148" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="C148" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="D148" t="s">
         <v>599</v>
@@ -7942,22 +7942,22 @@
         <v>599</v>
       </c>
       <c r="F148">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G148">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H148">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I148">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J148">
         <v>1</v>
       </c>
       <c r="K148">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L148" t="s">
         <v>599</v>
@@ -7965,19 +7965,19 @@
     </row>
     <row r="149" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>20</v>
+        <v>244</v>
       </c>
       <c r="B149" t="s">
-        <v>43</v>
+        <v>305</v>
       </c>
       <c r="C149" t="s">
-        <v>44</v>
+        <v>306</v>
       </c>
       <c r="D149" t="s">
         <v>599</v>
       </c>
       <c r="E149" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="F149">
         <v>1</v>
@@ -7995,7 +7995,7 @@
         <v>1</v>
       </c>
       <c r="K149">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L149" t="s">
         <v>599</v>
@@ -8003,13 +8003,13 @@
     </row>
     <row r="150" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>374</v>
+        <v>244</v>
       </c>
       <c r="B150" t="s">
-        <v>399</v>
+        <v>307</v>
       </c>
       <c r="C150" t="s">
-        <v>400</v>
+        <v>308</v>
       </c>
       <c r="D150" t="s">
         <v>599</v>
@@ -8079,37 +8079,37 @@
     </row>
     <row r="152" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>374</v>
+        <v>244</v>
       </c>
       <c r="B152" t="s">
-        <v>401</v>
+        <v>311</v>
       </c>
       <c r="C152" t="s">
-        <v>402</v>
+        <v>312</v>
       </c>
       <c r="D152" t="s">
         <v>599</v>
       </c>
       <c r="E152" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="F152">
         <v>1</v>
       </c>
       <c r="G152">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H152">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I152">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J152">
         <v>1</v>
       </c>
       <c r="K152">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L152" t="s">
         <v>599</v>
@@ -8120,10 +8120,10 @@
         <v>244</v>
       </c>
       <c r="B153" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="C153" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="D153" t="s">
         <v>599</v>
@@ -8132,19 +8132,19 @@
         <v>599</v>
       </c>
       <c r="F153">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G153">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H153">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I153">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J153">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K153">
         <v>1</v>
@@ -8155,31 +8155,31 @@
     </row>
     <row r="154" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>374</v>
+        <v>244</v>
       </c>
       <c r="B154" t="s">
-        <v>403</v>
+        <v>313</v>
       </c>
       <c r="C154" t="s">
-        <v>404</v>
+        <v>314</v>
       </c>
       <c r="D154" t="s">
         <v>599</v>
       </c>
       <c r="E154" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="F154">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G154">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H154">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I154">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J154">
         <v>1</v>
@@ -8193,34 +8193,34 @@
     </row>
     <row r="155" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>374</v>
+        <v>244</v>
       </c>
       <c r="B155" t="s">
-        <v>407</v>
+        <v>327</v>
       </c>
       <c r="C155" t="s">
-        <v>408</v>
+        <v>328</v>
       </c>
       <c r="D155" t="s">
         <v>599</v>
       </c>
       <c r="E155" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="F155">
         <v>0</v>
       </c>
       <c r="G155">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H155">
         <v>0</v>
       </c>
       <c r="I155">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J155">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K155">
         <v>1</v>
@@ -8234,10 +8234,10 @@
         <v>244</v>
       </c>
       <c r="B156" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="C156" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="D156" t="s">
         <v>599</v>
@@ -8246,7 +8246,7 @@
         <v>599</v>
       </c>
       <c r="F156">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G156">
         <v>0</v>
@@ -8255,10 +8255,10 @@
         <v>0</v>
       </c>
       <c r="I156">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J156">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K156">
         <v>1</v>
@@ -8269,40 +8269,40 @@
     </row>
     <row r="157" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>526</v>
+        <v>244</v>
       </c>
       <c r="B157" t="s">
-        <v>551</v>
+        <v>317</v>
       </c>
       <c r="C157" t="s">
-        <v>552</v>
+        <v>318</v>
       </c>
       <c r="D157" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="E157" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="F157">
         <v>1</v>
       </c>
       <c r="G157">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H157">
         <v>1</v>
       </c>
       <c r="I157">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J157">
         <v>1</v>
       </c>
       <c r="K157">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L157" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="158" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -8310,10 +8310,10 @@
         <v>244</v>
       </c>
       <c r="B158" t="s">
-        <v>313</v>
+        <v>333</v>
       </c>
       <c r="C158" t="s">
-        <v>314</v>
+        <v>334</v>
       </c>
       <c r="D158" t="s">
         <v>599</v>
@@ -8322,22 +8322,22 @@
         <v>599</v>
       </c>
       <c r="F158">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G158">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H158">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I158">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J158">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K158">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L158" t="s">
         <v>599</v>
@@ -8345,13 +8345,13 @@
     </row>
     <row r="159" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="B159" t="s">
-        <v>235</v>
+        <v>321</v>
       </c>
       <c r="C159" t="s">
-        <v>236</v>
+        <v>322</v>
       </c>
       <c r="D159" t="s">
         <v>599</v>
@@ -8363,7 +8363,7 @@
         <v>1</v>
       </c>
       <c r="G159">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H159">
         <v>1</v>
@@ -8375,7 +8375,7 @@
         <v>1</v>
       </c>
       <c r="K159">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L159" t="s">
         <v>599</v>
@@ -8386,10 +8386,10 @@
         <v>244</v>
       </c>
       <c r="B160" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="C160" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="D160" t="s">
         <v>599</v>
@@ -8398,22 +8398,22 @@
         <v>599</v>
       </c>
       <c r="F160">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G160">
         <v>0</v>
       </c>
       <c r="H160">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I160">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J160">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K160">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L160" t="s">
         <v>599</v>
@@ -8424,10 +8424,10 @@
         <v>244</v>
       </c>
       <c r="B161" t="s">
-        <v>315</v>
+        <v>325</v>
       </c>
       <c r="C161" t="s">
-        <v>316</v>
+        <v>326</v>
       </c>
       <c r="D161" t="s">
         <v>599</v>
@@ -8442,7 +8442,7 @@
         <v>0</v>
       </c>
       <c r="H161">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I161">
         <v>1</v>
@@ -8451,7 +8451,7 @@
         <v>1</v>
       </c>
       <c r="K161">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L161" t="s">
         <v>599</v>
@@ -8462,10 +8462,10 @@
         <v>244</v>
       </c>
       <c r="B162" t="s">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="C162" t="s">
-        <v>318</v>
+        <v>330</v>
       </c>
       <c r="D162" t="s">
         <v>599</v>
@@ -8477,7 +8477,7 @@
         <v>1</v>
       </c>
       <c r="G162">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H162">
         <v>1</v>
@@ -8489,7 +8489,7 @@
         <v>1</v>
       </c>
       <c r="K162">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L162" t="s">
         <v>599</v>
@@ -8500,10 +8500,10 @@
         <v>244</v>
       </c>
       <c r="B163" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C163" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="D163" t="s">
         <v>599</v>
@@ -8512,22 +8512,22 @@
         <v>599</v>
       </c>
       <c r="F163">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G163">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H163">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I163">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J163">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K163">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L163" t="s">
         <v>599</v>
@@ -8535,31 +8535,31 @@
     </row>
     <row r="164" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>48</v>
+        <v>244</v>
       </c>
       <c r="B164" t="s">
-        <v>55</v>
+        <v>335</v>
       </c>
       <c r="C164" t="s">
-        <v>56</v>
+        <v>336</v>
       </c>
       <c r="D164" t="s">
         <v>599</v>
       </c>
       <c r="E164" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="F164">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G164">
         <v>0</v>
       </c>
       <c r="H164">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I164">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J164">
         <v>1</v>
@@ -8573,13 +8573,13 @@
     </row>
     <row r="165" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>374</v>
+        <v>244</v>
       </c>
       <c r="B165" t="s">
-        <v>409</v>
+        <v>337</v>
       </c>
       <c r="C165" t="s">
-        <v>410</v>
+        <v>338</v>
       </c>
       <c r="D165" t="s">
         <v>599</v>
@@ -8588,10 +8588,10 @@
         <v>599</v>
       </c>
       <c r="F165">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G165">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H165">
         <v>0</v>
@@ -8603,7 +8603,7 @@
         <v>1</v>
       </c>
       <c r="K165">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L165" t="s">
         <v>599</v>
@@ -8611,25 +8611,25 @@
     </row>
     <row r="166" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>526</v>
+        <v>244</v>
       </c>
       <c r="B166" t="s">
-        <v>553</v>
+        <v>339</v>
       </c>
       <c r="C166" t="s">
-        <v>554</v>
+        <v>340</v>
       </c>
       <c r="D166" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="E166" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="F166">
         <v>0</v>
       </c>
       <c r="G166">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H166">
         <v>0</v>
@@ -8641,27 +8641,27 @@
         <v>1</v>
       </c>
       <c r="K166">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L166" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="167" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>374</v>
+        <v>244</v>
       </c>
       <c r="B167" t="s">
-        <v>411</v>
+        <v>341</v>
       </c>
       <c r="C167" t="s">
-        <v>412</v>
+        <v>342</v>
       </c>
       <c r="D167" t="s">
         <v>599</v>
       </c>
       <c r="E167" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="F167">
         <v>0</v>
@@ -8690,10 +8690,10 @@
         <v>244</v>
       </c>
       <c r="B168" t="s">
-        <v>321</v>
+        <v>343</v>
       </c>
       <c r="C168" t="s">
-        <v>322</v>
+        <v>344</v>
       </c>
       <c r="D168" t="s">
         <v>599</v>
@@ -8705,7 +8705,7 @@
         <v>1</v>
       </c>
       <c r="G168">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H168">
         <v>1</v>
@@ -8725,13 +8725,13 @@
     </row>
     <row r="169" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>374</v>
+        <v>244</v>
       </c>
       <c r="B169" t="s">
-        <v>413</v>
+        <v>345</v>
       </c>
       <c r="C169" t="s">
-        <v>414</v>
+        <v>346</v>
       </c>
       <c r="D169" t="s">
         <v>599</v>
@@ -8746,7 +8746,7 @@
         <v>1</v>
       </c>
       <c r="H169">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I169">
         <v>1</v>
@@ -8755,7 +8755,7 @@
         <v>1</v>
       </c>
       <c r="K169">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L169" t="s">
         <v>599</v>
@@ -8763,37 +8763,37 @@
     </row>
     <row r="170" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>374</v>
+        <v>244</v>
       </c>
       <c r="B170" t="s">
-        <v>415</v>
+        <v>347</v>
       </c>
       <c r="C170" t="s">
-        <v>416</v>
+        <v>348</v>
       </c>
       <c r="D170" t="s">
         <v>599</v>
       </c>
       <c r="E170" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="F170">
         <v>0</v>
       </c>
       <c r="G170">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H170">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I170">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J170">
         <v>1</v>
       </c>
       <c r="K170">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L170" t="s">
         <v>599</v>
@@ -8801,25 +8801,25 @@
     </row>
     <row r="171" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>48</v>
+        <v>244</v>
       </c>
       <c r="B171" t="s">
-        <v>57</v>
+        <v>349</v>
       </c>
       <c r="C171" t="s">
-        <v>58</v>
+        <v>350</v>
       </c>
       <c r="D171" t="s">
         <v>599</v>
       </c>
       <c r="E171" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="F171">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G171">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H171">
         <v>1</v>
@@ -8842,10 +8842,10 @@
         <v>244</v>
       </c>
       <c r="B172" t="s">
-        <v>323</v>
+        <v>351</v>
       </c>
       <c r="C172" t="s">
-        <v>324</v>
+        <v>352</v>
       </c>
       <c r="D172" t="s">
         <v>599</v>
@@ -8877,28 +8877,28 @@
     </row>
     <row r="173" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
-        <v>374</v>
+        <v>244</v>
       </c>
       <c r="B173" t="s">
-        <v>417</v>
+        <v>353</v>
       </c>
       <c r="C173" t="s">
-        <v>418</v>
+        <v>354</v>
       </c>
       <c r="D173" t="s">
         <v>599</v>
       </c>
       <c r="E173" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="F173">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G173">
         <v>1</v>
       </c>
       <c r="H173">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I173">
         <v>1</v>
@@ -8907,7 +8907,7 @@
         <v>1</v>
       </c>
       <c r="K173">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L173" t="s">
         <v>599</v>
@@ -8915,37 +8915,37 @@
     </row>
     <row r="174" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
-        <v>374</v>
+        <v>244</v>
       </c>
       <c r="B174" t="s">
-        <v>419</v>
+        <v>355</v>
       </c>
       <c r="C174" t="s">
-        <v>420</v>
+        <v>356</v>
       </c>
       <c r="D174" t="s">
         <v>599</v>
       </c>
       <c r="E174" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="F174">
         <v>0</v>
       </c>
       <c r="G174">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H174">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I174">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J174">
         <v>1</v>
       </c>
       <c r="K174">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L174" t="s">
         <v>599</v>
@@ -8956,10 +8956,10 @@
         <v>244</v>
       </c>
       <c r="B175" t="s">
-        <v>325</v>
+        <v>357</v>
       </c>
       <c r="C175" t="s">
-        <v>326</v>
+        <v>358</v>
       </c>
       <c r="D175" t="s">
         <v>599</v>
@@ -8974,7 +8974,7 @@
         <v>0</v>
       </c>
       <c r="H175">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I175">
         <v>1</v>
@@ -8983,7 +8983,7 @@
         <v>1</v>
       </c>
       <c r="K175">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L175" t="s">
         <v>599</v>
@@ -8991,19 +8991,19 @@
     </row>
     <row r="176" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
-        <v>3</v>
+        <v>244</v>
       </c>
       <c r="B176" t="s">
-        <v>14</v>
+        <v>359</v>
       </c>
       <c r="C176" t="s">
-        <v>15</v>
+        <v>360</v>
       </c>
       <c r="D176" t="s">
         <v>599</v>
       </c>
       <c r="E176" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="F176">
         <v>1</v>
@@ -9029,31 +9029,31 @@
     </row>
     <row r="177" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
-        <v>374</v>
+        <v>244</v>
       </c>
       <c r="B177" t="s">
-        <v>421</v>
+        <v>361</v>
       </c>
       <c r="C177" t="s">
-        <v>422</v>
+        <v>362</v>
       </c>
       <c r="D177" t="s">
         <v>599</v>
       </c>
       <c r="E177" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="F177">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G177">
         <v>0</v>
       </c>
       <c r="H177">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I177">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J177">
         <v>1</v>
@@ -9067,13 +9067,13 @@
     </row>
     <row r="178" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
-        <v>69</v>
+        <v>363</v>
       </c>
       <c r="B178" t="s">
-        <v>166</v>
+        <v>364</v>
       </c>
       <c r="C178" t="s">
-        <v>167</v>
+        <v>365</v>
       </c>
       <c r="D178" t="s">
         <v>600</v>
@@ -9082,13 +9082,13 @@
         <v>600</v>
       </c>
       <c r="F178">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G178">
         <v>1</v>
       </c>
       <c r="H178">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I178">
         <v>1</v>
@@ -9097,7 +9097,7 @@
         <v>1</v>
       </c>
       <c r="K178">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L178" t="s">
         <v>600</v>
@@ -9105,13 +9105,13 @@
     </row>
     <row r="179" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
-        <v>374</v>
+        <v>363</v>
       </c>
       <c r="B179" t="s">
-        <v>423</v>
+        <v>366</v>
       </c>
       <c r="C179" t="s">
-        <v>424</v>
+        <v>367</v>
       </c>
       <c r="D179" t="s">
         <v>599</v>
@@ -9120,13 +9120,13 @@
         <v>600</v>
       </c>
       <c r="F179">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G179">
         <v>0</v>
       </c>
       <c r="H179">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I179">
         <v>0</v>
@@ -9143,13 +9143,13 @@
     </row>
     <row r="180" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
-        <v>69</v>
+        <v>363</v>
       </c>
       <c r="B180" t="s">
-        <v>168</v>
+        <v>368</v>
       </c>
       <c r="C180" t="s">
-        <v>169</v>
+        <v>369</v>
       </c>
       <c r="D180" t="s">
         <v>600</v>
@@ -9158,16 +9158,16 @@
         <v>600</v>
       </c>
       <c r="F180">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G180">
         <v>1</v>
       </c>
       <c r="H180">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I180">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J180">
         <v>1</v>
@@ -9181,13 +9181,13 @@
     </row>
     <row r="181" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>69</v>
+        <v>363</v>
       </c>
       <c r="B181" t="s">
-        <v>170</v>
+        <v>372</v>
       </c>
       <c r="C181" t="s">
-        <v>171</v>
+        <v>373</v>
       </c>
       <c r="D181" t="s">
         <v>600</v>
@@ -9199,7 +9199,7 @@
         <v>0</v>
       </c>
       <c r="G181">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H181">
         <v>0</v>
@@ -9211,7 +9211,7 @@
         <v>1</v>
       </c>
       <c r="K181">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L181" t="s">
         <v>600</v>
@@ -9219,13 +9219,13 @@
     </row>
     <row r="182" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
-        <v>69</v>
+        <v>363</v>
       </c>
       <c r="B182" t="s">
-        <v>172</v>
+        <v>370</v>
       </c>
       <c r="C182" t="s">
-        <v>173</v>
+        <v>371</v>
       </c>
       <c r="D182" t="s">
         <v>600</v>
@@ -9234,19 +9234,19 @@
         <v>600</v>
       </c>
       <c r="F182">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G182">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H182">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I182">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J182">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K182">
         <v>1</v>
@@ -9257,37 +9257,37 @@
     </row>
     <row r="183" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
-        <v>244</v>
+        <v>374</v>
       </c>
       <c r="B183" t="s">
-        <v>329</v>
+        <v>375</v>
       </c>
       <c r="C183" t="s">
-        <v>330</v>
+        <v>376</v>
       </c>
       <c r="D183" t="s">
         <v>599</v>
       </c>
       <c r="E183" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="F183">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G183">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H183">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I183">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J183">
         <v>1</v>
       </c>
       <c r="K183">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L183" t="s">
         <v>599</v>
@@ -9298,10 +9298,10 @@
         <v>374</v>
       </c>
       <c r="B184" t="s">
-        <v>425</v>
+        <v>377</v>
       </c>
       <c r="C184" t="s">
-        <v>426</v>
+        <v>378</v>
       </c>
       <c r="D184" t="s">
         <v>599</v>
@@ -9316,10 +9316,10 @@
         <v>0</v>
       </c>
       <c r="H184">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I184">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J184">
         <v>1</v>
@@ -9333,13 +9333,13 @@
     </row>
     <row r="185" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
-        <v>453</v>
+        <v>374</v>
       </c>
       <c r="B185" t="s">
-        <v>492</v>
+        <v>379</v>
       </c>
       <c r="C185" t="s">
-        <v>493</v>
+        <v>380</v>
       </c>
       <c r="D185" t="s">
         <v>600</v>
@@ -9351,7 +9351,7 @@
         <v>0</v>
       </c>
       <c r="G185">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H185">
         <v>0</v>
@@ -9363,7 +9363,7 @@
         <v>1</v>
       </c>
       <c r="K185">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L185" t="s">
         <v>600</v>
@@ -9371,13 +9371,13 @@
     </row>
     <row r="186" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>244</v>
+        <v>374</v>
       </c>
       <c r="B186" t="s">
-        <v>331</v>
+        <v>381</v>
       </c>
       <c r="C186" t="s">
-        <v>332</v>
+        <v>382</v>
       </c>
       <c r="D186" t="s">
         <v>599</v>
@@ -9386,10 +9386,10 @@
         <v>599</v>
       </c>
       <c r="F186">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G186">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H186">
         <v>1</v>
@@ -9409,28 +9409,28 @@
     </row>
     <row r="187" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
-        <v>526</v>
+        <v>374</v>
       </c>
       <c r="B187" t="s">
-        <v>557</v>
+        <v>383</v>
       </c>
       <c r="C187" t="s">
-        <v>558</v>
+        <v>384</v>
       </c>
       <c r="D187" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="E187" t="s">
         <v>600</v>
       </c>
       <c r="F187">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G187">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H187">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I187">
         <v>0</v>
@@ -9439,21 +9439,21 @@
         <v>1</v>
       </c>
       <c r="K187">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L187" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="188" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
-        <v>526</v>
+        <v>374</v>
       </c>
       <c r="B188" t="s">
-        <v>555</v>
+        <v>389</v>
       </c>
       <c r="C188" t="s">
-        <v>556</v>
+        <v>390</v>
       </c>
       <c r="D188" t="s">
         <v>599</v>
@@ -9468,7 +9468,7 @@
         <v>0</v>
       </c>
       <c r="H188">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I188">
         <v>1</v>
@@ -9477,21 +9477,21 @@
         <v>0</v>
       </c>
       <c r="K188">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L188" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="189" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
-        <v>3</v>
+        <v>374</v>
       </c>
       <c r="B189" t="s">
-        <v>16</v>
+        <v>385</v>
       </c>
       <c r="C189" t="s">
-        <v>17</v>
+        <v>386</v>
       </c>
       <c r="D189" t="s">
         <v>599</v>
@@ -9509,7 +9509,7 @@
         <v>1</v>
       </c>
       <c r="I189">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J189">
         <v>1</v>
@@ -9523,22 +9523,22 @@
     </row>
     <row r="190" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
-        <v>526</v>
+        <v>374</v>
       </c>
       <c r="B190" t="s">
-        <v>559</v>
+        <v>387</v>
       </c>
       <c r="C190" t="s">
-        <v>560</v>
+        <v>388</v>
       </c>
       <c r="D190" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="E190" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="F190">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G190">
         <v>1</v>
@@ -9547,39 +9547,39 @@
         <v>1</v>
       </c>
       <c r="I190">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J190">
         <v>1</v>
       </c>
       <c r="K190">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L190" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="191" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
-        <v>363</v>
+        <v>374</v>
       </c>
       <c r="B191" t="s">
-        <v>372</v>
+        <v>391</v>
       </c>
       <c r="C191" t="s">
-        <v>373</v>
+        <v>392</v>
       </c>
       <c r="D191" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="E191" t="s">
         <v>600</v>
       </c>
       <c r="F191">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G191">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H191">
         <v>0</v>
@@ -9591,21 +9591,21 @@
         <v>1</v>
       </c>
       <c r="K191">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L191" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="192" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
-        <v>48</v>
+        <v>374</v>
       </c>
       <c r="B192" t="s">
-        <v>59</v>
+        <v>405</v>
       </c>
       <c r="C192" t="s">
-        <v>60</v>
+        <v>406</v>
       </c>
       <c r="D192" t="s">
         <v>599</v>
@@ -9626,7 +9626,7 @@
         <v>0</v>
       </c>
       <c r="J192">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K192">
         <v>0</v>
@@ -9637,28 +9637,28 @@
     </row>
     <row r="193" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
-        <v>244</v>
+        <v>374</v>
       </c>
       <c r="B193" t="s">
-        <v>335</v>
+        <v>393</v>
       </c>
       <c r="C193" t="s">
-        <v>336</v>
+        <v>394</v>
       </c>
       <c r="D193" t="s">
         <v>599</v>
       </c>
       <c r="E193" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="F193">
         <v>0</v>
       </c>
       <c r="G193">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H193">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I193">
         <v>0</v>
@@ -9675,22 +9675,22 @@
     </row>
     <row r="194" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
-        <v>244</v>
+        <v>374</v>
       </c>
       <c r="B194" t="s">
-        <v>337</v>
+        <v>395</v>
       </c>
       <c r="C194" t="s">
-        <v>338</v>
+        <v>396</v>
       </c>
       <c r="D194" t="s">
         <v>599</v>
       </c>
       <c r="E194" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="F194">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G194">
         <v>0</v>
@@ -9699,7 +9699,7 @@
         <v>0</v>
       </c>
       <c r="I194">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J194">
         <v>1</v>
@@ -9716,10 +9716,10 @@
         <v>374</v>
       </c>
       <c r="B195" t="s">
-        <v>427</v>
+        <v>397</v>
       </c>
       <c r="C195" t="s">
-        <v>428</v>
+        <v>398</v>
       </c>
       <c r="D195" t="s">
         <v>599</v>
@@ -9754,16 +9754,16 @@
         <v>374</v>
       </c>
       <c r="B196" t="s">
-        <v>429</v>
+        <v>399</v>
       </c>
       <c r="C196" t="s">
-        <v>430</v>
+        <v>400</v>
       </c>
       <c r="D196" t="s">
         <v>599</v>
       </c>
       <c r="E196" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="F196">
         <v>0</v>
@@ -9789,25 +9789,25 @@
     </row>
     <row r="197" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>244</v>
+        <v>374</v>
       </c>
       <c r="B197" t="s">
-        <v>339</v>
+        <v>401</v>
       </c>
       <c r="C197" t="s">
-        <v>340</v>
+        <v>402</v>
       </c>
       <c r="D197" t="s">
         <v>599</v>
       </c>
       <c r="E197" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="F197">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G197">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H197">
         <v>0</v>
@@ -9819,7 +9819,7 @@
         <v>1</v>
       </c>
       <c r="K197">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L197" t="s">
         <v>599</v>
@@ -9827,13 +9827,13 @@
     </row>
     <row r="198" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
-        <v>48</v>
+        <v>374</v>
       </c>
       <c r="B198" t="s">
-        <v>61</v>
+        <v>403</v>
       </c>
       <c r="C198" t="s">
-        <v>62</v>
+        <v>404</v>
       </c>
       <c r="D198" t="s">
         <v>599</v>
@@ -9842,16 +9842,16 @@
         <v>600</v>
       </c>
       <c r="F198">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G198">
         <v>0</v>
       </c>
       <c r="H198">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I198">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J198">
         <v>1</v>
@@ -9868,10 +9868,10 @@
         <v>374</v>
       </c>
       <c r="B199" t="s">
-        <v>431</v>
+        <v>407</v>
       </c>
       <c r="C199" t="s">
-        <v>432</v>
+        <v>408</v>
       </c>
       <c r="D199" t="s">
         <v>599</v>
@@ -9883,19 +9883,19 @@
         <v>0</v>
       </c>
       <c r="G199">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H199">
         <v>0</v>
       </c>
       <c r="I199">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J199">
         <v>1</v>
       </c>
       <c r="K199">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L199" t="s">
         <v>599</v>
@@ -9906,10 +9906,10 @@
         <v>374</v>
       </c>
       <c r="B200" t="s">
-        <v>433</v>
+        <v>409</v>
       </c>
       <c r="C200" t="s">
-        <v>434</v>
+        <v>410</v>
       </c>
       <c r="D200" t="s">
         <v>599</v>
@@ -9921,10 +9921,10 @@
         <v>1</v>
       </c>
       <c r="G200">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H200">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I200">
         <v>1</v>
@@ -9933,7 +9933,7 @@
         <v>1</v>
       </c>
       <c r="K200">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L200" t="s">
         <v>599</v>
@@ -9941,19 +9941,19 @@
     </row>
     <row r="201" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
-        <v>244</v>
+        <v>374</v>
       </c>
       <c r="B201" t="s">
-        <v>341</v>
+        <v>411</v>
       </c>
       <c r="C201" t="s">
-        <v>342</v>
+        <v>412</v>
       </c>
       <c r="D201" t="s">
         <v>599</v>
       </c>
       <c r="E201" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="F201">
         <v>0</v>
@@ -9979,13 +9979,13 @@
     </row>
     <row r="202" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
-        <v>244</v>
+        <v>374</v>
       </c>
       <c r="B202" t="s">
-        <v>343</v>
+        <v>413</v>
       </c>
       <c r="C202" t="s">
-        <v>344</v>
+        <v>414</v>
       </c>
       <c r="D202" t="s">
         <v>599</v>
@@ -10000,7 +10000,7 @@
         <v>1</v>
       </c>
       <c r="H202">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I202">
         <v>1</v>
@@ -10009,7 +10009,7 @@
         <v>1</v>
       </c>
       <c r="K202">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L202" t="s">
         <v>599</v>
@@ -10017,13 +10017,13 @@
     </row>
     <row r="203" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
-        <v>69</v>
+        <v>374</v>
       </c>
       <c r="B203" t="s">
-        <v>192</v>
+        <v>415</v>
       </c>
       <c r="C203" t="s">
-        <v>193</v>
+        <v>416</v>
       </c>
       <c r="D203" t="s">
         <v>599</v>
@@ -10032,51 +10032,51 @@
         <v>600</v>
       </c>
       <c r="F203">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G203">
         <v>0</v>
       </c>
       <c r="H203">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I203">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J203">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K203">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L203" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="204" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
-        <v>244</v>
+        <v>374</v>
       </c>
       <c r="B204" t="s">
-        <v>345</v>
+        <v>417</v>
       </c>
       <c r="C204" t="s">
-        <v>346</v>
+        <v>418</v>
       </c>
       <c r="D204" t="s">
         <v>599</v>
       </c>
       <c r="E204" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="F204">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G204">
         <v>1</v>
       </c>
       <c r="H204">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I204">
         <v>1</v>
@@ -10085,7 +10085,7 @@
         <v>1</v>
       </c>
       <c r="K204">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L204" t="s">
         <v>599</v>
@@ -10093,13 +10093,13 @@
     </row>
     <row r="205" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
-        <v>237</v>
+        <v>374</v>
       </c>
       <c r="B205" t="s">
-        <v>238</v>
+        <v>419</v>
       </c>
       <c r="C205" t="s">
-        <v>239</v>
+        <v>420</v>
       </c>
       <c r="D205" t="s">
         <v>599</v>
@@ -10108,7 +10108,7 @@
         <v>600</v>
       </c>
       <c r="F205">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G205">
         <v>0</v>
@@ -10117,13 +10117,13 @@
         <v>1</v>
       </c>
       <c r="I205">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J205">
         <v>1</v>
       </c>
       <c r="K205">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L205" t="s">
         <v>599</v>
@@ -10131,13 +10131,13 @@
     </row>
     <row r="206" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>48</v>
+        <v>374</v>
       </c>
       <c r="B206" t="s">
-        <v>63</v>
+        <v>421</v>
       </c>
       <c r="C206" t="s">
-        <v>64</v>
+        <v>422</v>
       </c>
       <c r="D206" t="s">
         <v>599</v>
@@ -10146,16 +10146,16 @@
         <v>600</v>
       </c>
       <c r="F206">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G206">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H206">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I206">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J206">
         <v>1</v>
@@ -10169,13 +10169,13 @@
     </row>
     <row r="207" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
-        <v>48</v>
+        <v>374</v>
       </c>
       <c r="B207" t="s">
-        <v>65</v>
+        <v>423</v>
       </c>
       <c r="C207" t="s">
-        <v>66</v>
+        <v>424</v>
       </c>
       <c r="D207" t="s">
         <v>599</v>
@@ -10184,16 +10184,16 @@
         <v>600</v>
       </c>
       <c r="F207">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G207">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H207">
         <v>1</v>
       </c>
       <c r="I207">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J207">
         <v>1</v>
@@ -10207,25 +10207,25 @@
     </row>
     <row r="208" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
-        <v>244</v>
+        <v>374</v>
       </c>
       <c r="B208" t="s">
-        <v>347</v>
+        <v>425</v>
       </c>
       <c r="C208" t="s">
-        <v>348</v>
+        <v>426</v>
       </c>
       <c r="D208" t="s">
         <v>599</v>
       </c>
       <c r="E208" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="F208">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G208">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H208">
         <v>0</v>
@@ -10237,21 +10237,21 @@
         <v>1</v>
       </c>
       <c r="K208">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L208" t="s">
         <v>599</v>
       </c>
     </row>
-    <row r="209" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
-        <v>45</v>
+        <v>374</v>
       </c>
       <c r="B209" t="s">
-        <v>46</v>
+        <v>427</v>
       </c>
       <c r="C209" t="s">
-        <v>47</v>
+        <v>428</v>
       </c>
       <c r="D209" t="s">
         <v>599</v>
@@ -10269,27 +10269,27 @@
         <v>0</v>
       </c>
       <c r="I209">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J209">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K209">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L209" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="210" spans="1:12" x14ac:dyDescent="0.3">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="210" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
-        <v>3</v>
+        <v>374</v>
       </c>
       <c r="B210" t="s">
-        <v>4</v>
+        <v>429</v>
       </c>
       <c r="C210" t="s">
-        <v>5</v>
+        <v>430</v>
       </c>
       <c r="D210" t="s">
         <v>599</v>
@@ -10310,24 +10310,24 @@
         <v>0</v>
       </c>
       <c r="J210">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K210">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L210" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="211" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
-        <v>3</v>
+        <v>374</v>
       </c>
       <c r="B211" t="s">
-        <v>18</v>
+        <v>431</v>
       </c>
       <c r="C211" t="s">
-        <v>19</v>
+        <v>432</v>
       </c>
       <c r="D211" t="s">
         <v>599</v>
@@ -10336,22 +10336,22 @@
         <v>600</v>
       </c>
       <c r="F211">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G211">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H211">
         <v>0</v>
       </c>
       <c r="I211">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J211">
         <v>1</v>
       </c>
       <c r="K211">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L211" t="s">
         <v>599</v>
@@ -10359,13 +10359,13 @@
     </row>
     <row r="212" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
-        <v>244</v>
+        <v>374</v>
       </c>
       <c r="B212" t="s">
-        <v>349</v>
+        <v>433</v>
       </c>
       <c r="C212" t="s">
-        <v>350</v>
+        <v>434</v>
       </c>
       <c r="D212" t="s">
         <v>599</v>
@@ -10377,7 +10377,7 @@
         <v>1</v>
       </c>
       <c r="G212">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H212">
         <v>1</v>
@@ -10397,25 +10397,25 @@
     </row>
     <row r="213" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
-        <v>244</v>
+        <v>374</v>
       </c>
       <c r="B213" t="s">
-        <v>351</v>
+        <v>435</v>
       </c>
       <c r="C213" t="s">
-        <v>352</v>
+        <v>436</v>
       </c>
       <c r="D213" t="s">
         <v>599</v>
       </c>
       <c r="E213" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="F213">
         <v>1</v>
       </c>
       <c r="G213">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H213">
         <v>1</v>
@@ -10427,7 +10427,7 @@
         <v>1</v>
       </c>
       <c r="K213">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L213" t="s">
         <v>599</v>
@@ -10435,34 +10435,34 @@
     </row>
     <row r="214" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
-        <v>244</v>
+        <v>374</v>
       </c>
       <c r="B214" t="s">
-        <v>353</v>
+        <v>443</v>
       </c>
       <c r="C214" t="s">
-        <v>354</v>
+        <v>444</v>
       </c>
       <c r="D214" t="s">
         <v>599</v>
       </c>
       <c r="E214" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="F214">
         <v>1</v>
       </c>
       <c r="G214">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H214">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I214">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J214">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K214">
         <v>0</v>
@@ -10476,10 +10476,10 @@
         <v>374</v>
       </c>
       <c r="B215" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="C215" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="D215" t="s">
         <v>599</v>
@@ -10488,10 +10488,10 @@
         <v>600</v>
       </c>
       <c r="F215">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G215">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H215">
         <v>1</v>
@@ -10511,19 +10511,19 @@
     </row>
     <row r="216" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
-        <v>526</v>
+        <v>374</v>
       </c>
       <c r="B216" t="s">
-        <v>563</v>
+        <v>439</v>
       </c>
       <c r="C216" t="s">
-        <v>564</v>
+        <v>440</v>
       </c>
       <c r="D216" t="s">
         <v>599</v>
       </c>
       <c r="E216" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="F216">
         <v>1</v>
@@ -10549,25 +10549,25 @@
     </row>
     <row r="217" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
-        <v>526</v>
+        <v>374</v>
       </c>
       <c r="B217" t="s">
-        <v>565</v>
+        <v>441</v>
       </c>
       <c r="C217" t="s">
-        <v>566</v>
+        <v>442</v>
       </c>
       <c r="D217" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="E217" t="s">
         <v>600</v>
       </c>
       <c r="F217">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G217">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H217">
         <v>0</v>
@@ -10582,18 +10582,18 @@
         <v>0</v>
       </c>
       <c r="L217" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="218" spans="1:12" x14ac:dyDescent="0.3">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="218" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>374</v>
       </c>
       <c r="B218" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C218" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="D218" t="s">
         <v>599</v>
@@ -10602,36 +10602,36 @@
         <v>600</v>
       </c>
       <c r="F218">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G218">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H218">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I218">
         <v>0</v>
       </c>
       <c r="J218">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K218">
         <v>0</v>
       </c>
       <c r="L218" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="219" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
-        <v>69</v>
+        <v>374</v>
       </c>
       <c r="B219" t="s">
-        <v>174</v>
+        <v>447</v>
       </c>
       <c r="C219" t="s">
-        <v>175</v>
+        <v>448</v>
       </c>
       <c r="D219" t="s">
         <v>600</v>
@@ -10640,16 +10640,16 @@
         <v>600</v>
       </c>
       <c r="F219">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G219">
         <v>1</v>
       </c>
       <c r="H219">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I219">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J219">
         <v>1</v>
@@ -10663,28 +10663,28 @@
     </row>
     <row r="220" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
-        <v>244</v>
+        <v>374</v>
       </c>
       <c r="B220" t="s">
-        <v>355</v>
+        <v>449</v>
       </c>
       <c r="C220" t="s">
-        <v>356</v>
+        <v>450</v>
       </c>
       <c r="D220" t="s">
         <v>599</v>
       </c>
       <c r="E220" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="F220">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G220">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H220">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I220">
         <v>1</v>
@@ -10693,7 +10693,7 @@
         <v>1</v>
       </c>
       <c r="K220">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L220" t="s">
         <v>599</v>
@@ -10701,22 +10701,22 @@
     </row>
     <row r="221" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
-        <v>244</v>
+        <v>374</v>
       </c>
       <c r="B221" t="s">
-        <v>357</v>
+        <v>451</v>
       </c>
       <c r="C221" t="s">
-        <v>358</v>
+        <v>452</v>
       </c>
       <c r="D221" t="s">
         <v>599</v>
       </c>
       <c r="E221" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="F221">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G221">
         <v>0</v>
@@ -10725,13 +10725,13 @@
         <v>0</v>
       </c>
       <c r="I221">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J221">
         <v>1</v>
       </c>
       <c r="K221">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L221" t="s">
         <v>599</v>
@@ -10739,13 +10739,13 @@
     </row>
     <row r="222" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
-        <v>69</v>
+        <v>453</v>
       </c>
       <c r="B222" t="s">
-        <v>176</v>
+        <v>454</v>
       </c>
       <c r="C222" t="s">
-        <v>177</v>
+        <v>455</v>
       </c>
       <c r="D222" t="s">
         <v>600</v>
@@ -10777,13 +10777,13 @@
     </row>
     <row r="223" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
-        <v>69</v>
+        <v>453</v>
       </c>
       <c r="B223" t="s">
-        <v>178</v>
+        <v>456</v>
       </c>
       <c r="C223" t="s">
-        <v>179</v>
+        <v>457</v>
       </c>
       <c r="D223" t="s">
         <v>600</v>
@@ -10792,7 +10792,7 @@
         <v>600</v>
       </c>
       <c r="F223">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G223">
         <v>1</v>
@@ -10815,13 +10815,13 @@
     </row>
     <row r="224" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
-        <v>69</v>
+        <v>453</v>
       </c>
       <c r="B224" t="s">
-        <v>180</v>
+        <v>458</v>
       </c>
       <c r="C224" t="s">
-        <v>181</v>
+        <v>459</v>
       </c>
       <c r="D224" t="s">
         <v>600</v>
@@ -10839,10 +10839,10 @@
         <v>0</v>
       </c>
       <c r="I224">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J224">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K224">
         <v>1</v>
@@ -10853,13 +10853,13 @@
     </row>
     <row r="225" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
-        <v>69</v>
+        <v>453</v>
       </c>
       <c r="B225" t="s">
-        <v>182</v>
+        <v>460</v>
       </c>
       <c r="C225" t="s">
-        <v>183</v>
+        <v>461</v>
       </c>
       <c r="D225" t="s">
         <v>600</v>
@@ -10891,13 +10891,13 @@
     </row>
     <row r="226" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
-        <v>69</v>
+        <v>453</v>
       </c>
       <c r="B226" t="s">
-        <v>184</v>
+        <v>462</v>
       </c>
       <c r="C226" t="s">
-        <v>185</v>
+        <v>463</v>
       </c>
       <c r="D226" t="s">
         <v>600</v>
@@ -10921,7 +10921,7 @@
         <v>1</v>
       </c>
       <c r="K226">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L226" t="s">
         <v>600</v>
@@ -10929,13 +10929,13 @@
     </row>
     <row r="227" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
-        <v>69</v>
+        <v>453</v>
       </c>
       <c r="B227" t="s">
-        <v>186</v>
+        <v>464</v>
       </c>
       <c r="C227" t="s">
-        <v>187</v>
+        <v>465</v>
       </c>
       <c r="D227" t="s">
         <v>600</v>
@@ -10944,7 +10944,7 @@
         <v>600</v>
       </c>
       <c r="F227">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G227">
         <v>1</v>
@@ -10970,10 +10970,10 @@
         <v>453</v>
       </c>
       <c r="B228" t="s">
-        <v>494</v>
+        <v>466</v>
       </c>
       <c r="C228" t="s">
-        <v>495</v>
+        <v>467</v>
       </c>
       <c r="D228" t="s">
         <v>600</v>
@@ -10982,22 +10982,22 @@
         <v>600</v>
       </c>
       <c r="F228">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G228">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H228">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I228">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J228">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K228">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L228" t="s">
         <v>600</v>
@@ -11008,10 +11008,10 @@
         <v>453</v>
       </c>
       <c r="B229" t="s">
-        <v>496</v>
+        <v>468</v>
       </c>
       <c r="C229" t="s">
-        <v>497</v>
+        <v>469</v>
       </c>
       <c r="D229" t="s">
         <v>600</v>
@@ -11020,10 +11020,10 @@
         <v>600</v>
       </c>
       <c r="F229">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G229">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H229">
         <v>0</v>
@@ -11043,13 +11043,13 @@
     </row>
     <row r="230" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
-        <v>363</v>
+        <v>453</v>
       </c>
       <c r="B230" t="s">
-        <v>370</v>
+        <v>470</v>
       </c>
       <c r="C230" t="s">
-        <v>371</v>
+        <v>471</v>
       </c>
       <c r="D230" t="s">
         <v>600</v>
@@ -11058,19 +11058,19 @@
         <v>600</v>
       </c>
       <c r="F230">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G230">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H230">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I230">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J230">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K230">
         <v>1</v>
@@ -11081,13 +11081,13 @@
     </row>
     <row r="231" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
-        <v>69</v>
+        <v>453</v>
       </c>
       <c r="B231" t="s">
-        <v>188</v>
+        <v>472</v>
       </c>
       <c r="C231" t="s">
-        <v>189</v>
+        <v>473</v>
       </c>
       <c r="D231" t="s">
         <v>600</v>
@@ -11096,13 +11096,13 @@
         <v>600</v>
       </c>
       <c r="F231">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G231">
         <v>1</v>
       </c>
       <c r="H231">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I231">
         <v>1</v>
@@ -11111,7 +11111,7 @@
         <v>1</v>
       </c>
       <c r="K231">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L231" t="s">
         <v>600</v>
@@ -11122,10 +11122,10 @@
         <v>453</v>
       </c>
       <c r="B232" t="s">
-        <v>498</v>
+        <v>474</v>
       </c>
       <c r="C232" t="s">
-        <v>499</v>
+        <v>475</v>
       </c>
       <c r="D232" t="s">
         <v>600</v>
@@ -11134,10 +11134,10 @@
         <v>600</v>
       </c>
       <c r="F232">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G232">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H232">
         <v>0</v>
@@ -11160,10 +11160,10 @@
         <v>453</v>
       </c>
       <c r="B233" t="s">
-        <v>500</v>
+        <v>476</v>
       </c>
       <c r="C233" t="s">
-        <v>501</v>
+        <v>477</v>
       </c>
       <c r="D233" t="s">
         <v>600</v>
@@ -11172,7 +11172,7 @@
         <v>600</v>
       </c>
       <c r="F233">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G233">
         <v>1</v>
@@ -11187,7 +11187,7 @@
         <v>1</v>
       </c>
       <c r="K233">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L233" t="s">
         <v>600</v>
@@ -11195,25 +11195,25 @@
     </row>
     <row r="234" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
-        <v>374</v>
+        <v>453</v>
       </c>
       <c r="B234" t="s">
-        <v>437</v>
+        <v>478</v>
       </c>
       <c r="C234" t="s">
-        <v>438</v>
+        <v>479</v>
       </c>
       <c r="D234" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="E234" t="s">
         <v>600</v>
       </c>
       <c r="F234">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G234">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H234">
         <v>1</v>
@@ -11228,24 +11228,24 @@
         <v>1</v>
       </c>
       <c r="L234" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="235" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
-        <v>374</v>
+        <v>453</v>
       </c>
       <c r="B235" t="s">
-        <v>439</v>
+        <v>480</v>
       </c>
       <c r="C235" t="s">
-        <v>440</v>
+        <v>481</v>
       </c>
       <c r="D235" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="E235" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="F235">
         <v>1</v>
@@ -11254,7 +11254,7 @@
         <v>1</v>
       </c>
       <c r="H235">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I235">
         <v>1</v>
@@ -11266,21 +11266,21 @@
         <v>1</v>
       </c>
       <c r="L235" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="236" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
-        <v>374</v>
+        <v>453</v>
       </c>
       <c r="B236" t="s">
-        <v>441</v>
+        <v>482</v>
       </c>
       <c r="C236" t="s">
-        <v>442</v>
+        <v>483</v>
       </c>
       <c r="D236" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="E236" t="s">
         <v>600</v>
@@ -11289,7 +11289,7 @@
         <v>0</v>
       </c>
       <c r="G236">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H236">
         <v>0</v>
@@ -11298,24 +11298,24 @@
         <v>0</v>
       </c>
       <c r="J236">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K236">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L236" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="237" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
-        <v>69</v>
+        <v>453</v>
       </c>
       <c r="B237" t="s">
-        <v>190</v>
+        <v>484</v>
       </c>
       <c r="C237" t="s">
-        <v>191</v>
+        <v>485</v>
       </c>
       <c r="D237" t="s">
         <v>600</v>
@@ -11330,7 +11330,7 @@
         <v>1</v>
       </c>
       <c r="H237">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I237">
         <v>1</v>
@@ -11339,7 +11339,7 @@
         <v>1</v>
       </c>
       <c r="K237">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L237" t="s">
         <v>600</v>
@@ -11347,28 +11347,28 @@
     </row>
     <row r="238" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
-        <v>244</v>
+        <v>453</v>
       </c>
       <c r="B238" t="s">
-        <v>359</v>
+        <v>486</v>
       </c>
       <c r="C238" t="s">
-        <v>360</v>
+        <v>487</v>
       </c>
       <c r="D238" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="E238" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="F238">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G238">
         <v>1</v>
       </c>
       <c r="H238">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I238">
         <v>1</v>
@@ -11377,21 +11377,21 @@
         <v>1</v>
       </c>
       <c r="K238">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L238" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="239" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
-        <v>69</v>
+        <v>453</v>
       </c>
       <c r="B239" t="s">
-        <v>194</v>
+        <v>488</v>
       </c>
       <c r="C239" t="s">
-        <v>195</v>
+        <v>489</v>
       </c>
       <c r="D239" t="s">
         <v>600</v>
@@ -11400,10 +11400,10 @@
         <v>600</v>
       </c>
       <c r="F239">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G239">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H239">
         <v>1</v>
@@ -11426,10 +11426,10 @@
         <v>453</v>
       </c>
       <c r="B240" t="s">
-        <v>502</v>
+        <v>490</v>
       </c>
       <c r="C240" t="s">
-        <v>503</v>
+        <v>491</v>
       </c>
       <c r="D240" t="s">
         <v>600</v>
@@ -11444,7 +11444,7 @@
         <v>1</v>
       </c>
       <c r="H240">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I240">
         <v>1</v>
@@ -11461,13 +11461,13 @@
     </row>
     <row r="241" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
-        <v>69</v>
+        <v>453</v>
       </c>
       <c r="B241" t="s">
-        <v>196</v>
+        <v>492</v>
       </c>
       <c r="C241" t="s">
-        <v>197</v>
+        <v>493</v>
       </c>
       <c r="D241" t="s">
         <v>600</v>
@@ -11476,13 +11476,13 @@
         <v>600</v>
       </c>
       <c r="F241">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G241">
         <v>1</v>
       </c>
       <c r="H241">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I241">
         <v>1</v>
@@ -11499,13 +11499,13 @@
     </row>
     <row r="242" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
-        <v>69</v>
+        <v>453</v>
       </c>
       <c r="B242" t="s">
-        <v>198</v>
+        <v>494</v>
       </c>
       <c r="C242" t="s">
-        <v>199</v>
+        <v>495</v>
       </c>
       <c r="D242" t="s">
         <v>600</v>
@@ -11517,10 +11517,10 @@
         <v>1</v>
       </c>
       <c r="G242">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H242">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I242">
         <v>1</v>
@@ -11529,7 +11529,7 @@
         <v>1</v>
       </c>
       <c r="K242">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L242" t="s">
         <v>600</v>
@@ -11540,10 +11540,10 @@
         <v>453</v>
       </c>
       <c r="B243" t="s">
-        <v>504</v>
+        <v>496</v>
       </c>
       <c r="C243" t="s">
-        <v>505</v>
+        <v>497</v>
       </c>
       <c r="D243" t="s">
         <v>600</v>
@@ -11552,10 +11552,10 @@
         <v>600</v>
       </c>
       <c r="F243">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G243">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H243">
         <v>0</v>
@@ -11575,13 +11575,13 @@
     </row>
     <row r="244" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
-        <v>69</v>
+        <v>453</v>
       </c>
       <c r="B244" t="s">
-        <v>200</v>
+        <v>498</v>
       </c>
       <c r="C244" t="s">
-        <v>201</v>
+        <v>499</v>
       </c>
       <c r="D244" t="s">
         <v>600</v>
@@ -11590,13 +11590,13 @@
         <v>600</v>
       </c>
       <c r="F244">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G244">
         <v>1</v>
       </c>
       <c r="H244">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I244">
         <v>1</v>
@@ -11613,13 +11613,13 @@
     </row>
     <row r="245" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
-        <v>69</v>
+        <v>453</v>
       </c>
       <c r="B245" t="s">
-        <v>202</v>
+        <v>500</v>
       </c>
       <c r="C245" t="s">
-        <v>203</v>
+        <v>501</v>
       </c>
       <c r="D245" t="s">
         <v>600</v>
@@ -11628,7 +11628,7 @@
         <v>600</v>
       </c>
       <c r="F245">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G245">
         <v>1</v>
@@ -11643,7 +11643,7 @@
         <v>1</v>
       </c>
       <c r="K245">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L245" t="s">
         <v>600</v>
@@ -11654,10 +11654,10 @@
         <v>453</v>
       </c>
       <c r="B246" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="C246" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="D246" t="s">
         <v>600</v>
@@ -11669,16 +11669,16 @@
         <v>0</v>
       </c>
       <c r="G246">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H246">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I246">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J246">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K246">
         <v>1</v>
@@ -11689,13 +11689,13 @@
     </row>
     <row r="247" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
-        <v>69</v>
+        <v>453</v>
       </c>
       <c r="B247" t="s">
-        <v>204</v>
+        <v>504</v>
       </c>
       <c r="C247" t="s">
-        <v>205</v>
+        <v>505</v>
       </c>
       <c r="D247" t="s">
         <v>600</v>
@@ -11704,13 +11704,13 @@
         <v>600</v>
       </c>
       <c r="F247">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G247">
         <v>1</v>
       </c>
       <c r="H247">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I247">
         <v>1</v>
@@ -11727,13 +11727,13 @@
     </row>
     <row r="248" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
-        <v>526</v>
+        <v>453</v>
       </c>
       <c r="B248" t="s">
-        <v>561</v>
+        <v>506</v>
       </c>
       <c r="C248" t="s">
-        <v>562</v>
+        <v>507</v>
       </c>
       <c r="D248" t="s">
         <v>600</v>
@@ -11765,13 +11765,13 @@
     </row>
     <row r="249" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
-        <v>69</v>
+        <v>453</v>
       </c>
       <c r="B249" t="s">
-        <v>206</v>
+        <v>508</v>
       </c>
       <c r="C249" t="s">
-        <v>207</v>
+        <v>509</v>
       </c>
       <c r="D249" t="s">
         <v>600</v>
@@ -11780,19 +11780,19 @@
         <v>600</v>
       </c>
       <c r="F249">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G249">
         <v>1</v>
       </c>
       <c r="H249">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I249">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J249">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K249">
         <v>1</v>
@@ -11803,13 +11803,13 @@
     </row>
     <row r="250" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
-        <v>69</v>
+        <v>453</v>
       </c>
       <c r="B250" t="s">
-        <v>208</v>
+        <v>510</v>
       </c>
       <c r="C250" t="s">
-        <v>209</v>
+        <v>511</v>
       </c>
       <c r="D250" t="s">
         <v>600</v>
@@ -11841,13 +11841,13 @@
     </row>
     <row r="251" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
-        <v>69</v>
+        <v>453</v>
       </c>
       <c r="B251" t="s">
-        <v>210</v>
+        <v>512</v>
       </c>
       <c r="C251" t="s">
-        <v>211</v>
+        <v>513</v>
       </c>
       <c r="D251" t="s">
         <v>600</v>
@@ -11859,7 +11859,7 @@
         <v>1</v>
       </c>
       <c r="G251">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H251">
         <v>1</v>
@@ -11882,10 +11882,10 @@
         <v>453</v>
       </c>
       <c r="B252" t="s">
-        <v>508</v>
+        <v>514</v>
       </c>
       <c r="C252" t="s">
-        <v>509</v>
+        <v>515</v>
       </c>
       <c r="D252" t="s">
         <v>600</v>
@@ -11900,7 +11900,7 @@
         <v>1</v>
       </c>
       <c r="H252">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I252">
         <v>1</v>
@@ -11920,10 +11920,10 @@
         <v>453</v>
       </c>
       <c r="B253" t="s">
-        <v>510</v>
+        <v>516</v>
       </c>
       <c r="C253" t="s">
-        <v>511</v>
+        <v>517</v>
       </c>
       <c r="D253" t="s">
         <v>600</v>
@@ -11932,7 +11932,7 @@
         <v>600</v>
       </c>
       <c r="F253">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G253">
         <v>1</v>
@@ -11958,10 +11958,10 @@
         <v>453</v>
       </c>
       <c r="B254" t="s">
-        <v>512</v>
+        <v>518</v>
       </c>
       <c r="C254" t="s">
-        <v>513</v>
+        <v>519</v>
       </c>
       <c r="D254" t="s">
         <v>600</v>
@@ -11976,7 +11976,7 @@
         <v>0</v>
       </c>
       <c r="H254">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I254">
         <v>1</v>
@@ -11985,7 +11985,7 @@
         <v>1</v>
       </c>
       <c r="K254">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L254" t="s">
         <v>600</v>
@@ -11993,13 +11993,13 @@
     </row>
     <row r="255" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
-        <v>69</v>
+        <v>453</v>
       </c>
       <c r="B255" t="s">
-        <v>212</v>
+        <v>520</v>
       </c>
       <c r="C255" t="s">
-        <v>213</v>
+        <v>521</v>
       </c>
       <c r="D255" t="s">
         <v>600</v>
@@ -12011,10 +12011,10 @@
         <v>1</v>
       </c>
       <c r="G255">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H255">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I255">
         <v>1</v>
@@ -12031,13 +12031,13 @@
     </row>
     <row r="256" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
-        <v>69</v>
+        <v>453</v>
       </c>
       <c r="B256" t="s">
-        <v>214</v>
+        <v>522</v>
       </c>
       <c r="C256" t="s">
-        <v>215</v>
+        <v>523</v>
       </c>
       <c r="D256" t="s">
         <v>600</v>
@@ -12046,19 +12046,19 @@
         <v>600</v>
       </c>
       <c r="F256">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G256">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H256">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I256">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J256">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K256">
         <v>1</v>
@@ -12069,28 +12069,28 @@
     </row>
     <row r="257" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
-        <v>244</v>
+        <v>453</v>
       </c>
       <c r="B257" t="s">
-        <v>361</v>
+        <v>524</v>
       </c>
       <c r="C257" t="s">
-        <v>362</v>
+        <v>525</v>
       </c>
       <c r="D257" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="E257" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="F257">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G257">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H257">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I257">
         <v>1</v>
@@ -12099,24 +12099,24 @@
         <v>1</v>
       </c>
       <c r="K257">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L257" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="258" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
-        <v>374</v>
+        <v>526</v>
       </c>
       <c r="B258" t="s">
-        <v>445</v>
+        <v>527</v>
       </c>
       <c r="C258" t="s">
-        <v>446</v>
+        <v>528</v>
       </c>
       <c r="D258" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="E258" t="s">
         <v>600</v>
@@ -12125,10 +12125,10 @@
         <v>0</v>
       </c>
       <c r="G258">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H258">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I258">
         <v>0</v>
@@ -12140,18 +12140,18 @@
         <v>0</v>
       </c>
       <c r="L258" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="259" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
-        <v>69</v>
+        <v>526</v>
       </c>
       <c r="B259" t="s">
-        <v>216</v>
+        <v>531</v>
       </c>
       <c r="C259" t="s">
-        <v>217</v>
+        <v>532</v>
       </c>
       <c r="D259" t="s">
         <v>600</v>
@@ -12160,7 +12160,7 @@
         <v>600</v>
       </c>
       <c r="F259">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G259">
         <v>0</v>
@@ -12169,13 +12169,13 @@
         <v>0</v>
       </c>
       <c r="I259">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J259">
         <v>1</v>
       </c>
       <c r="K259">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L259" t="s">
         <v>600</v>
@@ -12183,22 +12183,22 @@
     </row>
     <row r="260" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
-        <v>69</v>
+        <v>526</v>
       </c>
       <c r="B260" t="s">
-        <v>218</v>
+        <v>533</v>
       </c>
       <c r="C260" t="s">
-        <v>219</v>
+        <v>534</v>
       </c>
       <c r="D260" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="E260" t="s">
         <v>600</v>
       </c>
       <c r="F260">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G260">
         <v>0</v>
@@ -12207,7 +12207,7 @@
         <v>0</v>
       </c>
       <c r="I260">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J260">
         <v>1</v>
@@ -12216,56 +12216,56 @@
         <v>1</v>
       </c>
       <c r="L260" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="261" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
-        <v>237</v>
+        <v>526</v>
       </c>
       <c r="B261" t="s">
-        <v>240</v>
+        <v>529</v>
       </c>
       <c r="C261" t="s">
-        <v>241</v>
+        <v>530</v>
       </c>
       <c r="D261" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="E261" t="s">
         <v>600</v>
       </c>
       <c r="F261">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G261">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H261">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I261">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J261">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K261">
         <v>1</v>
       </c>
       <c r="L261" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="262" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
-        <v>453</v>
+        <v>526</v>
       </c>
       <c r="B262" t="s">
-        <v>514</v>
+        <v>535</v>
       </c>
       <c r="C262" t="s">
-        <v>515</v>
+        <v>536</v>
       </c>
       <c r="D262" t="s">
         <v>600</v>
@@ -12274,22 +12274,22 @@
         <v>600</v>
       </c>
       <c r="F262">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G262">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H262">
         <v>0</v>
       </c>
       <c r="I262">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J262">
         <v>1</v>
       </c>
       <c r="K262">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L262" t="s">
         <v>600</v>
@@ -12297,13 +12297,13 @@
     </row>
     <row r="263" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
-        <v>453</v>
+        <v>526</v>
       </c>
       <c r="B263" t="s">
-        <v>516</v>
+        <v>537</v>
       </c>
       <c r="C263" t="s">
-        <v>517</v>
+        <v>538</v>
       </c>
       <c r="D263" t="s">
         <v>600</v>
@@ -12312,7 +12312,7 @@
         <v>600</v>
       </c>
       <c r="F263">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G263">
         <v>1</v>
@@ -12321,13 +12321,13 @@
         <v>1</v>
       </c>
       <c r="I263">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J263">
         <v>1</v>
       </c>
       <c r="K263">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L263" t="s">
         <v>600</v>
@@ -12335,13 +12335,13 @@
     </row>
     <row r="264" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
-        <v>69</v>
+        <v>526</v>
       </c>
       <c r="B264" t="s">
-        <v>220</v>
+        <v>539</v>
       </c>
       <c r="C264" t="s">
-        <v>221</v>
+        <v>540</v>
       </c>
       <c r="D264" t="s">
         <v>600</v>
@@ -12350,16 +12350,16 @@
         <v>600</v>
       </c>
       <c r="F264">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G264">
         <v>1</v>
       </c>
       <c r="H264">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I264">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J264">
         <v>1</v>
@@ -12373,13 +12373,13 @@
     </row>
     <row r="265" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
-        <v>453</v>
+        <v>526</v>
       </c>
       <c r="B265" t="s">
-        <v>518</v>
+        <v>543</v>
       </c>
       <c r="C265" t="s">
-        <v>519</v>
+        <v>544</v>
       </c>
       <c r="D265" t="s">
         <v>600</v>
@@ -12388,7 +12388,7 @@
         <v>600</v>
       </c>
       <c r="F265">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G265">
         <v>0</v>
@@ -12397,10 +12397,10 @@
         <v>0</v>
       </c>
       <c r="I265">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J265">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K265">
         <v>1</v>
@@ -12411,13 +12411,13 @@
     </row>
     <row r="266" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
-        <v>69</v>
+        <v>526</v>
       </c>
       <c r="B266" t="s">
-        <v>222</v>
+        <v>547</v>
       </c>
       <c r="C266" t="s">
-        <v>223</v>
+        <v>548</v>
       </c>
       <c r="D266" t="s">
         <v>600</v>
@@ -12426,19 +12426,19 @@
         <v>600</v>
       </c>
       <c r="F266">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G266">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H266">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I266">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J266">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K266">
         <v>1</v>
@@ -12447,15 +12447,15 @@
         <v>600</v>
       </c>
     </row>
-    <row r="267" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
-        <v>374</v>
+        <v>526</v>
       </c>
       <c r="B267" t="s">
-        <v>447</v>
+        <v>541</v>
       </c>
       <c r="C267" t="s">
-        <v>448</v>
+        <v>542</v>
       </c>
       <c r="D267" t="s">
         <v>600</v>
@@ -12479,7 +12479,7 @@
         <v>1</v>
       </c>
       <c r="K267">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L267" t="s">
         <v>600</v>
@@ -12487,13 +12487,13 @@
     </row>
     <row r="268" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
-        <v>237</v>
+        <v>526</v>
       </c>
       <c r="B268" t="s">
-        <v>242</v>
+        <v>545</v>
       </c>
       <c r="C268" t="s">
-        <v>243</v>
+        <v>546</v>
       </c>
       <c r="D268" t="s">
         <v>599</v>
@@ -12505,7 +12505,7 @@
         <v>0</v>
       </c>
       <c r="G268">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H268">
         <v>0</v>
@@ -12525,13 +12525,13 @@
     </row>
     <row r="269" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
-        <v>453</v>
+        <v>526</v>
       </c>
       <c r="B269" t="s">
-        <v>520</v>
+        <v>549</v>
       </c>
       <c r="C269" t="s">
-        <v>521</v>
+        <v>550</v>
       </c>
       <c r="D269" t="s">
         <v>600</v>
@@ -12546,16 +12546,16 @@
         <v>0</v>
       </c>
       <c r="H269">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I269">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J269">
         <v>1</v>
       </c>
       <c r="K269">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L269" t="s">
         <v>600</v>
@@ -12563,13 +12563,13 @@
     </row>
     <row r="270" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
-        <v>453</v>
+        <v>526</v>
       </c>
       <c r="B270" t="s">
-        <v>522</v>
+        <v>551</v>
       </c>
       <c r="C270" t="s">
-        <v>523</v>
+        <v>552</v>
       </c>
       <c r="D270" t="s">
         <v>600</v>
@@ -12578,19 +12578,19 @@
         <v>600</v>
       </c>
       <c r="F270">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G270">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H270">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I270">
         <v>0</v>
       </c>
       <c r="J270">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K270">
         <v>1</v>
@@ -12599,15 +12599,15 @@
         <v>600</v>
       </c>
     </row>
-    <row r="271" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
-        <v>48</v>
+        <v>526</v>
       </c>
       <c r="B271" t="s">
-        <v>67</v>
+        <v>553</v>
       </c>
       <c r="C271" t="s">
-        <v>68</v>
+        <v>554</v>
       </c>
       <c r="D271" t="s">
         <v>600</v>
@@ -12622,10 +12622,10 @@
         <v>0</v>
       </c>
       <c r="H271">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I271">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J271">
         <v>1</v>
@@ -12639,16 +12639,16 @@
     </row>
     <row r="272" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
-        <v>374</v>
+        <v>526</v>
       </c>
       <c r="B272" t="s">
-        <v>449</v>
+        <v>557</v>
       </c>
       <c r="C272" t="s">
-        <v>450</v>
+        <v>558</v>
       </c>
       <c r="D272" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="E272" t="s">
         <v>600</v>
@@ -12657,36 +12657,36 @@
         <v>1</v>
       </c>
       <c r="G272">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H272">
         <v>1</v>
       </c>
       <c r="I272">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J272">
         <v>1</v>
       </c>
       <c r="K272">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L272" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="273" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A273" t="s">
+        <v>526</v>
+      </c>
+      <c r="B273" t="s">
+        <v>555</v>
+      </c>
+      <c r="C273" t="s">
+        <v>556</v>
+      </c>
+      <c r="D273" t="s">
         <v>599</v>
-      </c>
-    </row>
-    <row r="273" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A273" t="s">
-        <v>453</v>
-      </c>
-      <c r="B273" t="s">
-        <v>524</v>
-      </c>
-      <c r="C273" t="s">
-        <v>525</v>
-      </c>
-      <c r="D273" t="s">
-        <v>600</v>
       </c>
       <c r="E273" t="s">
         <v>600</v>
@@ -12695,19 +12695,19 @@
         <v>0</v>
       </c>
       <c r="G273">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H273">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I273">
         <v>1</v>
       </c>
       <c r="J273">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K273">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L273" t="s">
         <v>600</v>
@@ -12715,13 +12715,13 @@
     </row>
     <row r="274" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
-        <v>69</v>
+        <v>526</v>
       </c>
       <c r="B274" t="s">
-        <v>224</v>
+        <v>559</v>
       </c>
       <c r="C274" t="s">
-        <v>225</v>
+        <v>560</v>
       </c>
       <c r="D274" t="s">
         <v>600</v>
@@ -12730,22 +12730,22 @@
         <v>600</v>
       </c>
       <c r="F274">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G274">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H274">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I274">
         <v>0</v>
       </c>
       <c r="J274">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K274">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L274" t="s">
         <v>600</v>
@@ -12753,16 +12753,16 @@
     </row>
     <row r="275" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
-        <v>69</v>
+        <v>526</v>
       </c>
       <c r="B275" t="s">
-        <v>226</v>
+        <v>563</v>
       </c>
       <c r="C275" t="s">
-        <v>227</v>
+        <v>564</v>
       </c>
       <c r="D275" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="E275" t="s">
         <v>600</v>
@@ -12786,30 +12786,30 @@
         <v>1</v>
       </c>
       <c r="L275" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="276" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
-        <v>374</v>
+        <v>526</v>
       </c>
       <c r="B276" t="s">
-        <v>451</v>
+        <v>565</v>
       </c>
       <c r="C276" t="s">
-        <v>452</v>
+        <v>566</v>
       </c>
       <c r="D276" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="E276" t="s">
         <v>600</v>
       </c>
       <c r="F276">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G276">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H276">
         <v>0</v>
@@ -12824,18 +12824,18 @@
         <v>0</v>
       </c>
       <c r="L276" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="277" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
-        <v>69</v>
+        <v>526</v>
       </c>
       <c r="B277" t="s">
-        <v>228</v>
+        <v>561</v>
       </c>
       <c r="C277" t="s">
-        <v>229</v>
+        <v>562</v>
       </c>
       <c r="D277" t="s">
         <v>600</v>
@@ -12844,19 +12844,19 @@
         <v>600</v>
       </c>
       <c r="F277">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G277">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H277">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I277">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J277">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K277">
         <v>1</v>
@@ -12867,12 +12867,9 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:L277">
-    <filterColumn colId="0">
+    <filterColumn colId="3">
       <filters>
-        <filter val="Amfibieën"/>
-        <filter val="Kevers"/>
-        <filter val="Libellen"/>
-        <filter val="Vogels"/>
+        <filter val="ja"/>
       </filters>
     </filterColumn>
     <filterColumn colId="11">
@@ -12880,6 +12877,9 @@
         <filter val="nee"/>
       </filters>
     </filterColumn>
+    <sortState ref="A2:L277">
+      <sortCondition ref="A1:A277"/>
+    </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/data/input/Excel_files/Soortenlijst_Maatwerkgebieden.xlsx
+++ b/data/input/Excel_files/Soortenlijst_Maatwerkgebieden.xlsx
@@ -2415,7 +2415,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2450,7 +2450,7 @@
         <v>0</v>
       </c>
       <c r="L3" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="4" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -2605,7 +2605,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -2640,7 +2640,7 @@
         <v>1</v>
       </c>
       <c r="L8" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="9" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -5531,7 +5531,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>69</v>
       </c>
@@ -5566,7 +5566,7 @@
         <v>1</v>
       </c>
       <c r="L85" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="86" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -12675,7 +12675,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="273" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
         <v>526</v>
       </c>
@@ -12710,7 +12710,7 @@
         <v>0</v>
       </c>
       <c r="L273" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="274" spans="1:12" hidden="1" x14ac:dyDescent="0.3">

--- a/data/input/Excel_files/Soortenlijst_Maatwerkgebieden.xlsx
+++ b/data/input/Excel_files/Soortenlijst_Maatwerkgebieden.xlsx
@@ -3137,7 +3137,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>45</v>
       </c>
@@ -3517,7 +3517,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="32" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>48</v>
       </c>
@@ -3528,7 +3528,7 @@
         <v>68</v>
       </c>
       <c r="D32" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="E32" t="s">
         <v>600</v>
@@ -3552,7 +3552,7 @@
         <v>0</v>
       </c>
       <c r="L32" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="33" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -12867,12 +12867,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:L277">
-    <filterColumn colId="3">
+    <filterColumn colId="0">
       <filters>
-        <filter val="ja"/>
+        <filter val="Libellen"/>
       </filters>
     </filterColumn>
-    <filterColumn colId="11">
+    <filterColumn colId="3">
       <filters>
         <filter val="nee"/>
       </filters>

--- a/data/input/Excel_files/Soortenlijst_Maatwerkgebieden.xlsx
+++ b/data/input/Excel_files/Soortenlijst_Maatwerkgebieden.xlsx
@@ -3175,7 +3175,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="23" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>48</v>
       </c>
@@ -3213,7 +3213,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="24" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>48</v>
       </c>
@@ -3251,7 +3251,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="25" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>48</v>
       </c>
@@ -3289,7 +3289,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="26" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>48</v>
       </c>
@@ -3327,7 +3327,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="27" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>48</v>
       </c>
@@ -3365,7 +3365,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="28" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>48</v>
       </c>
@@ -3403,7 +3403,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="29" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>48</v>
       </c>
@@ -3441,7 +3441,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="30" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>48</v>
       </c>
@@ -3479,7 +3479,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="31" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>48</v>
       </c>
@@ -12870,11 +12870,6 @@
     <filterColumn colId="0">
       <filters>
         <filter val="Libellen"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="3">
-      <filters>
-        <filter val="nee"/>
       </filters>
     </filterColumn>
     <sortState ref="A2:L277">

--- a/data/input/Excel_files/Soortenlijst_Maatwerkgebieden.xlsx
+++ b/data/input/Excel_files/Soortenlijst_Maatwerkgebieden.xlsx
@@ -2377,7 +2377,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="2" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2453,7 +2453,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="4" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2491,7 +2491,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="5" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -2529,7 +2529,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="6" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -2567,7 +2567,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="7" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -2643,7 +2643,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="9" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -2681,7 +2681,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="10" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>20</v>
       </c>
@@ -2719,7 +2719,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="11" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>20</v>
       </c>
@@ -2757,7 +2757,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="12" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>20</v>
       </c>
@@ -2795,7 +2795,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="13" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>20</v>
       </c>
@@ -2833,7 +2833,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="14" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>20</v>
       </c>
@@ -2871,7 +2871,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="15" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>20</v>
       </c>
@@ -2909,7 +2909,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="16" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>20</v>
       </c>
@@ -2947,7 +2947,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="17" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>20</v>
       </c>
@@ -2985,7 +2985,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="18" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>20</v>
       </c>
@@ -3023,7 +3023,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="19" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>20</v>
       </c>
@@ -3061,7 +3061,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="20" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>20</v>
       </c>
@@ -3099,7 +3099,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="21" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>20</v>
       </c>
@@ -3172,7 +3172,7 @@
         <v>1</v>
       </c>
       <c r="L22" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.3">
@@ -6595,7 +6595,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="113" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>230</v>
       </c>
@@ -6633,7 +6633,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="114" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>230</v>
       </c>
@@ -6671,7 +6671,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="115" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>230</v>
       </c>
@@ -6709,7 +6709,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="116" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>237</v>
       </c>
@@ -6747,7 +6747,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="117" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>237</v>
       </c>
@@ -6785,7 +6785,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="118" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>237</v>
       </c>
@@ -6823,7 +6823,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="119" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>244</v>
       </c>
@@ -6861,7 +6861,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="120" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>244</v>
       </c>
@@ -6899,7 +6899,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="121" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>244</v>
       </c>
@@ -6937,7 +6937,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="122" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>244</v>
       </c>
@@ -6975,7 +6975,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="123" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>244</v>
       </c>
@@ -7013,7 +7013,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="124" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>244</v>
       </c>
@@ -7051,7 +7051,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="125" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>244</v>
       </c>
@@ -7089,7 +7089,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="126" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>244</v>
       </c>
@@ -7127,7 +7127,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="127" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>244</v>
       </c>
@@ -7165,7 +7165,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="128" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>244</v>
       </c>
@@ -7203,7 +7203,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="129" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>244</v>
       </c>
@@ -7241,7 +7241,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="130" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>244</v>
       </c>
@@ -7279,7 +7279,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="131" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>244</v>
       </c>
@@ -7317,7 +7317,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="132" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>244</v>
       </c>
@@ -7355,7 +7355,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="133" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>244</v>
       </c>
@@ -7393,7 +7393,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="134" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>244</v>
       </c>
@@ -7431,7 +7431,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="135" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>244</v>
       </c>
@@ -7469,7 +7469,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="136" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>244</v>
       </c>
@@ -7507,7 +7507,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="137" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>244</v>
       </c>
@@ -7545,7 +7545,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="138" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>244</v>
       </c>
@@ -7583,7 +7583,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="139" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>244</v>
       </c>
@@ -7621,7 +7621,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="140" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>244</v>
       </c>
@@ -7659,7 +7659,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="141" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>244</v>
       </c>
@@ -7697,7 +7697,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="142" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>244</v>
       </c>
@@ -7735,7 +7735,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="143" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>244</v>
       </c>
@@ -7773,7 +7773,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="144" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>244</v>
       </c>
@@ -7811,7 +7811,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="145" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>244</v>
       </c>
@@ -7849,7 +7849,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="146" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>244</v>
       </c>
@@ -7887,7 +7887,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="147" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>244</v>
       </c>
@@ -7925,7 +7925,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="148" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>244</v>
       </c>
@@ -7963,7 +7963,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="149" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>244</v>
       </c>
@@ -8001,7 +8001,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="150" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>244</v>
       </c>
@@ -8039,7 +8039,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="151" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>244</v>
       </c>
@@ -8077,7 +8077,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="152" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>244</v>
       </c>
@@ -8153,7 +8153,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="154" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>244</v>
       </c>
@@ -8229,7 +8229,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="156" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>244</v>
       </c>
@@ -8267,7 +8267,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="157" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>244</v>
       </c>
@@ -8343,7 +8343,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="159" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>244</v>
       </c>
@@ -8381,7 +8381,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="160" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>244</v>
       </c>
@@ -8419,7 +8419,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="161" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>244</v>
       </c>
@@ -8457,7 +8457,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="162" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>244</v>
       </c>
@@ -8495,7 +8495,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="163" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>244</v>
       </c>
@@ -8533,7 +8533,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="164" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>244</v>
       </c>
@@ -8571,7 +8571,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="165" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>244</v>
       </c>
@@ -8609,7 +8609,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="166" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>244</v>
       </c>
@@ -8647,7 +8647,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="167" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>244</v>
       </c>
@@ -8685,7 +8685,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="168" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>244</v>
       </c>
@@ -8723,7 +8723,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="169" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>244</v>
       </c>
@@ -8761,7 +8761,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="170" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>244</v>
       </c>
@@ -8799,7 +8799,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="171" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>244</v>
       </c>
@@ -8837,7 +8837,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="172" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>244</v>
       </c>
@@ -8875,7 +8875,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="173" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>244</v>
       </c>
@@ -8913,7 +8913,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="174" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>244</v>
       </c>
@@ -8951,7 +8951,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="175" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>244</v>
       </c>
@@ -8989,7 +8989,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="176" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>244</v>
       </c>
@@ -9027,7 +9027,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="177" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>244</v>
       </c>
@@ -9103,7 +9103,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="179" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>363</v>
       </c>
@@ -9255,7 +9255,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="183" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>374</v>
       </c>
@@ -9293,7 +9293,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="184" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>374</v>
       </c>
@@ -9369,7 +9369,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="186" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>374</v>
       </c>
@@ -9407,7 +9407,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="187" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>374</v>
       </c>
@@ -9483,7 +9483,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="189" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>374</v>
       </c>
@@ -9521,7 +9521,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="190" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>374</v>
       </c>
@@ -9559,7 +9559,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="191" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>374</v>
       </c>
@@ -9635,7 +9635,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="193" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>374</v>
       </c>
@@ -9673,7 +9673,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="194" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>374</v>
       </c>
@@ -9711,7 +9711,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="195" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>374</v>
       </c>
@@ -9749,7 +9749,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="196" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>374</v>
       </c>
@@ -9787,7 +9787,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="197" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>374</v>
       </c>
@@ -9825,7 +9825,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="198" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>374</v>
       </c>
@@ -9863,7 +9863,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="199" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>374</v>
       </c>
@@ -9901,7 +9901,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="200" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>374</v>
       </c>
@@ -9939,7 +9939,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="201" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>374</v>
       </c>
@@ -9977,7 +9977,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="202" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>374</v>
       </c>
@@ -10015,7 +10015,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="203" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>374</v>
       </c>
@@ -10053,7 +10053,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="204" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>374</v>
       </c>
@@ -10091,7 +10091,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="205" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>374</v>
       </c>
@@ -10129,7 +10129,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="206" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>374</v>
       </c>
@@ -10167,7 +10167,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="207" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>374</v>
       </c>
@@ -10205,7 +10205,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="208" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>374</v>
       </c>
@@ -10243,7 +10243,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="209" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>374</v>
       </c>
@@ -10281,7 +10281,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="210" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>374</v>
       </c>
@@ -10319,7 +10319,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="211" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>374</v>
       </c>
@@ -10357,7 +10357,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="212" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>374</v>
       </c>
@@ -10395,7 +10395,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="213" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>374</v>
       </c>
@@ -10471,7 +10471,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="215" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>374</v>
       </c>
@@ -10509,7 +10509,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="216" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>374</v>
       </c>
@@ -10547,7 +10547,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="217" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>374</v>
       </c>
@@ -10585,7 +10585,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="218" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>374</v>
       </c>
@@ -10661,7 +10661,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="220" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>374</v>
       </c>
@@ -10699,7 +10699,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="221" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>374</v>
       </c>
@@ -12181,7 +12181,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="260" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
         <v>526</v>
       </c>
@@ -12485,7 +12485,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="268" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
         <v>526</v>
       </c>
@@ -12751,7 +12751,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="275" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
         <v>526</v>
       </c>
@@ -12867,9 +12867,14 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:L277">
-    <filterColumn colId="0">
+    <filterColumn colId="9">
       <filters>
-        <filter val="Libellen"/>
+        <filter val="1"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="11">
+      <filters>
+        <filter val="ja"/>
       </filters>
     </filterColumn>
     <sortState ref="A2:L277">

--- a/data/input/Excel_files/Soortenlijst_Maatwerkgebieden.xlsx
+++ b/data/input/Excel_files/Soortenlijst_Maatwerkgebieden.xlsx
@@ -2415,7 +2415,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="3" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2605,7 +2605,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="8" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -3137,7 +3137,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="22" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>45</v>
       </c>
@@ -5531,7 +5531,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="85" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>69</v>
       </c>
@@ -8115,7 +8115,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="153" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>244</v>
       </c>
@@ -8191,7 +8191,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="155" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>244</v>
       </c>
@@ -8305,7 +8305,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="158" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>244</v>
       </c>
@@ -9445,7 +9445,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="188" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>374</v>
       </c>
@@ -9597,7 +9597,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="192" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>374</v>
       </c>
@@ -10433,7 +10433,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="214" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>374</v>
       </c>
@@ -12675,7 +12675,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="273" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
         <v>526</v>
       </c>
@@ -12867,11 +12867,6 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:L277">
-    <filterColumn colId="9">
-      <filters>
-        <filter val="1"/>
-      </filters>
-    </filterColumn>
     <filterColumn colId="11">
       <filters>
         <filter val="ja"/>

--- a/data/input/Excel_files/Soortenlijst_Maatwerkgebieden.xlsx
+++ b/data/input/Excel_files/Soortenlijst_Maatwerkgebieden.xlsx
@@ -2884,7 +2884,7 @@
         <v>380</v>
       </c>
       <c r="D15" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="E15" t="s">
         <v>596</v>
@@ -12460,7 +12460,7 @@
         <v>448</v>
       </c>
       <c r="D267" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="E267" t="s">
         <v>596</v>

--- a/data/input/Excel_files/Soortenlijst_Maatwerkgebieden.xlsx
+++ b/data/input/Excel_files/Soortenlijst_Maatwerkgebieden.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9072"/>
+    <workbookView minimized="1" xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9072"/>
   </bookViews>
   <sheets>
     <sheet name="Maatwerkgebieden" sheetId="1" r:id="rId1"/>
@@ -2326,6 +2326,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:L277"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -2379,7 +2380,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>20</v>
       </c>
@@ -2417,7 +2418,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>230</v>
       </c>
@@ -2455,7 +2456,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>244</v>
       </c>
@@ -2493,7 +2494,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>244</v>
       </c>
@@ -2569,7 +2570,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>363</v>
       </c>
@@ -2607,7 +2608,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>48</v>
       </c>
@@ -2645,7 +2646,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>244</v>
       </c>
@@ -2683,7 +2684,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>374</v>
       </c>
@@ -2721,7 +2722,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>69</v>
       </c>
@@ -2759,7 +2760,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>69</v>
       </c>
@@ -2797,7 +2798,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>244</v>
       </c>
@@ -2835,7 +2836,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>374</v>
       </c>
@@ -2873,7 +2874,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>374</v>
       </c>
@@ -2911,7 +2912,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>453</v>
       </c>
@@ -2949,7 +2950,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>244</v>
       </c>
@@ -2987,7 +2988,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>69</v>
       </c>
@@ -3025,7 +3026,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>20</v>
       </c>
@@ -3063,7 +3064,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>69</v>
       </c>
@@ -3101,7 +3102,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>3</v>
       </c>
@@ -3139,7 +3140,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>374</v>
       </c>
@@ -3177,7 +3178,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>374</v>
       </c>
@@ -3215,7 +3216,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>69</v>
       </c>
@@ -3253,7 +3254,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>453</v>
       </c>
@@ -3291,7 +3292,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>69</v>
       </c>
@@ -3329,7 +3330,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>69</v>
       </c>
@@ -3443,7 +3444,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>244</v>
       </c>
@@ -3481,7 +3482,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>20</v>
       </c>
@@ -3519,7 +3520,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>69</v>
       </c>
@@ -3557,7 +3558,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>20</v>
       </c>
@@ -3595,7 +3596,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>69</v>
       </c>
@@ -3633,7 +3634,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>69</v>
       </c>
@@ -3671,7 +3672,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>374</v>
       </c>
@@ -3709,7 +3710,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>69</v>
       </c>
@@ -3747,7 +3748,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>244</v>
       </c>
@@ -3785,7 +3786,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>69</v>
       </c>
@@ -3823,7 +3824,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>69</v>
       </c>
@@ -3861,7 +3862,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>453</v>
       </c>
@@ -3899,7 +3900,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>453</v>
       </c>
@@ -3937,7 +3938,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>244</v>
       </c>
@@ -3975,7 +3976,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>244</v>
       </c>
@@ -4013,7 +4014,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>69</v>
       </c>
@@ -4051,7 +4052,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>244</v>
       </c>
@@ -4089,7 +4090,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>244</v>
       </c>
@@ -4127,7 +4128,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>69</v>
       </c>
@@ -4165,7 +4166,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>20</v>
       </c>
@@ -4203,7 +4204,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>244</v>
       </c>
@@ -4241,7 +4242,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>244</v>
       </c>
@@ -4279,7 +4280,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>69</v>
       </c>
@@ -4355,7 +4356,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>69</v>
       </c>
@@ -4393,7 +4394,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>453</v>
       </c>
@@ -4469,7 +4470,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>374</v>
       </c>
@@ -4545,7 +4546,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>69</v>
       </c>
@@ -4583,7 +4584,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>69</v>
       </c>
@@ -4621,7 +4622,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>69</v>
       </c>
@@ -4659,7 +4660,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>69</v>
       </c>
@@ -4697,7 +4698,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>69</v>
       </c>
@@ -4735,7 +4736,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>244</v>
       </c>
@@ -4773,7 +4774,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>69</v>
       </c>
@@ -4811,7 +4812,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>20</v>
       </c>
@@ -4849,7 +4850,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>69</v>
       </c>
@@ -4887,7 +4888,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>20</v>
       </c>
@@ -4925,7 +4926,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>453</v>
       </c>
@@ -4963,7 +4964,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>69</v>
       </c>
@@ -5001,7 +5002,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>69</v>
       </c>
@@ -5039,7 +5040,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>69</v>
       </c>
@@ -5077,7 +5078,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>69</v>
       </c>
@@ -5115,7 +5116,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>48</v>
       </c>
@@ -5153,7 +5154,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>69</v>
       </c>
@@ -5267,7 +5268,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>230</v>
       </c>
@@ -5305,7 +5306,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>244</v>
       </c>
@@ -5343,7 +5344,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>453</v>
       </c>
@@ -5381,7 +5382,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>69</v>
       </c>
@@ -5419,7 +5420,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>69</v>
       </c>
@@ -5457,7 +5458,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>453</v>
       </c>
@@ -5495,7 +5496,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>69</v>
       </c>
@@ -5533,7 +5534,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>374</v>
       </c>
@@ -5571,7 +5572,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>69</v>
       </c>
@@ -5609,7 +5610,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>69</v>
       </c>
@@ -5685,7 +5686,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>69</v>
       </c>
@@ -5723,7 +5724,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>69</v>
       </c>
@@ -5761,7 +5762,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>244</v>
       </c>
@@ -5799,7 +5800,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>20</v>
       </c>
@@ -5875,7 +5876,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>363</v>
       </c>
@@ -5913,7 +5914,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>244</v>
       </c>
@@ -5951,7 +5952,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>244</v>
       </c>
@@ -5989,7 +5990,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="97" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>453</v>
       </c>
@@ -6027,7 +6028,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>453</v>
       </c>
@@ -6065,7 +6066,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>244</v>
       </c>
@@ -6103,7 +6104,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="100" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>374</v>
       </c>
@@ -6141,7 +6142,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="101" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>374</v>
       </c>
@@ -6179,7 +6180,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="102" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>244</v>
       </c>
@@ -6255,7 +6256,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="104" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>20</v>
       </c>
@@ -6293,7 +6294,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="105" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>453</v>
       </c>
@@ -6331,7 +6332,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="106" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>69</v>
       </c>
@@ -6369,7 +6370,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="107" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>69</v>
       </c>
@@ -6407,7 +6408,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="108" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>244</v>
       </c>
@@ -6445,7 +6446,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="109" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>69</v>
       </c>
@@ -6483,7 +6484,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>453</v>
       </c>
@@ -6521,7 +6522,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="111" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>69</v>
       </c>
@@ -6559,7 +6560,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="112" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>69</v>
       </c>
@@ -6597,7 +6598,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="113" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>453</v>
       </c>
@@ -6635,7 +6636,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="114" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>3</v>
       </c>
@@ -6673,7 +6674,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="115" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>20</v>
       </c>
@@ -6711,7 +6712,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="116" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>453</v>
       </c>
@@ -6749,7 +6750,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="117" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>69</v>
       </c>
@@ -6787,7 +6788,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="118" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>69</v>
       </c>
@@ -6825,7 +6826,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="119" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>244</v>
       </c>
@@ -6863,7 +6864,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="120" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>48</v>
       </c>
@@ -6901,7 +6902,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="121" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>69</v>
       </c>
@@ -6939,7 +6940,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="122" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>69</v>
       </c>
@@ -6977,7 +6978,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="123" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>374</v>
       </c>
@@ -7053,7 +7054,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="125" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>3</v>
       </c>
@@ -7091,7 +7092,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="126" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>244</v>
       </c>
@@ -7129,7 +7130,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="127" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>374</v>
       </c>
@@ -7167,7 +7168,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="128" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>453</v>
       </c>
@@ -7205,7 +7206,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="129" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>244</v>
       </c>
@@ -7243,7 +7244,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="130" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>20</v>
       </c>
@@ -7281,7 +7282,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="131" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>244</v>
       </c>
@@ -7319,7 +7320,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="132" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>244</v>
       </c>
@@ -7357,7 +7358,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="133" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>244</v>
       </c>
@@ -7395,7 +7396,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="134" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>453</v>
       </c>
@@ -7471,7 +7472,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="136" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>69</v>
       </c>
@@ -7509,7 +7510,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="137" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>363</v>
       </c>
@@ -7547,7 +7548,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="138" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>244</v>
       </c>
@@ -7585,7 +7586,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="139" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>69</v>
       </c>
@@ -7623,7 +7624,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="140" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>244</v>
       </c>
@@ -7661,7 +7662,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="141" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>244</v>
       </c>
@@ -7699,7 +7700,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="142" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>244</v>
       </c>
@@ -7737,7 +7738,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="143" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>453</v>
       </c>
@@ -7775,7 +7776,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="144" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>3</v>
       </c>
@@ -7813,7 +7814,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="145" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>244</v>
       </c>
@@ -7851,7 +7852,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="146" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>20</v>
       </c>
@@ -7889,7 +7890,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="147" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>374</v>
       </c>
@@ -7927,7 +7928,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="148" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>69</v>
       </c>
@@ -7965,7 +7966,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="149" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>453</v>
       </c>
@@ -8003,7 +8004,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="150" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>453</v>
       </c>
@@ -8041,7 +8042,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="151" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>244</v>
       </c>
@@ -8079,7 +8080,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="152" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>374</v>
       </c>
@@ -8117,7 +8118,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="153" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>244</v>
       </c>
@@ -8155,7 +8156,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="154" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>374</v>
       </c>
@@ -8193,7 +8194,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="155" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>374</v>
       </c>
@@ -8231,7 +8232,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="156" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>374</v>
       </c>
@@ -8307,7 +8308,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="158" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>244</v>
       </c>
@@ -8345,7 +8346,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="159" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>230</v>
       </c>
@@ -8383,7 +8384,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="160" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>244</v>
       </c>
@@ -8421,7 +8422,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="161" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>244</v>
       </c>
@@ -8459,7 +8460,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="162" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>48</v>
       </c>
@@ -8497,7 +8498,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="163" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>244</v>
       </c>
@@ -8535,7 +8536,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="164" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>374</v>
       </c>
@@ -8611,7 +8612,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="166" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>374</v>
       </c>
@@ -8649,7 +8650,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="167" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>69</v>
       </c>
@@ -8687,7 +8688,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="168" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>69</v>
       </c>
@@ -8725,7 +8726,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="169" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>244</v>
       </c>
@@ -8763,7 +8764,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="170" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>69</v>
       </c>
@@ -8801,7 +8802,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="171" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>69</v>
       </c>
@@ -8839,7 +8840,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="172" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>374</v>
       </c>
@@ -8877,7 +8878,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="173" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>374</v>
       </c>
@@ -8915,7 +8916,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="174" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>48</v>
       </c>
@@ -8953,7 +8954,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="175" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>453</v>
       </c>
@@ -8991,7 +8992,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="176" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>244</v>
       </c>
@@ -9029,7 +9030,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="177" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>69</v>
       </c>
@@ -9067,7 +9068,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="178" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>374</v>
       </c>
@@ -9105,7 +9106,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="179" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>69</v>
       </c>
@@ -9143,7 +9144,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="180" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>374</v>
       </c>
@@ -9181,7 +9182,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="181" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>69</v>
       </c>
@@ -9219,7 +9220,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="182" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>244</v>
       </c>
@@ -9257,7 +9258,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="183" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>3</v>
       </c>
@@ -9295,7 +9296,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="184" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>69</v>
       </c>
@@ -9333,7 +9334,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="185" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>374</v>
       </c>
@@ -9371,7 +9372,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="186" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>244</v>
       </c>
@@ -9409,7 +9410,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="187" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>69</v>
       </c>
@@ -9447,7 +9448,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="188" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>69</v>
       </c>
@@ -9485,7 +9486,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="189" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>69</v>
       </c>
@@ -9523,7 +9524,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="190" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>374</v>
       </c>
@@ -9561,7 +9562,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="191" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>453</v>
       </c>
@@ -9599,7 +9600,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="192" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>453</v>
       </c>
@@ -9637,7 +9638,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="193" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>363</v>
       </c>
@@ -9675,7 +9676,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="194" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>244</v>
       </c>
@@ -9713,7 +9714,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="195" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>374</v>
       </c>
@@ -9751,7 +9752,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="196" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>244</v>
       </c>
@@ -9789,7 +9790,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="197" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>69</v>
       </c>
@@ -9827,7 +9828,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="198" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>453</v>
       </c>
@@ -9865,7 +9866,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="199" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>453</v>
       </c>
@@ -9941,7 +9942,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="201" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>3</v>
       </c>
@@ -10017,7 +10018,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="203" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>244</v>
       </c>
@@ -10055,7 +10056,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="204" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>363</v>
       </c>
@@ -10093,7 +10094,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="205" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>48</v>
       </c>
@@ -10131,7 +10132,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="206" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>244</v>
       </c>
@@ -10169,7 +10170,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="207" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>244</v>
       </c>
@@ -10207,7 +10208,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="208" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>374</v>
       </c>
@@ -10245,7 +10246,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="209" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>69</v>
       </c>
@@ -10283,7 +10284,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="210" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>374</v>
       </c>
@@ -10321,7 +10322,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="211" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>244</v>
       </c>
@@ -10359,7 +10360,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="212" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>69</v>
       </c>
@@ -10397,7 +10398,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="213" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>69</v>
       </c>
@@ -10435,7 +10436,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="214" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>48</v>
       </c>
@@ -10473,7 +10474,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="215" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>453</v>
       </c>
@@ -10511,7 +10512,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="216" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>69</v>
       </c>
@@ -10549,7 +10550,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="217" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>69</v>
       </c>
@@ -10587,7 +10588,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="218" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>453</v>
       </c>
@@ -10625,7 +10626,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="219" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>374</v>
       </c>
@@ -10663,7 +10664,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="220" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>69</v>
       </c>
@@ -10701,7 +10702,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="221" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>69</v>
       </c>
@@ -10739,7 +10740,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="222" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>374</v>
       </c>
@@ -10777,7 +10778,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="223" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>244</v>
       </c>
@@ -10815,7 +10816,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="224" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>453</v>
       </c>
@@ -10853,7 +10854,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="225" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>69</v>
       </c>
@@ -10929,7 +10930,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="227" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>69</v>
       </c>
@@ -10967,7 +10968,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="228" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>69</v>
       </c>
@@ -11005,7 +11006,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="229" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>69</v>
       </c>
@@ -11043,7 +11044,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="230" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
         <v>453</v>
       </c>
@@ -11081,7 +11082,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="231" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
         <v>244</v>
       </c>
@@ -11119,7 +11120,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="232" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
         <v>244</v>
       </c>
@@ -11157,7 +11158,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="233" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
         <v>237</v>
       </c>
@@ -11195,7 +11196,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="234" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
         <v>48</v>
       </c>
@@ -11233,7 +11234,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="235" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
         <v>48</v>
       </c>
@@ -11271,7 +11272,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="236" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
         <v>453</v>
       </c>
@@ -11309,7 +11310,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="237" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
         <v>453</v>
       </c>
@@ -11347,7 +11348,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="238" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
         <v>45</v>
       </c>
@@ -11385,7 +11386,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="239" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
         <v>244</v>
       </c>
@@ -11423,7 +11424,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="240" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
         <v>3</v>
       </c>
@@ -11461,7 +11462,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="241" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
         <v>69</v>
       </c>
@@ -11499,7 +11500,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="242" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
         <v>69</v>
       </c>
@@ -11537,7 +11538,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="243" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
         <v>3</v>
       </c>
@@ -11575,7 +11576,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="244" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
         <v>244</v>
       </c>
@@ -11613,7 +11614,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="245" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
         <v>244</v>
       </c>
@@ -11651,7 +11652,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="246" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
         <v>244</v>
       </c>
@@ -11689,7 +11690,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="247" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
         <v>374</v>
       </c>
@@ -11803,7 +11804,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="250" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
         <v>244</v>
       </c>
@@ -11841,7 +11842,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="251" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
         <v>244</v>
       </c>
@@ -11879,7 +11880,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="252" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
         <v>374</v>
       </c>
@@ -11917,7 +11918,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="253" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
         <v>374</v>
       </c>
@@ -11955,7 +11956,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="254" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
         <v>69</v>
       </c>
@@ -11993,7 +11994,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="255" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
         <v>374</v>
       </c>
@@ -12031,7 +12032,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="256" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
         <v>244</v>
       </c>
@@ -12069,7 +12070,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="257" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
         <v>244</v>
       </c>
@@ -12107,7 +12108,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="258" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
         <v>69</v>
       </c>
@@ -12145,7 +12146,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="259" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
         <v>374</v>
       </c>
@@ -12183,7 +12184,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="260" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
         <v>374</v>
       </c>
@@ -12221,7 +12222,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="261" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
         <v>453</v>
       </c>
@@ -12259,7 +12260,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="262" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
         <v>453</v>
       </c>
@@ -12297,7 +12298,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="263" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
         <v>237</v>
       </c>
@@ -12335,7 +12336,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="264" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
         <v>69</v>
       </c>
@@ -12373,7 +12374,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="265" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
         <v>453</v>
       </c>
@@ -12411,7 +12412,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="266" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
         <v>69</v>
       </c>
@@ -12449,7 +12450,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="267" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
         <v>374</v>
       </c>
@@ -12487,7 +12488,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="268" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
         <v>237</v>
       </c>
@@ -12525,7 +12526,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="269" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
         <v>453</v>
       </c>
@@ -12563,7 +12564,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="270" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
         <v>453</v>
       </c>
@@ -12601,7 +12602,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="271" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
         <v>48</v>
       </c>
@@ -12639,7 +12640,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="272" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
         <v>453</v>
       </c>
@@ -12677,7 +12678,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="273" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
         <v>374</v>
       </c>
@@ -12715,7 +12716,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="274" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
         <v>69</v>
       </c>
@@ -12753,7 +12754,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="275" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
         <v>69</v>
       </c>
@@ -12791,7 +12792,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="276" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
         <v>374</v>
       </c>
@@ -12829,7 +12830,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="277" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
         <v>69</v>
       </c>
@@ -12869,6 +12870,11 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:L277">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="Zoogdieren"/>
+      </filters>
+    </filterColumn>
     <sortState ref="A2:L277">
       <sortCondition ref="B1:B277"/>
     </sortState>

--- a/data/input/Excel_files/Soortenlijst_Maatwerkgebieden.xlsx
+++ b/data/input/Excel_files/Soortenlijst_Maatwerkgebieden.xlsx
@@ -1206,9 +1206,6 @@
     <t>Grote zilverreiger</t>
   </si>
   <si>
-    <t>Grote zilvereiger</t>
-  </si>
-  <si>
     <t>Grutto</t>
   </si>
   <si>
@@ -1786,6 +1783,9 @@
   </si>
   <si>
     <t>Turnhouts_Vennegebied</t>
+  </si>
+  <si>
+    <t>Limosa limosa</t>
   </si>
 </sst>
 </file>
@@ -2278,7 +2278,7 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
@@ -2287,34 +2287,34 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="E1" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="F1" t="s">
+        <v>579</v>
+      </c>
+      <c r="G1" t="s">
+        <v>545</v>
+      </c>
+      <c r="H1" t="s">
         <v>580</v>
       </c>
-      <c r="G1" t="s">
-        <v>546</v>
-      </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>581</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>582</v>
       </c>
-      <c r="J1" t="s">
-        <v>583</v>
-      </c>
       <c r="K1" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="L1" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -2325,10 +2325,10 @@
         <v>7</v>
       </c>
       <c r="D2" t="s">
+        <v>572</v>
+      </c>
+      <c r="E2" t="s">
         <v>573</v>
-      </c>
-      <c r="E2" t="s">
-        <v>574</v>
       </c>
       <c r="F2">
         <v>1</v>
@@ -2349,10 +2349,10 @@
         <v>0</v>
       </c>
       <c r="L2" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -2363,10 +2363,10 @@
         <v>9</v>
       </c>
       <c r="D3" t="s">
+        <v>572</v>
+      </c>
+      <c r="E3" t="s">
         <v>573</v>
-      </c>
-      <c r="E3" t="s">
-        <v>574</v>
       </c>
       <c r="F3">
         <v>1</v>
@@ -2387,10 +2387,10 @@
         <v>0</v>
       </c>
       <c r="L3" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2401,10 +2401,10 @@
         <v>11</v>
       </c>
       <c r="D4" t="s">
+        <v>572</v>
+      </c>
+      <c r="E4" t="s">
         <v>573</v>
-      </c>
-      <c r="E4" t="s">
-        <v>574</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -2425,10 +2425,10 @@
         <v>1</v>
       </c>
       <c r="L4" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -2439,10 +2439,10 @@
         <v>13</v>
       </c>
       <c r="D5" t="s">
+        <v>572</v>
+      </c>
+      <c r="E5" t="s">
         <v>573</v>
-      </c>
-      <c r="E5" t="s">
-        <v>574</v>
       </c>
       <c r="F5">
         <v>1</v>
@@ -2463,10 +2463,10 @@
         <v>0</v>
       </c>
       <c r="L5" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -2477,10 +2477,10 @@
         <v>15</v>
       </c>
       <c r="D6" t="s">
+        <v>572</v>
+      </c>
+      <c r="E6" t="s">
         <v>573</v>
-      </c>
-      <c r="E6" t="s">
-        <v>574</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -2501,10 +2501,10 @@
         <v>0</v>
       </c>
       <c r="L6" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -2515,10 +2515,10 @@
         <v>17</v>
       </c>
       <c r="D7" t="s">
+        <v>572</v>
+      </c>
+      <c r="E7" t="s">
         <v>573</v>
-      </c>
-      <c r="E7" t="s">
-        <v>574</v>
       </c>
       <c r="F7">
         <v>1</v>
@@ -2539,10 +2539,10 @@
         <v>0</v>
       </c>
       <c r="L7" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -2553,10 +2553,10 @@
         <v>5</v>
       </c>
       <c r="D8" t="s">
+        <v>572</v>
+      </c>
+      <c r="E8" t="s">
         <v>573</v>
-      </c>
-      <c r="E8" t="s">
-        <v>574</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -2577,10 +2577,10 @@
         <v>1</v>
       </c>
       <c r="L8" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -2591,10 +2591,10 @@
         <v>19</v>
       </c>
       <c r="D9" t="s">
+        <v>572</v>
+      </c>
+      <c r="E9" t="s">
         <v>573</v>
-      </c>
-      <c r="E9" t="s">
-        <v>574</v>
       </c>
       <c r="F9">
         <v>1</v>
@@ -2615,7 +2615,7 @@
         <v>1</v>
       </c>
       <c r="L9" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="10" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -2629,10 +2629,10 @@
         <v>22</v>
       </c>
       <c r="D10" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="E10" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="F10">
         <v>1</v>
@@ -2653,7 +2653,7 @@
         <v>1</v>
       </c>
       <c r="L10" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="11" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -2667,11 +2667,11 @@
         <v>24</v>
       </c>
       <c r="D11" t="s">
+        <v>572</v>
+      </c>
+      <c r="E11" t="s">
         <v>573</v>
       </c>
-      <c r="E11" t="s">
-        <v>574</v>
-      </c>
       <c r="F11">
         <v>1</v>
       </c>
@@ -2691,7 +2691,7 @@
         <v>1</v>
       </c>
       <c r="L11" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="12" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -2705,10 +2705,10 @@
         <v>26</v>
       </c>
       <c r="D12" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="E12" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="F12">
         <v>1</v>
@@ -2729,7 +2729,7 @@
         <v>1</v>
       </c>
       <c r="L12" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="13" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -2743,11 +2743,11 @@
         <v>28</v>
       </c>
       <c r="D13" t="s">
+        <v>572</v>
+      </c>
+      <c r="E13" t="s">
         <v>573</v>
       </c>
-      <c r="E13" t="s">
-        <v>574</v>
-      </c>
       <c r="F13">
         <v>1</v>
       </c>
@@ -2767,7 +2767,7 @@
         <v>1</v>
       </c>
       <c r="L13" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="14" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -2781,10 +2781,10 @@
         <v>30</v>
       </c>
       <c r="D14" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="E14" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -2805,7 +2805,7 @@
         <v>1</v>
       </c>
       <c r="L14" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="15" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -2819,10 +2819,10 @@
         <v>32</v>
       </c>
       <c r="D15" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="E15" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="F15">
         <v>0</v>
@@ -2843,7 +2843,7 @@
         <v>1</v>
       </c>
       <c r="L15" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="16" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -2857,10 +2857,10 @@
         <v>34</v>
       </c>
       <c r="D16" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="E16" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="F16">
         <v>1</v>
@@ -2881,7 +2881,7 @@
         <v>0</v>
       </c>
       <c r="L16" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="17" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -2895,10 +2895,10 @@
         <v>36</v>
       </c>
       <c r="D17" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="E17" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="F17">
         <v>1</v>
@@ -2919,7 +2919,7 @@
         <v>1</v>
       </c>
       <c r="L17" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="18" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -2933,10 +2933,10 @@
         <v>38</v>
       </c>
       <c r="D18" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="E18" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="F18">
         <v>1</v>
@@ -2957,7 +2957,7 @@
         <v>1</v>
       </c>
       <c r="L18" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="19" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -2971,11 +2971,11 @@
         <v>40</v>
       </c>
       <c r="D19" t="s">
+        <v>572</v>
+      </c>
+      <c r="E19" t="s">
         <v>573</v>
       </c>
-      <c r="E19" t="s">
-        <v>574</v>
-      </c>
       <c r="F19">
         <v>1</v>
       </c>
@@ -2995,7 +2995,7 @@
         <v>1</v>
       </c>
       <c r="L19" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="20" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -3009,10 +3009,10 @@
         <v>42</v>
       </c>
       <c r="D20" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="E20" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="F20">
         <v>0</v>
@@ -3033,7 +3033,7 @@
         <v>1</v>
       </c>
       <c r="L20" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="21" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -3047,11 +3047,11 @@
         <v>44</v>
       </c>
       <c r="D21" t="s">
+        <v>572</v>
+      </c>
+      <c r="E21" t="s">
         <v>573</v>
       </c>
-      <c r="E21" t="s">
-        <v>574</v>
-      </c>
       <c r="F21">
         <v>1</v>
       </c>
@@ -3071,7 +3071,7 @@
         <v>1</v>
       </c>
       <c r="L21" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="22" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -3085,10 +3085,10 @@
         <v>47</v>
       </c>
       <c r="D22" t="s">
+        <v>572</v>
+      </c>
+      <c r="E22" t="s">
         <v>573</v>
-      </c>
-      <c r="E22" t="s">
-        <v>574</v>
       </c>
       <c r="F22">
         <v>0</v>
@@ -3109,7 +3109,7 @@
         <v>1</v>
       </c>
       <c r="L22" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="23" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -3123,10 +3123,10 @@
         <v>50</v>
       </c>
       <c r="D23" t="s">
+        <v>572</v>
+      </c>
+      <c r="E23" t="s">
         <v>573</v>
-      </c>
-      <c r="E23" t="s">
-        <v>574</v>
       </c>
       <c r="F23">
         <v>0</v>
@@ -3147,7 +3147,7 @@
         <v>1</v>
       </c>
       <c r="L23" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="24" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -3161,10 +3161,10 @@
         <v>52</v>
       </c>
       <c r="D24" t="s">
+        <v>572</v>
+      </c>
+      <c r="E24" t="s">
         <v>573</v>
-      </c>
-      <c r="E24" t="s">
-        <v>574</v>
       </c>
       <c r="F24">
         <v>1</v>
@@ -3185,7 +3185,7 @@
         <v>0</v>
       </c>
       <c r="L24" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="25" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -3199,10 +3199,10 @@
         <v>54</v>
       </c>
       <c r="D25" t="s">
+        <v>572</v>
+      </c>
+      <c r="E25" t="s">
         <v>573</v>
-      </c>
-      <c r="E25" t="s">
-        <v>574</v>
       </c>
       <c r="F25">
         <v>1</v>
@@ -3223,7 +3223,7 @@
         <v>0</v>
       </c>
       <c r="L25" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="26" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -3237,10 +3237,10 @@
         <v>56</v>
       </c>
       <c r="D26" t="s">
+        <v>572</v>
+      </c>
+      <c r="E26" t="s">
         <v>573</v>
-      </c>
-      <c r="E26" t="s">
-        <v>574</v>
       </c>
       <c r="F26">
         <v>1</v>
@@ -3261,7 +3261,7 @@
         <v>0</v>
       </c>
       <c r="L26" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="27" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -3275,10 +3275,10 @@
         <v>58</v>
       </c>
       <c r="D27" t="s">
+        <v>572</v>
+      </c>
+      <c r="E27" t="s">
         <v>573</v>
-      </c>
-      <c r="E27" t="s">
-        <v>574</v>
       </c>
       <c r="F27">
         <v>0</v>
@@ -3299,7 +3299,7 @@
         <v>0</v>
       </c>
       <c r="L27" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="28" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -3313,10 +3313,10 @@
         <v>60</v>
       </c>
       <c r="D28" t="s">
+        <v>572</v>
+      </c>
+      <c r="E28" t="s">
         <v>573</v>
-      </c>
-      <c r="E28" t="s">
-        <v>574</v>
       </c>
       <c r="F28">
         <v>1</v>
@@ -3337,7 +3337,7 @@
         <v>0</v>
       </c>
       <c r="L28" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="29" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -3351,10 +3351,10 @@
         <v>62</v>
       </c>
       <c r="D29" t="s">
+        <v>572</v>
+      </c>
+      <c r="E29" t="s">
         <v>573</v>
-      </c>
-      <c r="E29" t="s">
-        <v>574</v>
       </c>
       <c r="F29">
         <v>1</v>
@@ -3375,7 +3375,7 @@
         <v>0</v>
       </c>
       <c r="L29" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="30" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -3389,10 +3389,10 @@
         <v>64</v>
       </c>
       <c r="D30" t="s">
+        <v>572</v>
+      </c>
+      <c r="E30" t="s">
         <v>573</v>
-      </c>
-      <c r="E30" t="s">
-        <v>574</v>
       </c>
       <c r="F30">
         <v>1</v>
@@ -3413,7 +3413,7 @@
         <v>0</v>
       </c>
       <c r="L30" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="31" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -3427,10 +3427,10 @@
         <v>66</v>
       </c>
       <c r="D31" t="s">
+        <v>572</v>
+      </c>
+      <c r="E31" t="s">
         <v>573</v>
-      </c>
-      <c r="E31" t="s">
-        <v>574</v>
       </c>
       <c r="F31">
         <v>1</v>
@@ -3451,7 +3451,7 @@
         <v>0</v>
       </c>
       <c r="L31" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="32" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -3465,10 +3465,10 @@
         <v>68</v>
       </c>
       <c r="D32" t="s">
+        <v>572</v>
+      </c>
+      <c r="E32" t="s">
         <v>573</v>
-      </c>
-      <c r="E32" t="s">
-        <v>574</v>
       </c>
       <c r="F32">
         <v>0</v>
@@ -3489,7 +3489,7 @@
         <v>0</v>
       </c>
       <c r="L32" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="33" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -3503,10 +3503,10 @@
         <v>193</v>
       </c>
       <c r="D33" t="s">
+        <v>572</v>
+      </c>
+      <c r="E33" t="s">
         <v>573</v>
-      </c>
-      <c r="E33" t="s">
-        <v>574</v>
       </c>
       <c r="F33">
         <v>1</v>
@@ -3527,10 +3527,10 @@
         <v>1</v>
       </c>
       <c r="L33" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>230</v>
       </c>
@@ -3541,10 +3541,10 @@
         <v>232</v>
       </c>
       <c r="D34" t="s">
+        <v>572</v>
+      </c>
+      <c r="E34" t="s">
         <v>573</v>
-      </c>
-      <c r="E34" t="s">
-        <v>574</v>
       </c>
       <c r="F34">
         <v>1</v>
@@ -3565,10 +3565,10 @@
         <v>0</v>
       </c>
       <c r="L34" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>230</v>
       </c>
@@ -3579,11 +3579,11 @@
         <v>234</v>
       </c>
       <c r="D35" t="s">
+        <v>572</v>
+      </c>
+      <c r="E35" t="s">
         <v>573</v>
       </c>
-      <c r="E35" t="s">
-        <v>574</v>
-      </c>
       <c r="F35">
         <v>1</v>
       </c>
@@ -3603,10 +3603,10 @@
         <v>1</v>
       </c>
       <c r="L35" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>230</v>
       </c>
@@ -3617,11 +3617,11 @@
         <v>236</v>
       </c>
       <c r="D36" t="s">
+        <v>572</v>
+      </c>
+      <c r="E36" t="s">
         <v>573</v>
       </c>
-      <c r="E36" t="s">
-        <v>574</v>
-      </c>
       <c r="F36">
         <v>1</v>
       </c>
@@ -3641,7 +3641,7 @@
         <v>1</v>
       </c>
       <c r="L36" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="37" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -3655,10 +3655,10 @@
         <v>239</v>
       </c>
       <c r="D37" t="s">
+        <v>572</v>
+      </c>
+      <c r="E37" t="s">
         <v>573</v>
-      </c>
-      <c r="E37" t="s">
-        <v>574</v>
       </c>
       <c r="F37">
         <v>1</v>
@@ -3679,7 +3679,7 @@
         <v>1</v>
       </c>
       <c r="L37" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="38" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -3693,11 +3693,11 @@
         <v>241</v>
       </c>
       <c r="D38" t="s">
+        <v>572</v>
+      </c>
+      <c r="E38" t="s">
         <v>573</v>
       </c>
-      <c r="E38" t="s">
-        <v>574</v>
-      </c>
       <c r="F38">
         <v>1</v>
       </c>
@@ -3717,7 +3717,7 @@
         <v>1</v>
       </c>
       <c r="L38" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="39" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -3731,10 +3731,10 @@
         <v>243</v>
       </c>
       <c r="D39" t="s">
+        <v>572</v>
+      </c>
+      <c r="E39" t="s">
         <v>573</v>
-      </c>
-      <c r="E39" t="s">
-        <v>574</v>
       </c>
       <c r="F39">
         <v>0</v>
@@ -3755,7 +3755,7 @@
         <v>1</v>
       </c>
       <c r="L39" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="40" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -3769,10 +3769,10 @@
         <v>246</v>
       </c>
       <c r="D40" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="E40" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="F40">
         <v>0</v>
@@ -3793,7 +3793,7 @@
         <v>0</v>
       </c>
       <c r="L40" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="41" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -3807,10 +3807,10 @@
         <v>248</v>
       </c>
       <c r="D41" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="E41" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="F41">
         <v>0</v>
@@ -3831,7 +3831,7 @@
         <v>0</v>
       </c>
       <c r="L41" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="42" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -3845,10 +3845,10 @@
         <v>250</v>
       </c>
       <c r="D42" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="E42" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="F42">
         <v>1</v>
@@ -3869,7 +3869,7 @@
         <v>0</v>
       </c>
       <c r="L42" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="43" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -3883,10 +3883,10 @@
         <v>252</v>
       </c>
       <c r="D43" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="E43" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="F43">
         <v>0</v>
@@ -3907,7 +3907,7 @@
         <v>1</v>
       </c>
       <c r="L43" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="44" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -3921,10 +3921,10 @@
         <v>254</v>
       </c>
       <c r="D44" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="E44" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="F44">
         <v>0</v>
@@ -3945,7 +3945,7 @@
         <v>1</v>
       </c>
       <c r="L44" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="45" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -3959,10 +3959,10 @@
         <v>256</v>
       </c>
       <c r="D45" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="E45" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="F45">
         <v>0</v>
@@ -3983,7 +3983,7 @@
         <v>0</v>
       </c>
       <c r="L45" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="46" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -3997,10 +3997,10 @@
         <v>258</v>
       </c>
       <c r="D46" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="E46" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="F46">
         <v>1</v>
@@ -4021,7 +4021,7 @@
         <v>0</v>
       </c>
       <c r="L46" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="47" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -4035,10 +4035,10 @@
         <v>260</v>
       </c>
       <c r="D47" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="E47" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="F47">
         <v>0</v>
@@ -4059,7 +4059,7 @@
         <v>1</v>
       </c>
       <c r="L47" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="48" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -4073,10 +4073,10 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="E48" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="F48">
         <v>1</v>
@@ -4097,7 +4097,7 @@
         <v>0</v>
       </c>
       <c r="L48" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="49" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -4111,10 +4111,10 @@
         <v>264</v>
       </c>
       <c r="D49" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="E49" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="F49">
         <v>1</v>
@@ -4135,7 +4135,7 @@
         <v>0</v>
       </c>
       <c r="L49" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="50" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -4149,10 +4149,10 @@
         <v>266</v>
       </c>
       <c r="D50" t="s">
+        <v>572</v>
+      </c>
+      <c r="E50" t="s">
         <v>573</v>
-      </c>
-      <c r="E50" t="s">
-        <v>574</v>
       </c>
       <c r="F50">
         <v>1</v>
@@ -4173,7 +4173,7 @@
         <v>0</v>
       </c>
       <c r="L50" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="51" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -4187,10 +4187,10 @@
         <v>268</v>
       </c>
       <c r="D51" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="E51" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="F51">
         <v>1</v>
@@ -4211,7 +4211,7 @@
         <v>0</v>
       </c>
       <c r="L51" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="52" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -4225,10 +4225,10 @@
         <v>270</v>
       </c>
       <c r="D52" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="E52" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="F52">
         <v>1</v>
@@ -4249,7 +4249,7 @@
         <v>0</v>
       </c>
       <c r="L52" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="53" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -4263,10 +4263,10 @@
         <v>272</v>
       </c>
       <c r="D53" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="E53" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="F53">
         <v>0</v>
@@ -4287,7 +4287,7 @@
         <v>1</v>
       </c>
       <c r="L53" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="54" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -4301,10 +4301,10 @@
         <v>274</v>
       </c>
       <c r="D54" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="E54" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="F54">
         <v>1</v>
@@ -4325,7 +4325,7 @@
         <v>0</v>
       </c>
       <c r="L54" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="55" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -4339,10 +4339,10 @@
         <v>276</v>
       </c>
       <c r="D55" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="E55" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="F55">
         <v>0</v>
@@ -4363,7 +4363,7 @@
         <v>0</v>
       </c>
       <c r="L55" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="56" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -4377,10 +4377,10 @@
         <v>278</v>
       </c>
       <c r="D56" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="E56" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="F56">
         <v>0</v>
@@ -4401,7 +4401,7 @@
         <v>1</v>
       </c>
       <c r="L56" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="57" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -4415,10 +4415,10 @@
         <v>280</v>
       </c>
       <c r="D57" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="E57" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="F57">
         <v>0</v>
@@ -4439,7 +4439,7 @@
         <v>1</v>
       </c>
       <c r="L57" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="58" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -4453,10 +4453,10 @@
         <v>282</v>
       </c>
       <c r="D58" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="E58" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="F58">
         <v>1</v>
@@ -4477,7 +4477,7 @@
         <v>1</v>
       </c>
       <c r="L58" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="59" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -4491,10 +4491,10 @@
         <v>284</v>
       </c>
       <c r="D59" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="E59" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="F59">
         <v>0</v>
@@ -4515,7 +4515,7 @@
         <v>1</v>
       </c>
       <c r="L59" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="60" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -4529,10 +4529,10 @@
         <v>286</v>
       </c>
       <c r="D60" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="E60" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="F60">
         <v>1</v>
@@ -4553,7 +4553,7 @@
         <v>1</v>
       </c>
       <c r="L60" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="61" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -4567,10 +4567,10 @@
         <v>288</v>
       </c>
       <c r="D61" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="E61" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="F61">
         <v>1</v>
@@ -4591,7 +4591,7 @@
         <v>1</v>
       </c>
       <c r="L61" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="62" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -4605,10 +4605,10 @@
         <v>290</v>
       </c>
       <c r="D62" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="E62" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="F62">
         <v>0</v>
@@ -4629,7 +4629,7 @@
         <v>1</v>
       </c>
       <c r="L62" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="63" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -4643,10 +4643,10 @@
         <v>292</v>
       </c>
       <c r="D63" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="E63" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="F63">
         <v>1</v>
@@ -4667,7 +4667,7 @@
         <v>0</v>
       </c>
       <c r="L63" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="64" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -4681,10 +4681,10 @@
         <v>294</v>
       </c>
       <c r="D64" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="E64" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="F64">
         <v>0</v>
@@ -4705,7 +4705,7 @@
         <v>0</v>
       </c>
       <c r="L64" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="65" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -4719,10 +4719,10 @@
         <v>296</v>
       </c>
       <c r="D65" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="E65" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="F65">
         <v>1</v>
@@ -4743,7 +4743,7 @@
         <v>0</v>
       </c>
       <c r="L65" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="66" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -4757,10 +4757,10 @@
         <v>298</v>
       </c>
       <c r="D66" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="E66" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="F66">
         <v>1</v>
@@ -4781,7 +4781,7 @@
         <v>1</v>
       </c>
       <c r="L66" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="67" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -4795,10 +4795,10 @@
         <v>300</v>
       </c>
       <c r="D67" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="E67" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="F67">
         <v>0</v>
@@ -4819,7 +4819,7 @@
         <v>1</v>
       </c>
       <c r="L67" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="68" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -4833,10 +4833,10 @@
         <v>302</v>
       </c>
       <c r="D68" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="E68" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="F68">
         <v>0</v>
@@ -4857,7 +4857,7 @@
         <v>1</v>
       </c>
       <c r="L68" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="69" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -4871,10 +4871,10 @@
         <v>304</v>
       </c>
       <c r="D69" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="E69" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="F69">
         <v>1</v>
@@ -4895,7 +4895,7 @@
         <v>1</v>
       </c>
       <c r="L69" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="70" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -4909,10 +4909,10 @@
         <v>306</v>
       </c>
       <c r="D70" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="E70" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="F70">
         <v>1</v>
@@ -4933,7 +4933,7 @@
         <v>0</v>
       </c>
       <c r="L70" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="71" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -4947,10 +4947,10 @@
         <v>308</v>
       </c>
       <c r="D71" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="E71" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="F71">
         <v>0</v>
@@ -4971,7 +4971,7 @@
         <v>0</v>
       </c>
       <c r="L71" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="72" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -4985,10 +4985,10 @@
         <v>310</v>
       </c>
       <c r="D72" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="E72" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="F72">
         <v>1</v>
@@ -5009,7 +5009,7 @@
         <v>0</v>
       </c>
       <c r="L72" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="73" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -5023,10 +5023,10 @@
         <v>312</v>
       </c>
       <c r="D73" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="E73" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="F73">
         <v>1</v>
@@ -5047,7 +5047,7 @@
         <v>1</v>
       </c>
       <c r="L73" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="74" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -5061,10 +5061,10 @@
         <v>314</v>
       </c>
       <c r="D74" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="E74" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="F74">
         <v>1</v>
@@ -5085,7 +5085,7 @@
         <v>0</v>
       </c>
       <c r="L74" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="75" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -5099,10 +5099,10 @@
         <v>316</v>
       </c>
       <c r="D75" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="E75" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="F75">
         <v>1</v>
@@ -5123,7 +5123,7 @@
         <v>1</v>
       </c>
       <c r="L75" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="76" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -5137,10 +5137,10 @@
         <v>318</v>
       </c>
       <c r="D76" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="E76" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="F76">
         <v>1</v>
@@ -5161,7 +5161,7 @@
         <v>0</v>
       </c>
       <c r="L76" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="77" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -5175,10 +5175,10 @@
         <v>320</v>
       </c>
       <c r="D77" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="E77" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="F77">
         <v>0</v>
@@ -5199,7 +5199,7 @@
         <v>1</v>
       </c>
       <c r="L77" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="78" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -5213,10 +5213,10 @@
         <v>322</v>
       </c>
       <c r="D78" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="E78" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="F78">
         <v>1</v>
@@ -5237,7 +5237,7 @@
         <v>0</v>
       </c>
       <c r="L78" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="79" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -5251,10 +5251,10 @@
         <v>324</v>
       </c>
       <c r="D79" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="E79" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="F79">
         <v>1</v>
@@ -5275,7 +5275,7 @@
         <v>0</v>
       </c>
       <c r="L79" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="80" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -5289,10 +5289,10 @@
         <v>326</v>
       </c>
       <c r="D80" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="E80" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="F80">
         <v>1</v>
@@ -5313,7 +5313,7 @@
         <v>0</v>
       </c>
       <c r="L80" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="81" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -5327,10 +5327,10 @@
         <v>328</v>
       </c>
       <c r="D81" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="E81" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="F81">
         <v>0</v>
@@ -5351,7 +5351,7 @@
         <v>1</v>
       </c>
       <c r="L81" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="82" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -5365,10 +5365,10 @@
         <v>330</v>
       </c>
       <c r="D82" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="E82" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="F82">
         <v>1</v>
@@ -5389,7 +5389,7 @@
         <v>1</v>
       </c>
       <c r="L82" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="83" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -5403,10 +5403,10 @@
         <v>332</v>
       </c>
       <c r="D83" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="E83" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="F83">
         <v>1</v>
@@ -5427,7 +5427,7 @@
         <v>0</v>
       </c>
       <c r="L83" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="84" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -5441,10 +5441,10 @@
         <v>334</v>
       </c>
       <c r="D84" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="E84" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="F84">
         <v>0</v>
@@ -5465,7 +5465,7 @@
         <v>1</v>
       </c>
       <c r="L84" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="85" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -5479,10 +5479,10 @@
         <v>336</v>
       </c>
       <c r="D85" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="E85" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="F85">
         <v>0</v>
@@ -5503,7 +5503,7 @@
         <v>0</v>
       </c>
       <c r="L85" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="86" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -5517,10 +5517,10 @@
         <v>338</v>
       </c>
       <c r="D86" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="E86" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="F86">
         <v>0</v>
@@ -5541,7 +5541,7 @@
         <v>0</v>
       </c>
       <c r="L86" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="87" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -5555,10 +5555,10 @@
         <v>340</v>
       </c>
       <c r="D87" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="E87" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="F87">
         <v>0</v>
@@ -5579,7 +5579,7 @@
         <v>1</v>
       </c>
       <c r="L87" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="88" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -5593,10 +5593,10 @@
         <v>342</v>
       </c>
       <c r="D88" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="E88" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="F88">
         <v>0</v>
@@ -5617,7 +5617,7 @@
         <v>0</v>
       </c>
       <c r="L88" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="89" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -5631,10 +5631,10 @@
         <v>344</v>
       </c>
       <c r="D89" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="E89" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="F89">
         <v>1</v>
@@ -5655,7 +5655,7 @@
         <v>0</v>
       </c>
       <c r="L89" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="90" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -5669,10 +5669,10 @@
         <v>346</v>
       </c>
       <c r="D90" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="E90" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="F90">
         <v>1</v>
@@ -5693,7 +5693,7 @@
         <v>0</v>
       </c>
       <c r="L90" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="91" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -5707,10 +5707,10 @@
         <v>348</v>
       </c>
       <c r="D91" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="E91" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="F91">
         <v>0</v>
@@ -5731,7 +5731,7 @@
         <v>1</v>
       </c>
       <c r="L91" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="92" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -5745,10 +5745,10 @@
         <v>350</v>
       </c>
       <c r="D92" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="E92" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="F92">
         <v>1</v>
@@ -5769,7 +5769,7 @@
         <v>0</v>
       </c>
       <c r="L92" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="93" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -5783,10 +5783,10 @@
         <v>352</v>
       </c>
       <c r="D93" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="E93" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="F93">
         <v>1</v>
@@ -5807,7 +5807,7 @@
         <v>0</v>
       </c>
       <c r="L93" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="94" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -5821,10 +5821,10 @@
         <v>354</v>
       </c>
       <c r="D94" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="E94" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="F94">
         <v>1</v>
@@ -5845,7 +5845,7 @@
         <v>0</v>
       </c>
       <c r="L94" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="95" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -5859,10 +5859,10 @@
         <v>356</v>
       </c>
       <c r="D95" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="E95" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="F95">
         <v>0</v>
@@ -5883,7 +5883,7 @@
         <v>1</v>
       </c>
       <c r="L95" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="96" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -5897,10 +5897,10 @@
         <v>358</v>
       </c>
       <c r="D96" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="E96" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="F96">
         <v>1</v>
@@ -5921,7 +5921,7 @@
         <v>1</v>
       </c>
       <c r="L96" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="97" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -5935,10 +5935,10 @@
         <v>360</v>
       </c>
       <c r="D97" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="E97" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="F97">
         <v>1</v>
@@ -5959,7 +5959,7 @@
         <v>0</v>
       </c>
       <c r="L97" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="98" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -5973,10 +5973,10 @@
         <v>362</v>
       </c>
       <c r="D98" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="E98" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="F98">
         <v>1</v>
@@ -5997,7 +5997,7 @@
         <v>0</v>
       </c>
       <c r="L98" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="99" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -6011,10 +6011,10 @@
         <v>367</v>
       </c>
       <c r="D99" t="s">
+        <v>572</v>
+      </c>
+      <c r="E99" t="s">
         <v>573</v>
-      </c>
-      <c r="E99" t="s">
-        <v>574</v>
       </c>
       <c r="F99">
         <v>1</v>
@@ -6035,10 +6035,10 @@
         <v>0</v>
       </c>
       <c r="L99" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="100" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="100" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>372</v>
       </c>
@@ -6049,10 +6049,10 @@
         <v>374</v>
       </c>
       <c r="D100" t="s">
+        <v>572</v>
+      </c>
+      <c r="E100" t="s">
         <v>573</v>
-      </c>
-      <c r="E100" t="s">
-        <v>574</v>
       </c>
       <c r="F100">
         <v>0</v>
@@ -6073,10 +6073,10 @@
         <v>0</v>
       </c>
       <c r="L100" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="101" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="101" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>372</v>
       </c>
@@ -6087,10 +6087,10 @@
         <v>376</v>
       </c>
       <c r="D101" t="s">
+        <v>572</v>
+      </c>
+      <c r="E101" t="s">
         <v>573</v>
-      </c>
-      <c r="E101" t="s">
-        <v>574</v>
       </c>
       <c r="F101">
         <v>1</v>
@@ -6111,7 +6111,7 @@
         <v>0</v>
       </c>
       <c r="L101" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="102" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -6125,10 +6125,10 @@
         <v>378</v>
       </c>
       <c r="D102" t="s">
+        <v>572</v>
+      </c>
+      <c r="E102" t="s">
         <v>573</v>
-      </c>
-      <c r="E102" t="s">
-        <v>574</v>
       </c>
       <c r="F102">
         <v>0</v>
@@ -6149,10 +6149,10 @@
         <v>0</v>
       </c>
       <c r="L102" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="103" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="103" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>372</v>
       </c>
@@ -6163,10 +6163,10 @@
         <v>380</v>
       </c>
       <c r="D103" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="E103" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="F103">
         <v>0</v>
@@ -6187,10 +6187,10 @@
         <v>0</v>
       </c>
       <c r="L103" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="104" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="104" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>372</v>
       </c>
@@ -6201,10 +6201,10 @@
         <v>382</v>
       </c>
       <c r="D104" t="s">
+        <v>572</v>
+      </c>
+      <c r="E104" t="s">
         <v>573</v>
-      </c>
-      <c r="E104" t="s">
-        <v>574</v>
       </c>
       <c r="F104">
         <v>0</v>
@@ -6225,10 +6225,10 @@
         <v>0</v>
       </c>
       <c r="L104" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="105" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="105" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>372</v>
       </c>
@@ -6239,10 +6239,10 @@
         <v>384</v>
       </c>
       <c r="D105" t="s">
+        <v>572</v>
+      </c>
+      <c r="E105" t="s">
         <v>573</v>
-      </c>
-      <c r="E105" t="s">
-        <v>574</v>
       </c>
       <c r="F105">
         <v>1</v>
@@ -6263,10 +6263,10 @@
         <v>0</v>
       </c>
       <c r="L105" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="106" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="106" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>372</v>
       </c>
@@ -6277,10 +6277,10 @@
         <v>386</v>
       </c>
       <c r="D106" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="E106" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="F106">
         <v>0</v>
@@ -6301,7 +6301,7 @@
         <v>1</v>
       </c>
       <c r="L106" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="107" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -6315,10 +6315,10 @@
         <v>388</v>
       </c>
       <c r="D107" t="s">
+        <v>572</v>
+      </c>
+      <c r="E107" t="s">
         <v>573</v>
-      </c>
-      <c r="E107" t="s">
-        <v>574</v>
       </c>
       <c r="F107">
         <v>0</v>
@@ -6339,10 +6339,10 @@
         <v>1</v>
       </c>
       <c r="L107" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="108" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="108" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>372</v>
       </c>
@@ -6350,13 +6350,13 @@
         <v>389</v>
       </c>
       <c r="C108" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="D108" t="s">
+        <v>572</v>
+      </c>
+      <c r="E108" t="s">
         <v>573</v>
-      </c>
-      <c r="E108" t="s">
-        <v>574</v>
       </c>
       <c r="F108">
         <v>1</v>
@@ -6377,24 +6377,24 @@
         <v>0</v>
       </c>
       <c r="L108" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="109" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="109" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>372</v>
       </c>
       <c r="B109" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C109" t="s">
-        <v>392</v>
+        <v>583</v>
       </c>
       <c r="D109" t="s">
+        <v>572</v>
+      </c>
+      <c r="E109" t="s">
         <v>573</v>
-      </c>
-      <c r="E109" t="s">
-        <v>574</v>
       </c>
       <c r="F109">
         <v>0</v>
@@ -6415,24 +6415,24 @@
         <v>0</v>
       </c>
       <c r="L109" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="110" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="110" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>372</v>
       </c>
       <c r="B110" t="s">
+        <v>392</v>
+      </c>
+      <c r="C110" t="s">
         <v>393</v>
       </c>
-      <c r="C110" t="s">
-        <v>394</v>
-      </c>
       <c r="D110" t="s">
+        <v>572</v>
+      </c>
+      <c r="E110" t="s">
         <v>573</v>
-      </c>
-      <c r="E110" t="s">
-        <v>574</v>
       </c>
       <c r="F110">
         <v>1</v>
@@ -6453,24 +6453,24 @@
         <v>0</v>
       </c>
       <c r="L110" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="111" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="111" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>372</v>
       </c>
       <c r="B111" t="s">
+        <v>394</v>
+      </c>
+      <c r="C111" t="s">
         <v>395</v>
       </c>
-      <c r="C111" t="s">
-        <v>396</v>
-      </c>
       <c r="D111" t="s">
+        <v>572</v>
+      </c>
+      <c r="E111" t="s">
         <v>573</v>
-      </c>
-      <c r="E111" t="s">
-        <v>574</v>
       </c>
       <c r="F111">
         <v>0</v>
@@ -6491,24 +6491,24 @@
         <v>0</v>
       </c>
       <c r="L111" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="112" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="112" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>372</v>
       </c>
       <c r="B112" t="s">
+        <v>396</v>
+      </c>
+      <c r="C112" t="s">
         <v>397</v>
       </c>
-      <c r="C112" t="s">
-        <v>398</v>
-      </c>
       <c r="D112" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="E112" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="F112">
         <v>0</v>
@@ -6529,24 +6529,24 @@
         <v>0</v>
       </c>
       <c r="L112" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="113" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="113" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>372</v>
       </c>
       <c r="B113" t="s">
+        <v>398</v>
+      </c>
+      <c r="C113" t="s">
         <v>399</v>
       </c>
-      <c r="C113" t="s">
-        <v>400</v>
-      </c>
       <c r="D113" t="s">
+        <v>572</v>
+      </c>
+      <c r="E113" t="s">
         <v>573</v>
-      </c>
-      <c r="E113" t="s">
-        <v>574</v>
       </c>
       <c r="F113">
         <v>1</v>
@@ -6567,24 +6567,24 @@
         <v>0</v>
       </c>
       <c r="L113" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="114" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="114" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>372</v>
       </c>
       <c r="B114" t="s">
+        <v>400</v>
+      </c>
+      <c r="C114" t="s">
         <v>401</v>
       </c>
-      <c r="C114" t="s">
-        <v>402</v>
-      </c>
       <c r="D114" t="s">
+        <v>572</v>
+      </c>
+      <c r="E114" t="s">
         <v>573</v>
-      </c>
-      <c r="E114" t="s">
-        <v>574</v>
       </c>
       <c r="F114">
         <v>0</v>
@@ -6605,7 +6605,7 @@
         <v>0</v>
       </c>
       <c r="L114" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="115" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -6613,16 +6613,16 @@
         <v>372</v>
       </c>
       <c r="B115" t="s">
+        <v>402</v>
+      </c>
+      <c r="C115" t="s">
         <v>403</v>
       </c>
-      <c r="C115" t="s">
-        <v>404</v>
-      </c>
       <c r="D115" t="s">
+        <v>572</v>
+      </c>
+      <c r="E115" t="s">
         <v>573</v>
-      </c>
-      <c r="E115" t="s">
-        <v>574</v>
       </c>
       <c r="F115">
         <v>1</v>
@@ -6643,24 +6643,24 @@
         <v>0</v>
       </c>
       <c r="L115" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="116" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="116" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>372</v>
       </c>
       <c r="B116" t="s">
+        <v>404</v>
+      </c>
+      <c r="C116" t="s">
         <v>405</v>
       </c>
-      <c r="C116" t="s">
-        <v>406</v>
-      </c>
       <c r="D116" t="s">
+        <v>572</v>
+      </c>
+      <c r="E116" t="s">
         <v>573</v>
-      </c>
-      <c r="E116" t="s">
-        <v>574</v>
       </c>
       <c r="F116">
         <v>0</v>
@@ -6681,24 +6681,24 @@
         <v>1</v>
       </c>
       <c r="L116" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="117" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="117" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>372</v>
       </c>
       <c r="B117" t="s">
+        <v>406</v>
+      </c>
+      <c r="C117" t="s">
         <v>407</v>
       </c>
-      <c r="C117" t="s">
-        <v>408</v>
-      </c>
       <c r="D117" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="E117" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="F117">
         <v>1</v>
@@ -6719,24 +6719,24 @@
         <v>1</v>
       </c>
       <c r="L117" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="118" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="118" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>372</v>
       </c>
       <c r="B118" t="s">
+        <v>408</v>
+      </c>
+      <c r="C118" t="s">
         <v>409</v>
       </c>
-      <c r="C118" t="s">
-        <v>410</v>
-      </c>
       <c r="D118" t="s">
+        <v>572</v>
+      </c>
+      <c r="E118" t="s">
         <v>573</v>
-      </c>
-      <c r="E118" t="s">
-        <v>574</v>
       </c>
       <c r="F118">
         <v>0</v>
@@ -6757,24 +6757,24 @@
         <v>0</v>
       </c>
       <c r="L118" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="119" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="119" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>372</v>
       </c>
       <c r="B119" t="s">
+        <v>410</v>
+      </c>
+      <c r="C119" t="s">
         <v>411</v>
       </c>
-      <c r="C119" t="s">
-        <v>412</v>
-      </c>
       <c r="D119" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="E119" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="F119">
         <v>1</v>
@@ -6795,24 +6795,24 @@
         <v>1</v>
       </c>
       <c r="L119" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="120" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="120" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>372</v>
       </c>
       <c r="B120" t="s">
+        <v>412</v>
+      </c>
+      <c r="C120" t="s">
         <v>413</v>
       </c>
-      <c r="C120" t="s">
-        <v>414</v>
-      </c>
       <c r="D120" t="s">
+        <v>572</v>
+      </c>
+      <c r="E120" t="s">
         <v>573</v>
-      </c>
-      <c r="E120" t="s">
-        <v>574</v>
       </c>
       <c r="F120">
         <v>0</v>
@@ -6833,24 +6833,24 @@
         <v>0</v>
       </c>
       <c r="L120" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="121" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="121" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>372</v>
       </c>
       <c r="B121" t="s">
+        <v>414</v>
+      </c>
+      <c r="C121" t="s">
         <v>415</v>
       </c>
-      <c r="C121" t="s">
-        <v>416</v>
-      </c>
       <c r="D121" t="s">
+        <v>572</v>
+      </c>
+      <c r="E121" t="s">
         <v>573</v>
-      </c>
-      <c r="E121" t="s">
-        <v>574</v>
       </c>
       <c r="F121">
         <v>0</v>
@@ -6871,24 +6871,24 @@
         <v>1</v>
       </c>
       <c r="L121" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="122" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="122" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>372</v>
       </c>
       <c r="B122" t="s">
+        <v>416</v>
+      </c>
+      <c r="C122" t="s">
         <v>417</v>
       </c>
-      <c r="C122" t="s">
-        <v>418</v>
-      </c>
       <c r="D122" t="s">
+        <v>572</v>
+      </c>
+      <c r="E122" t="s">
         <v>573</v>
-      </c>
-      <c r="E122" t="s">
-        <v>574</v>
       </c>
       <c r="F122">
         <v>0</v>
@@ -6909,24 +6909,24 @@
         <v>0</v>
       </c>
       <c r="L122" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="123" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="123" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>372</v>
       </c>
       <c r="B123" t="s">
+        <v>418</v>
+      </c>
+      <c r="C123" t="s">
         <v>419</v>
       </c>
-      <c r="C123" t="s">
-        <v>420</v>
-      </c>
       <c r="D123" t="s">
+        <v>572</v>
+      </c>
+      <c r="E123" t="s">
         <v>573</v>
-      </c>
-      <c r="E123" t="s">
-        <v>574</v>
       </c>
       <c r="F123">
         <v>0</v>
@@ -6947,24 +6947,24 @@
         <v>0</v>
       </c>
       <c r="L123" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="124" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="124" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>372</v>
       </c>
       <c r="B124" t="s">
+        <v>420</v>
+      </c>
+      <c r="C124" t="s">
         <v>421</v>
       </c>
-      <c r="C124" t="s">
-        <v>422</v>
-      </c>
       <c r="D124" t="s">
+        <v>572</v>
+      </c>
+      <c r="E124" t="s">
         <v>573</v>
-      </c>
-      <c r="E124" t="s">
-        <v>574</v>
       </c>
       <c r="F124">
         <v>0</v>
@@ -6985,24 +6985,24 @@
         <v>0</v>
       </c>
       <c r="L124" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="125" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="125" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>372</v>
       </c>
       <c r="B125" t="s">
+        <v>422</v>
+      </c>
+      <c r="C125" t="s">
         <v>423</v>
       </c>
-      <c r="C125" t="s">
-        <v>424</v>
-      </c>
       <c r="D125" t="s">
+        <v>572</v>
+      </c>
+      <c r="E125" t="s">
         <v>573</v>
-      </c>
-      <c r="E125" t="s">
-        <v>574</v>
       </c>
       <c r="F125">
         <v>1</v>
@@ -7023,24 +7023,24 @@
         <v>0</v>
       </c>
       <c r="L125" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="126" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="126" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>372</v>
       </c>
       <c r="B126" t="s">
+        <v>424</v>
+      </c>
+      <c r="C126" t="s">
         <v>425</v>
       </c>
-      <c r="C126" t="s">
-        <v>426</v>
-      </c>
       <c r="D126" t="s">
+        <v>572</v>
+      </c>
+      <c r="E126" t="s">
         <v>573</v>
-      </c>
-      <c r="E126" t="s">
-        <v>574</v>
       </c>
       <c r="F126">
         <v>0</v>
@@ -7061,24 +7061,24 @@
         <v>0</v>
       </c>
       <c r="L126" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="127" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="127" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>372</v>
       </c>
       <c r="B127" t="s">
+        <v>426</v>
+      </c>
+      <c r="C127" t="s">
         <v>427</v>
       </c>
-      <c r="C127" t="s">
-        <v>428</v>
-      </c>
       <c r="D127" t="s">
+        <v>572</v>
+      </c>
+      <c r="E127" t="s">
         <v>573</v>
-      </c>
-      <c r="E127" t="s">
-        <v>574</v>
       </c>
       <c r="F127">
         <v>0</v>
@@ -7099,24 +7099,24 @@
         <v>0</v>
       </c>
       <c r="L127" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="128" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="128" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>372</v>
       </c>
       <c r="B128" t="s">
+        <v>428</v>
+      </c>
+      <c r="C128" t="s">
         <v>429</v>
       </c>
-      <c r="C128" t="s">
-        <v>430</v>
-      </c>
       <c r="D128" t="s">
+        <v>572</v>
+      </c>
+      <c r="E128" t="s">
         <v>573</v>
-      </c>
-      <c r="E128" t="s">
-        <v>574</v>
       </c>
       <c r="F128">
         <v>0</v>
@@ -7137,24 +7137,24 @@
         <v>0</v>
       </c>
       <c r="L128" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="129" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="129" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>372</v>
       </c>
       <c r="B129" t="s">
+        <v>430</v>
+      </c>
+      <c r="C129" t="s">
         <v>431</v>
       </c>
-      <c r="C129" t="s">
-        <v>432</v>
-      </c>
       <c r="D129" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="E129" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="F129">
         <v>1</v>
@@ -7175,25 +7175,25 @@
         <v>0</v>
       </c>
       <c r="L129" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="130" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="130" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>372</v>
       </c>
       <c r="B130" t="s">
+        <v>432</v>
+      </c>
+      <c r="C130" t="s">
         <v>433</v>
       </c>
-      <c r="C130" t="s">
-        <v>434</v>
-      </c>
       <c r="D130" t="s">
+        <v>572</v>
+      </c>
+      <c r="E130" t="s">
         <v>573</v>
       </c>
-      <c r="E130" t="s">
-        <v>574</v>
-      </c>
       <c r="F130">
         <v>1</v>
       </c>
@@ -7213,24 +7213,24 @@
         <v>1</v>
       </c>
       <c r="L130" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="131" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="131" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>372</v>
       </c>
       <c r="B131" t="s">
+        <v>434</v>
+      </c>
+      <c r="C131" t="s">
         <v>435</v>
       </c>
-      <c r="C131" t="s">
-        <v>436</v>
-      </c>
       <c r="D131" t="s">
+        <v>572</v>
+      </c>
+      <c r="E131" t="s">
         <v>573</v>
-      </c>
-      <c r="E131" t="s">
-        <v>574</v>
       </c>
       <c r="F131">
         <v>0</v>
@@ -7251,24 +7251,24 @@
         <v>1</v>
       </c>
       <c r="L131" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="132" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="132" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>372</v>
       </c>
       <c r="B132" t="s">
+        <v>436</v>
+      </c>
+      <c r="C132" t="s">
         <v>437</v>
       </c>
-      <c r="C132" t="s">
-        <v>438</v>
-      </c>
       <c r="D132" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="E132" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="F132">
         <v>1</v>
@@ -7289,24 +7289,24 @@
         <v>1</v>
       </c>
       <c r="L132" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="133" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="133" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>372</v>
       </c>
       <c r="B133" t="s">
+        <v>438</v>
+      </c>
+      <c r="C133" t="s">
         <v>439</v>
       </c>
-      <c r="C133" t="s">
-        <v>440</v>
-      </c>
       <c r="D133" t="s">
+        <v>572</v>
+      </c>
+      <c r="E133" t="s">
         <v>573</v>
-      </c>
-      <c r="E133" t="s">
-        <v>574</v>
       </c>
       <c r="F133">
         <v>0</v>
@@ -7327,7 +7327,7 @@
         <v>0</v>
       </c>
       <c r="L133" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="134" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -7335,16 +7335,16 @@
         <v>372</v>
       </c>
       <c r="B134" t="s">
+        <v>440</v>
+      </c>
+      <c r="C134" t="s">
         <v>441</v>
       </c>
-      <c r="C134" t="s">
-        <v>442</v>
-      </c>
       <c r="D134" t="s">
+        <v>572</v>
+      </c>
+      <c r="E134" t="s">
         <v>573</v>
-      </c>
-      <c r="E134" t="s">
-        <v>574</v>
       </c>
       <c r="F134">
         <v>1</v>
@@ -7365,24 +7365,24 @@
         <v>0</v>
       </c>
       <c r="L134" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="135" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="135" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>372</v>
       </c>
       <c r="B135" t="s">
+        <v>442</v>
+      </c>
+      <c r="C135" t="s">
         <v>443</v>
       </c>
-      <c r="C135" t="s">
-        <v>444</v>
-      </c>
       <c r="D135" t="s">
+        <v>572</v>
+      </c>
+      <c r="E135" t="s">
         <v>573</v>
-      </c>
-      <c r="E135" t="s">
-        <v>574</v>
       </c>
       <c r="F135">
         <v>0</v>
@@ -7403,7 +7403,7 @@
         <v>0</v>
       </c>
       <c r="L135" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="136" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
@@ -7411,16 +7411,16 @@
         <v>372</v>
       </c>
       <c r="B136" t="s">
+        <v>444</v>
+      </c>
+      <c r="C136" t="s">
         <v>445</v>
       </c>
-      <c r="C136" t="s">
-        <v>446</v>
-      </c>
       <c r="D136" t="s">
+        <v>572</v>
+      </c>
+      <c r="E136" t="s">
         <v>573</v>
-      </c>
-      <c r="E136" t="s">
-        <v>574</v>
       </c>
       <c r="F136">
         <v>0</v>
@@ -7441,24 +7441,24 @@
         <v>1</v>
       </c>
       <c r="L136" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="137" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="137" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>372</v>
       </c>
       <c r="B137" t="s">
+        <v>446</v>
+      </c>
+      <c r="C137" t="s">
         <v>447</v>
       </c>
-      <c r="C137" t="s">
-        <v>448</v>
-      </c>
       <c r="D137" t="s">
+        <v>572</v>
+      </c>
+      <c r="E137" t="s">
         <v>573</v>
-      </c>
-      <c r="E137" t="s">
-        <v>574</v>
       </c>
       <c r="F137">
         <v>1</v>
@@ -7479,24 +7479,24 @@
         <v>0</v>
       </c>
       <c r="L137" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="138" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="138" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>372</v>
       </c>
       <c r="B138" t="s">
+        <v>448</v>
+      </c>
+      <c r="C138" t="s">
         <v>449</v>
       </c>
-      <c r="C138" t="s">
-        <v>450</v>
-      </c>
       <c r="D138" t="s">
+        <v>572</v>
+      </c>
+      <c r="E138" t="s">
         <v>573</v>
-      </c>
-      <c r="E138" t="s">
-        <v>574</v>
       </c>
       <c r="F138">
         <v>0</v>
@@ -7517,24 +7517,24 @@
         <v>0</v>
       </c>
       <c r="L138" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="139" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B139" t="s">
+        <v>525</v>
+      </c>
+      <c r="C139" t="s">
         <v>526</v>
       </c>
-      <c r="C139" t="s">
-        <v>527</v>
-      </c>
       <c r="D139" t="s">
+        <v>572</v>
+      </c>
+      <c r="E139" t="s">
         <v>573</v>
-      </c>
-      <c r="E139" t="s">
-        <v>574</v>
       </c>
       <c r="F139">
         <v>0</v>
@@ -7555,24 +7555,24 @@
         <v>1</v>
       </c>
       <c r="L139" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="140" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B140" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="C140" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="D140" t="s">
+        <v>572</v>
+      </c>
+      <c r="E140" t="s">
         <v>573</v>
-      </c>
-      <c r="E140" t="s">
-        <v>574</v>
       </c>
       <c r="F140">
         <v>0</v>
@@ -7593,24 +7593,24 @@
         <v>0</v>
       </c>
       <c r="L140" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="141" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B141" t="s">
+        <v>532</v>
+      </c>
+      <c r="C141" t="s">
         <v>533</v>
       </c>
-      <c r="C141" t="s">
-        <v>534</v>
-      </c>
       <c r="D141" t="s">
+        <v>572</v>
+      </c>
+      <c r="E141" t="s">
         <v>573</v>
-      </c>
-      <c r="E141" t="s">
-        <v>574</v>
       </c>
       <c r="F141">
         <v>0</v>
@@ -7631,24 +7631,24 @@
         <v>1</v>
       </c>
       <c r="L141" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="142" spans="1:12" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B142" t="s">
+        <v>541</v>
+      </c>
+      <c r="C142" t="s">
         <v>542</v>
       </c>
-      <c r="C142" t="s">
-        <v>543</v>
-      </c>
       <c r="D142" t="s">
+        <v>572</v>
+      </c>
+      <c r="E142" t="s">
         <v>573</v>
-      </c>
-      <c r="E142" t="s">
-        <v>574</v>
       </c>
       <c r="F142">
         <v>1</v>
@@ -7669,15 +7669,24 @@
         <v>1</v>
       </c>
       <c r="L142" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:L142">
     <filterColumn colId="0">
       <filters>
-        <filter val="Amfibieën"/>
-        <filter val="Reptielen"/>
+        <filter val="Vogels"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="9">
+      <filters>
+        <filter val="1"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="11">
+      <filters>
+        <filter val="ja"/>
       </filters>
     </filterColumn>
     <sortState ref="A2:L277">
@@ -7781,57 +7790,57 @@
     </row>
     <row r="9" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>407</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>408</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>411</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>431</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>432</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>433</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>434</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>437</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>438</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -9200,7 +9209,7 @@
         <v>372</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="C139" s="8"/>
     </row>
@@ -9209,7 +9218,7 @@
         <v>372</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C140" s="8"/>
     </row>
@@ -9218,7 +9227,7 @@
         <v>372</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C141" s="8"/>
     </row>
@@ -9227,7 +9236,7 @@
         <v>372</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C142" s="8"/>
     </row>
@@ -9236,280 +9245,280 @@
         <v>372</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C143" s="8"/>
     </row>
     <row r="144" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A144" s="2" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C144" s="8"/>
     </row>
     <row r="145" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A145" s="2" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B145" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="C145" s="2" t="s">
         <v>512</v>
-      </c>
-      <c r="C145" s="2" t="s">
-        <v>513</v>
       </c>
     </row>
     <row r="146" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A146" s="2" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B146" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="C146" s="2" t="s">
         <v>476</v>
-      </c>
-      <c r="C146" s="2" t="s">
-        <v>477</v>
       </c>
     </row>
     <row r="147" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A147" s="2" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B147" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="C147" s="2" t="s">
         <v>458</v>
-      </c>
-      <c r="C147" s="2" t="s">
-        <v>459</v>
       </c>
     </row>
     <row r="148" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A148" s="2" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B148" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="C148" s="2" t="s">
         <v>506</v>
-      </c>
-      <c r="C148" s="2" t="s">
-        <v>507</v>
       </c>
     </row>
     <row r="149" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A149" s="2" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B149" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="C149" s="2" t="s">
         <v>468</v>
-      </c>
-      <c r="C149" s="2" t="s">
-        <v>469</v>
       </c>
     </row>
     <row r="150" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A150" s="2" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B150" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="C150" s="2" t="s">
         <v>508</v>
-      </c>
-      <c r="C150" s="2" t="s">
-        <v>509</v>
       </c>
     </row>
     <row r="151" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A151" s="2" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B151" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="C151" s="2" t="s">
         <v>478</v>
-      </c>
-      <c r="C151" s="2" t="s">
-        <v>479</v>
       </c>
     </row>
     <row r="152" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A152" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="B152" s="2" t="s">
         <v>451</v>
       </c>
-      <c r="B152" s="2" t="s">
+      <c r="C152" s="2" t="s">
         <v>452</v>
-      </c>
-      <c r="C152" s="2" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="153" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A153" s="2" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B153" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="C153" s="2" t="s">
         <v>492</v>
-      </c>
-      <c r="C153" s="2" t="s">
-        <v>493</v>
       </c>
     </row>
     <row r="154" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A154" s="2" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B154" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="C154" s="2" t="s">
         <v>494</v>
-      </c>
-      <c r="C154" s="2" t="s">
-        <v>495</v>
       </c>
     </row>
     <row r="155" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A155" s="2" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B155" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="C155" s="2" t="s">
         <v>486</v>
-      </c>
-      <c r="C155" s="2" t="s">
-        <v>487</v>
       </c>
     </row>
     <row r="156" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A156" s="2" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B156" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="C156" s="2" t="s">
         <v>510</v>
-      </c>
-      <c r="C156" s="2" t="s">
-        <v>511</v>
       </c>
     </row>
     <row r="157" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A157" s="2" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B157" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="C157" s="2" t="s">
         <v>482</v>
-      </c>
-      <c r="C157" s="2" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="158" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A158" s="2" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B158" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="C158" s="2" t="s">
         <v>460</v>
-      </c>
-      <c r="C158" s="2" t="s">
-        <v>461</v>
       </c>
     </row>
     <row r="159" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A159" s="2" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B159" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="C159" s="2" t="s">
         <v>516</v>
-      </c>
-      <c r="C159" s="2" t="s">
-        <v>517</v>
       </c>
     </row>
     <row r="160" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A160" s="2" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B160" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="C160" s="2" t="s">
         <v>474</v>
-      </c>
-      <c r="C160" s="2" t="s">
-        <v>475</v>
       </c>
     </row>
     <row r="161" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A161" s="2" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B161" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="C161" s="2" t="s">
         <v>518</v>
-      </c>
-      <c r="C161" s="2" t="s">
-        <v>519</v>
       </c>
     </row>
     <row r="162" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A162" s="2" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B162" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="C162" s="2" t="s">
         <v>472</v>
-      </c>
-      <c r="C162" s="2" t="s">
-        <v>473</v>
       </c>
     </row>
     <row r="163" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A163" s="2" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C163" s="8"/>
     </row>
     <row r="164" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A164" s="2" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C164" s="8"/>
     </row>
     <row r="165" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A165" s="2" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C165" s="8"/>
     </row>
     <row r="166" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A166" s="2" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="C166" s="8"/>
     </row>
     <row r="167" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A167" s="2" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C167" s="8"/>
     </row>
     <row r="168" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A168" s="2" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="C168" s="8"/>
     </row>
     <row r="169" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A169" s="2" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B169" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="C169" s="2" t="s">
         <v>542</v>
-      </c>
-      <c r="C169" s="2" t="s">
-        <v>543</v>
       </c>
     </row>
     <row r="170" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -13683,7 +13692,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="42" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -13694,7 +13703,7 @@
     </row>
     <row r="2" spans="1:3" ht="55.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>18</v>
@@ -13732,7 +13741,7 @@
     </row>
     <row r="6" spans="1:3" ht="42" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>385</v>
@@ -13743,68 +13752,68 @@
     </row>
     <row r="7" spans="1:3" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>405</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>406</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>407</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>408</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>411</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>415</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>433</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>434</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>437</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>438</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -13944,7 +13953,7 @@
         <v>48</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="C25" s="9"/>
     </row>
@@ -15139,7 +15148,7 @@
         <v>372</v>
       </c>
       <c r="B134" s="6" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C134" s="9"/>
     </row>
@@ -15148,7 +15157,7 @@
         <v>372</v>
       </c>
       <c r="B135" s="6" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C135" s="9"/>
     </row>
@@ -15157,368 +15166,368 @@
         <v>372</v>
       </c>
       <c r="B136" s="6" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C136" s="9"/>
     </row>
     <row r="137" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A137" s="5" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B137" s="6" t="s">
+        <v>511</v>
+      </c>
+      <c r="C137" s="6" t="s">
         <v>512</v>
-      </c>
-      <c r="C137" s="6" t="s">
-        <v>513</v>
       </c>
     </row>
     <row r="138" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A138" s="5" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B138" s="6" t="s">
+        <v>499</v>
+      </c>
+      <c r="C138" s="6" t="s">
         <v>500</v>
-      </c>
-      <c r="C138" s="6" t="s">
-        <v>501</v>
       </c>
     </row>
     <row r="139" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A139" s="5" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B139" s="6" t="s">
+        <v>475</v>
+      </c>
+      <c r="C139" s="6" t="s">
         <v>476</v>
-      </c>
-      <c r="C139" s="6" t="s">
-        <v>477</v>
       </c>
     </row>
     <row r="140" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A140" s="5" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B140" s="6" t="s">
+        <v>455</v>
+      </c>
+      <c r="C140" s="6" t="s">
         <v>456</v>
-      </c>
-      <c r="C140" s="6" t="s">
-        <v>457</v>
       </c>
     </row>
     <row r="141" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A141" s="5" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B141" s="6" t="s">
+        <v>453</v>
+      </c>
+      <c r="C141" s="6" t="s">
         <v>454</v>
-      </c>
-      <c r="C141" s="6" t="s">
-        <v>455</v>
       </c>
     </row>
     <row r="142" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A142" s="5" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B142" s="6" t="s">
+        <v>497</v>
+      </c>
+      <c r="C142" s="6" t="s">
         <v>498</v>
-      </c>
-      <c r="C142" s="6" t="s">
-        <v>499</v>
       </c>
     </row>
     <row r="143" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A143" s="5" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B143" s="6" t="s">
+        <v>521</v>
+      </c>
+      <c r="C143" s="6" t="s">
         <v>522</v>
-      </c>
-      <c r="C143" s="6" t="s">
-        <v>523</v>
       </c>
     </row>
     <row r="144" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A144" s="5" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B144" s="6" t="s">
+        <v>505</v>
+      </c>
+      <c r="C144" s="6" t="s">
         <v>506</v>
-      </c>
-      <c r="C144" s="6" t="s">
-        <v>507</v>
       </c>
     </row>
     <row r="145" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A145" s="5" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B145" s="6" t="s">
+        <v>467</v>
+      </c>
+      <c r="C145" s="6" t="s">
         <v>468</v>
-      </c>
-      <c r="C145" s="6" t="s">
-        <v>469</v>
       </c>
     </row>
     <row r="146" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A146" s="5" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B146" s="6" t="s">
+        <v>465</v>
+      </c>
+      <c r="C146" s="6" t="s">
         <v>466</v>
-      </c>
-      <c r="C146" s="6" t="s">
-        <v>467</v>
       </c>
     </row>
     <row r="147" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A147" s="5" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B147" s="6" t="s">
+        <v>507</v>
+      </c>
+      <c r="C147" s="6" t="s">
         <v>508</v>
-      </c>
-      <c r="C147" s="6" t="s">
-        <v>509</v>
       </c>
     </row>
     <row r="148" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A148" s="5" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B148" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="C148" s="6" t="s">
         <v>480</v>
-      </c>
-      <c r="C148" s="6" t="s">
-        <v>481</v>
       </c>
     </row>
     <row r="149" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A149" s="5" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B149" s="6" t="s">
+        <v>477</v>
+      </c>
+      <c r="C149" s="6" t="s">
         <v>478</v>
-      </c>
-      <c r="C149" s="6" t="s">
-        <v>479</v>
       </c>
     </row>
     <row r="150" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A150" s="5" t="s">
+        <v>450</v>
+      </c>
+      <c r="B150" s="6" t="s">
         <v>451</v>
       </c>
-      <c r="B150" s="6" t="s">
+      <c r="C150" s="6" t="s">
         <v>452</v>
-      </c>
-      <c r="C150" s="6" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="151" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A151" s="5" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B151" s="6" t="s">
+        <v>491</v>
+      </c>
+      <c r="C151" s="6" t="s">
         <v>492</v>
-      </c>
-      <c r="C151" s="6" t="s">
-        <v>493</v>
       </c>
     </row>
     <row r="152" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A152" s="5" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B152" s="6" t="s">
+        <v>481</v>
+      </c>
+      <c r="C152" s="6" t="s">
         <v>482</v>
-      </c>
-      <c r="C152" s="6" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="153" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A153" s="5" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B153" s="6" t="s">
+        <v>513</v>
+      </c>
+      <c r="C153" s="6" t="s">
         <v>514</v>
-      </c>
-      <c r="C153" s="6" t="s">
-        <v>515</v>
       </c>
     </row>
     <row r="154" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A154" s="5" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B154" s="6" t="s">
+        <v>495</v>
+      </c>
+      <c r="C154" s="6" t="s">
         <v>496</v>
-      </c>
-      <c r="C154" s="6" t="s">
-        <v>497</v>
       </c>
     </row>
     <row r="155" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A155" s="5" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B155" s="6" t="s">
+        <v>459</v>
+      </c>
+      <c r="C155" s="6" t="s">
         <v>460</v>
-      </c>
-      <c r="C155" s="6" t="s">
-        <v>461</v>
       </c>
     </row>
     <row r="156" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A156" s="5" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B156" s="6" t="s">
+        <v>489</v>
+      </c>
+      <c r="C156" s="6" t="s">
         <v>490</v>
-      </c>
-      <c r="C156" s="6" t="s">
-        <v>491</v>
       </c>
     </row>
     <row r="157" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A157" s="5" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B157" s="6" t="s">
+        <v>483</v>
+      </c>
+      <c r="C157" s="6" t="s">
         <v>484</v>
-      </c>
-      <c r="C157" s="6" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="158" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A158" s="5" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B158" s="6" t="s">
+        <v>473</v>
+      </c>
+      <c r="C158" s="6" t="s">
         <v>474</v>
-      </c>
-      <c r="C158" s="6" t="s">
-        <v>475</v>
       </c>
     </row>
     <row r="159" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A159" s="5" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B159" s="6" t="s">
+        <v>469</v>
+      </c>
+      <c r="C159" s="6" t="s">
         <v>470</v>
-      </c>
-      <c r="C159" s="6" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="160" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A160" s="5" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B160" s="6" t="s">
+        <v>501</v>
+      </c>
+      <c r="C160" s="6" t="s">
         <v>502</v>
-      </c>
-      <c r="C160" s="6" t="s">
-        <v>503</v>
       </c>
     </row>
     <row r="161" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A161" s="5" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B161" s="6" t="s">
+        <v>461</v>
+      </c>
+      <c r="C161" s="6" t="s">
         <v>462</v>
-      </c>
-      <c r="C161" s="6" t="s">
-        <v>463</v>
       </c>
     </row>
     <row r="162" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A162" s="5" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B162" s="6" t="s">
+        <v>487</v>
+      </c>
+      <c r="C162" s="6" t="s">
         <v>488</v>
-      </c>
-      <c r="C162" s="6" t="s">
-        <v>489</v>
       </c>
     </row>
     <row r="163" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A163" s="5" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B163" s="6" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="C163" s="9"/>
     </row>
     <row r="164" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A164" s="5" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B164" s="6" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="C164" s="9"/>
     </row>
     <row r="165" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A165" s="5" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B165" s="6" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="C165" s="9"/>
     </row>
     <row r="166" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A166" s="5" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B166" s="6" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="C166" s="9"/>
     </row>
     <row r="167" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A167" s="5" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B167" s="6" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="C167" s="9"/>
     </row>
     <row r="168" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A168" s="5" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B168" s="6" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="C168" s="9"/>
     </row>
     <row r="169" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A169" s="5" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B169" s="6" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="C169" s="9"/>
     </row>
     <row r="170" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A170" s="5" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B170" s="6" t="s">
+        <v>541</v>
+      </c>
+      <c r="C170" s="6" t="s">
         <v>542</v>
-      </c>
-      <c r="C170" s="6" t="s">
-        <v>543</v>
       </c>
     </row>
     <row r="171" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -19688,10 +19697,10 @@
   <sheetData>
     <row r="1" spans="1:3" ht="42" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -19784,7 +19793,7 @@
         <v>20</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>24</v>
@@ -20873,10 +20882,10 @@
         <v>372</v>
       </c>
       <c r="B109" s="6" t="s">
+        <v>430</v>
+      </c>
+      <c r="C109" s="6" t="s">
         <v>431</v>
-      </c>
-      <c r="C109" s="6" t="s">
-        <v>432</v>
       </c>
     </row>
     <row r="110" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -20884,10 +20893,10 @@
         <v>372</v>
       </c>
       <c r="B110" s="6" t="s">
+        <v>432</v>
+      </c>
+      <c r="C110" s="6" t="s">
         <v>433</v>
-      </c>
-      <c r="C110" s="6" t="s">
-        <v>434</v>
       </c>
     </row>
     <row r="111" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -20922,7 +20931,7 @@
         <v>372</v>
       </c>
       <c r="B114" s="6" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C114" s="9"/>
     </row>
@@ -20931,7 +20940,7 @@
         <v>372</v>
       </c>
       <c r="B115" s="6" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C115" s="9"/>
     </row>
@@ -20940,7 +20949,7 @@
         <v>372</v>
       </c>
       <c r="B116" s="6" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C116" s="9"/>
     </row>
@@ -20949,7 +20958,7 @@
         <v>372</v>
       </c>
       <c r="B117" s="6" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C117" s="9"/>
     </row>
@@ -20958,7 +20967,7 @@
         <v>372</v>
       </c>
       <c r="B118" s="6" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C118" s="9"/>
     </row>
@@ -20967,7 +20976,7 @@
         <v>372</v>
       </c>
       <c r="B119" s="6" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C119" s="9"/>
     </row>
@@ -20976,215 +20985,215 @@
         <v>372</v>
       </c>
       <c r="B120" s="6" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C120" s="9"/>
     </row>
     <row r="121" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A121" s="5" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B121" s="6" t="s">
+        <v>499</v>
+      </c>
+      <c r="C121" s="6" t="s">
         <v>500</v>
-      </c>
-      <c r="C121" s="6" t="s">
-        <v>501</v>
       </c>
     </row>
     <row r="122" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A122" s="5" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B122" s="6" t="s">
+        <v>475</v>
+      </c>
+      <c r="C122" s="6" t="s">
         <v>476</v>
-      </c>
-      <c r="C122" s="6" t="s">
-        <v>477</v>
       </c>
     </row>
     <row r="123" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A123" s="5" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B123" s="6" t="s">
+        <v>453</v>
+      </c>
+      <c r="C123" s="6" t="s">
         <v>454</v>
-      </c>
-      <c r="C123" s="6" t="s">
-        <v>455</v>
       </c>
     </row>
     <row r="124" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A124" s="5" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B124" s="6" t="s">
+        <v>497</v>
+      </c>
+      <c r="C124" s="6" t="s">
         <v>498</v>
-      </c>
-      <c r="C124" s="6" t="s">
-        <v>499</v>
       </c>
     </row>
     <row r="125" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A125" s="5" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B125" s="6" t="s">
+        <v>505</v>
+      </c>
+      <c r="C125" s="6" t="s">
         <v>506</v>
-      </c>
-      <c r="C125" s="6" t="s">
-        <v>507</v>
       </c>
     </row>
     <row r="126" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A126" s="5" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B126" s="6" t="s">
+        <v>467</v>
+      </c>
+      <c r="C126" s="6" t="s">
         <v>468</v>
-      </c>
-      <c r="C126" s="6" t="s">
-        <v>469</v>
       </c>
     </row>
     <row r="127" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A127" s="5" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B127" s="6" t="s">
+        <v>507</v>
+      </c>
+      <c r="C127" s="6" t="s">
         <v>508</v>
-      </c>
-      <c r="C127" s="6" t="s">
-        <v>509</v>
       </c>
     </row>
     <row r="128" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A128" s="5" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B128" s="6" t="s">
+        <v>477</v>
+      </c>
+      <c r="C128" s="6" t="s">
         <v>478</v>
-      </c>
-      <c r="C128" s="6" t="s">
-        <v>479</v>
       </c>
     </row>
     <row r="129" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A129" s="5" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B129" s="6" t="s">
+        <v>491</v>
+      </c>
+      <c r="C129" s="6" t="s">
         <v>492</v>
-      </c>
-      <c r="C129" s="6" t="s">
-        <v>493</v>
       </c>
     </row>
     <row r="130" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A130" s="5" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B130" s="6" t="s">
+        <v>485</v>
+      </c>
+      <c r="C130" s="6" t="s">
         <v>486</v>
-      </c>
-      <c r="C130" s="6" t="s">
-        <v>487</v>
       </c>
     </row>
     <row r="131" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A131" s="5" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B131" s="6" t="s">
+        <v>509</v>
+      </c>
+      <c r="C131" s="6" t="s">
         <v>510</v>
-      </c>
-      <c r="C131" s="6" t="s">
-        <v>511</v>
       </c>
     </row>
     <row r="132" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A132" s="5" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B132" s="6" t="s">
+        <v>513</v>
+      </c>
+      <c r="C132" s="6" t="s">
         <v>514</v>
-      </c>
-      <c r="C132" s="6" t="s">
-        <v>515</v>
       </c>
     </row>
     <row r="133" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A133" s="5" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B133" s="6" t="s">
+        <v>459</v>
+      </c>
+      <c r="C133" s="6" t="s">
         <v>460</v>
-      </c>
-      <c r="C133" s="6" t="s">
-        <v>461</v>
       </c>
     </row>
     <row r="134" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A134" s="5" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B134" s="6" t="s">
+        <v>473</v>
+      </c>
+      <c r="C134" s="6" t="s">
         <v>474</v>
-      </c>
-      <c r="C134" s="6" t="s">
-        <v>475</v>
       </c>
     </row>
     <row r="135" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A135" s="5" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B135" s="6" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="C135" s="9"/>
     </row>
     <row r="136" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A136" s="5" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B136" s="6" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="C136" s="9"/>
     </row>
     <row r="137" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A137" s="5" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B137" s="6" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="C137" s="9"/>
     </row>
     <row r="138" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A138" s="5" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B138" s="6" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="C138" s="9"/>
     </row>
     <row r="139" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A139" s="5" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B139" s="6" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="C139" s="9"/>
     </row>
     <row r="140" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A140" s="5" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B140" s="6" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="C140" s="9"/>
     </row>
@@ -25505,10 +25514,10 @@
   <sheetData>
     <row r="1" spans="1:3" ht="42" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="10" t="s">
+        <v>562</v>
+      </c>
+      <c r="B1" s="11" t="s">
         <v>563</v>
-      </c>
-      <c r="B1" s="11" t="s">
-        <v>564</v>
       </c>
       <c r="C1" s="11" t="s">
         <v>2</v>
@@ -25516,7 +25525,7 @@
     </row>
     <row r="2" spans="1:3" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>8</v>
@@ -25527,7 +25536,7 @@
     </row>
     <row r="3" spans="1:3" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>10</v>
@@ -25536,7 +25545,7 @@
     </row>
     <row r="4" spans="1:3" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>12</v>
@@ -25545,7 +25554,7 @@
     </row>
     <row r="5" spans="1:3" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>14</v>
@@ -25556,7 +25565,7 @@
     </row>
     <row r="6" spans="1:3" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>16</v>
@@ -25565,7 +25574,7 @@
     </row>
     <row r="7" spans="1:3" ht="55.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>18</v>
@@ -25576,7 +25585,7 @@
     </row>
     <row r="8" spans="1:3" ht="42" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="5" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>385</v>
@@ -25587,79 +25596,79 @@
     </row>
     <row r="9" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="5" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B9" s="6" t="s">
+        <v>404</v>
+      </c>
+      <c r="C9" s="6" t="s">
         <v>405</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>406</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="5" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B10" s="6" t="s">
+        <v>406</v>
+      </c>
+      <c r="C10" s="6" t="s">
         <v>407</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>408</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="5" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B11" s="6" t="s">
+        <v>410</v>
+      </c>
+      <c r="C11" s="6" t="s">
         <v>411</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="5" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B12" s="6" t="s">
+        <v>414</v>
+      </c>
+      <c r="C12" s="6" t="s">
         <v>415</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="5" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B13" s="6" t="s">
+        <v>430</v>
+      </c>
+      <c r="C13" s="6" t="s">
         <v>431</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>432</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="5" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B14" s="6" t="s">
+        <v>432</v>
+      </c>
+      <c r="C14" s="6" t="s">
         <v>433</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>434</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="5" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B15" s="6" t="s">
+        <v>436</v>
+      </c>
+      <c r="C15" s="6" t="s">
         <v>437</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>438</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -26809,7 +26818,7 @@
         <v>244</v>
       </c>
       <c r="B120" s="6" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="C120" s="6" t="s">
         <v>266</v>
@@ -27183,7 +27192,7 @@
         <v>363</v>
       </c>
       <c r="B154" s="6" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="C154" s="9"/>
     </row>
@@ -27228,7 +27237,7 @@
         <v>372</v>
       </c>
       <c r="B159" s="6" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C159" s="9"/>
     </row>
@@ -27237,7 +27246,7 @@
         <v>372</v>
       </c>
       <c r="B160" s="6" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C160" s="9"/>
     </row>
@@ -27246,380 +27255,380 @@
         <v>372</v>
       </c>
       <c r="B161" s="6" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C161" s="9"/>
     </row>
     <row r="162" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A162" s="5" t="s">
+        <v>450</v>
+      </c>
+      <c r="B162" s="6" t="s">
         <v>451</v>
       </c>
-      <c r="B162" s="6" t="s">
+      <c r="C162" s="6" t="s">
         <v>452</v>
-      </c>
-      <c r="C162" s="6" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="163" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A163" s="5" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B163" s="6" t="s">
+        <v>453</v>
+      </c>
+      <c r="C163" s="6" t="s">
         <v>454</v>
-      </c>
-      <c r="C163" s="6" t="s">
-        <v>455</v>
       </c>
     </row>
     <row r="164" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A164" s="5" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B164" s="6" t="s">
+        <v>455</v>
+      </c>
+      <c r="C164" s="6" t="s">
         <v>456</v>
-      </c>
-      <c r="C164" s="6" t="s">
-        <v>457</v>
       </c>
     </row>
     <row r="165" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A165" s="5" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B165" s="6" t="s">
+        <v>457</v>
+      </c>
+      <c r="C165" s="6" t="s">
         <v>458</v>
-      </c>
-      <c r="C165" s="6" t="s">
-        <v>459</v>
       </c>
     </row>
     <row r="166" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A166" s="5" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B166" s="6" t="s">
+        <v>459</v>
+      </c>
+      <c r="C166" s="6" t="s">
         <v>460</v>
-      </c>
-      <c r="C166" s="6" t="s">
-        <v>461</v>
       </c>
     </row>
     <row r="167" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A167" s="5" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B167" s="6" t="s">
+        <v>461</v>
+      </c>
+      <c r="C167" s="6" t="s">
         <v>462</v>
-      </c>
-      <c r="C167" s="6" t="s">
-        <v>463</v>
       </c>
     </row>
     <row r="168" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A168" s="5" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B168" s="6" t="s">
+        <v>465</v>
+      </c>
+      <c r="C168" s="6" t="s">
         <v>466</v>
-      </c>
-      <c r="C168" s="6" t="s">
-        <v>467</v>
       </c>
     </row>
     <row r="169" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A169" s="5" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B169" s="6" t="s">
+        <v>467</v>
+      </c>
+      <c r="C169" s="6" t="s">
         <v>468</v>
-      </c>
-      <c r="C169" s="6" t="s">
-        <v>469</v>
       </c>
     </row>
     <row r="170" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A170" s="5" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B170" s="6" t="s">
+        <v>469</v>
+      </c>
+      <c r="C170" s="6" t="s">
         <v>470</v>
-      </c>
-      <c r="C170" s="6" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="171" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A171" s="5" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B171" s="6" t="s">
+        <v>471</v>
+      </c>
+      <c r="C171" s="6" t="s">
         <v>472</v>
-      </c>
-      <c r="C171" s="6" t="s">
-        <v>473</v>
       </c>
     </row>
     <row r="172" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A172" s="5" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B172" s="6" t="s">
+        <v>473</v>
+      </c>
+      <c r="C172" s="6" t="s">
         <v>474</v>
-      </c>
-      <c r="C172" s="6" t="s">
-        <v>475</v>
       </c>
     </row>
     <row r="173" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A173" s="5" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B173" s="6" t="s">
+        <v>475</v>
+      </c>
+      <c r="C173" s="6" t="s">
         <v>476</v>
-      </c>
-      <c r="C173" s="6" t="s">
-        <v>477</v>
       </c>
     </row>
     <row r="174" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A174" s="5" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B174" s="6" t="s">
+        <v>477</v>
+      </c>
+      <c r="C174" s="6" t="s">
         <v>478</v>
-      </c>
-      <c r="C174" s="6" t="s">
-        <v>479</v>
       </c>
     </row>
     <row r="175" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A175" s="5" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B175" s="6" t="s">
+        <v>481</v>
+      </c>
+      <c r="C175" s="6" t="s">
         <v>482</v>
-      </c>
-      <c r="C175" s="6" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="176" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A176" s="5" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B176" s="6" t="s">
+        <v>483</v>
+      </c>
+      <c r="C176" s="6" t="s">
         <v>484</v>
-      </c>
-      <c r="C176" s="6" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="177" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A177" s="5" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B177" s="6" t="s">
+        <v>485</v>
+      </c>
+      <c r="C177" s="6" t="s">
         <v>486</v>
-      </c>
-      <c r="C177" s="6" t="s">
-        <v>487</v>
       </c>
     </row>
     <row r="178" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A178" s="2" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B178" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="C178" s="2" t="s">
         <v>488</v>
-      </c>
-      <c r="C178" s="2" t="s">
-        <v>489</v>
       </c>
     </row>
     <row r="179" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A179" s="2" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B179" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="C179" s="2" t="s">
         <v>490</v>
-      </c>
-      <c r="C179" s="2" t="s">
-        <v>491</v>
       </c>
     </row>
     <row r="180" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A180" s="2" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B180" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="C180" s="2" t="s">
         <v>492</v>
-      </c>
-      <c r="C180" s="2" t="s">
-        <v>493</v>
       </c>
     </row>
     <row r="181" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A181" s="2" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B181" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="C181" s="2" t="s">
         <v>494</v>
-      </c>
-      <c r="C181" s="2" t="s">
-        <v>495</v>
       </c>
     </row>
     <row r="182" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A182" s="2" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B182" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="C182" s="2" t="s">
         <v>496</v>
-      </c>
-      <c r="C182" s="2" t="s">
-        <v>497</v>
       </c>
     </row>
     <row r="183" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A183" s="2" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B183" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="C183" s="2" t="s">
         <v>498</v>
-      </c>
-      <c r="C183" s="2" t="s">
-        <v>499</v>
       </c>
     </row>
     <row r="184" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A184" s="2" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B184" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="C184" s="2" t="s">
         <v>500</v>
-      </c>
-      <c r="C184" s="2" t="s">
-        <v>501</v>
       </c>
     </row>
     <row r="185" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A185" s="2" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B185" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="C185" s="2" t="s">
         <v>502</v>
-      </c>
-      <c r="C185" s="2" t="s">
-        <v>503</v>
       </c>
     </row>
     <row r="186" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A186" s="2" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B186" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="C186" s="2" t="s">
         <v>506</v>
-      </c>
-      <c r="C186" s="2" t="s">
-        <v>507</v>
       </c>
     </row>
     <row r="187" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A187" s="2" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B187" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="C187" s="2" t="s">
         <v>508</v>
-      </c>
-      <c r="C187" s="2" t="s">
-        <v>509</v>
       </c>
     </row>
     <row r="188" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A188" s="2" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B188" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="C188" s="2" t="s">
         <v>510</v>
-      </c>
-      <c r="C188" s="2" t="s">
-        <v>511</v>
       </c>
     </row>
     <row r="189" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A189" s="2" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B189" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="C189" s="2" t="s">
         <v>512</v>
-      </c>
-      <c r="C189" s="2" t="s">
-        <v>513</v>
       </c>
     </row>
     <row r="190" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A190" s="2" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B190" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="C190" s="2" t="s">
         <v>514</v>
-      </c>
-      <c r="C190" s="2" t="s">
-        <v>515</v>
       </c>
     </row>
     <row r="191" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A191" s="2" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B191" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="C191" s="2" t="s">
         <v>516</v>
-      </c>
-      <c r="C191" s="2" t="s">
-        <v>517</v>
       </c>
     </row>
     <row r="192" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A192" s="2" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B192" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="C192" s="2" t="s">
         <v>518</v>
-      </c>
-      <c r="C192" s="2" t="s">
-        <v>519</v>
       </c>
     </row>
     <row r="193" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A193" s="2" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B193" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="C193" s="2" t="s">
         <v>522</v>
-      </c>
-      <c r="C193" s="2" t="s">
-        <v>523</v>
       </c>
     </row>
     <row r="194" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A194" s="2" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C194" s="8"/>
     </row>
     <row r="195" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A195" s="2" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B195" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="C195" s="2" t="s">
         <v>542</v>
-      </c>
-      <c r="C195" s="2" t="s">
-        <v>543</v>
       </c>
     </row>
     <row r="196" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -31664,7 +31673,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="10" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B1" s="11" t="s">
         <v>1</v>
@@ -31719,10 +31728,10 @@
     </row>
     <row r="6" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="5" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="C6" s="9"/>
     </row>
@@ -31821,7 +31830,7 @@
     </row>
     <row r="16" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>6</v>
@@ -31848,10 +31857,10 @@
     </row>
     <row r="19" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="5" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="C19" s="9"/>
     </row>
@@ -32801,13 +32810,13 @@
     </row>
     <row r="106" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A106" s="5" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B106" s="6" t="s">
+        <v>525</v>
+      </c>
+      <c r="C106" s="6" t="s">
         <v>526</v>
-      </c>
-      <c r="C106" s="6" t="s">
-        <v>527</v>
       </c>
     </row>
     <row r="107" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -32823,10 +32832,10 @@
     </row>
     <row r="108" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A108" s="5" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B108" s="6" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C108" s="9"/>
     </row>
@@ -32876,19 +32885,19 @@
     </row>
     <row r="113" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A113" s="5" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B113" s="6" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C113" s="9"/>
     </row>
     <row r="114" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A114" s="5" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B114" s="6" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="C114" s="9"/>
     </row>
@@ -32916,10 +32925,10 @@
     </row>
     <row r="117" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A117" s="5" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B117" s="6" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C117" s="9"/>
     </row>
@@ -33001,7 +33010,7 @@
         <v>372</v>
       </c>
       <c r="B125" s="6" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C125" s="9"/>
     </row>
@@ -33018,13 +33027,13 @@
     </row>
     <row r="127" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A127" s="5" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B127" s="6" t="s">
+        <v>532</v>
+      </c>
+      <c r="C127" s="6" t="s">
         <v>533</v>
-      </c>
-      <c r="C127" s="6" t="s">
-        <v>534</v>
       </c>
     </row>
     <row r="128" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -33051,7 +33060,7 @@
     </row>
     <row r="130" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A130" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B130" s="6" t="s">
         <v>8</v>
@@ -33098,13 +33107,13 @@
         <v>372</v>
       </c>
       <c r="B134" s="6" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="C134" s="9"/>
     </row>
     <row r="135" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A135" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B135" s="6" t="s">
         <v>10</v>
@@ -33127,7 +33136,7 @@
         <v>372</v>
       </c>
       <c r="B137" s="6" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C137" s="9"/>
     </row>
@@ -33188,10 +33197,10 @@
     </row>
     <row r="143" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A143" s="5" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B143" s="6" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C143" s="9"/>
     </row>
@@ -33275,7 +33284,7 @@
         <v>372</v>
       </c>
       <c r="B151" s="6" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C151" s="9"/>
     </row>
@@ -33295,7 +33304,7 @@
         <v>372</v>
       </c>
       <c r="B153" s="6" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C153" s="9"/>
     </row>
@@ -33315,7 +33324,7 @@
         <v>372</v>
       </c>
       <c r="B155" s="6" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C155" s="9"/>
     </row>
@@ -33324,18 +33333,18 @@
         <v>372</v>
       </c>
       <c r="B156" s="6" t="s">
+        <v>404</v>
+      </c>
+      <c r="C156" s="6" t="s">
         <v>405</v>
-      </c>
-      <c r="C156" s="6" t="s">
-        <v>406</v>
       </c>
     </row>
     <row r="157" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A157" s="5" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B157" s="6" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C157" s="9"/>
     </row>
@@ -33399,18 +33408,18 @@
         <v>372</v>
       </c>
       <c r="B163" s="6" t="s">
+        <v>406</v>
+      </c>
+      <c r="C163" s="6" t="s">
         <v>407</v>
-      </c>
-      <c r="C163" s="6" t="s">
-        <v>408</v>
       </c>
     </row>
     <row r="164" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A164" s="5" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B164" s="6" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="C164" s="9"/>
     </row>
@@ -33419,7 +33428,7 @@
         <v>372</v>
       </c>
       <c r="B165" s="6" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C165" s="9"/>
     </row>
@@ -33439,10 +33448,10 @@
         <v>372</v>
       </c>
       <c r="B167" s="6" t="s">
+        <v>410</v>
+      </c>
+      <c r="C167" s="6" t="s">
         <v>411</v>
-      </c>
-      <c r="C167" s="6" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="168" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -33450,7 +33459,7 @@
         <v>372</v>
       </c>
       <c r="B168" s="6" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C168" s="9"/>
     </row>
@@ -33481,10 +33490,10 @@
         <v>372</v>
       </c>
       <c r="B171" s="6" t="s">
+        <v>414</v>
+      </c>
+      <c r="C171" s="6" t="s">
         <v>415</v>
-      </c>
-      <c r="C171" s="6" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="172" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -33492,7 +33501,7 @@
         <v>372</v>
       </c>
       <c r="B172" s="6" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C172" s="9"/>
     </row>
@@ -33509,7 +33518,7 @@
     </row>
     <row r="174" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A174" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B174" s="6" t="s">
         <v>14</v>
@@ -33523,7 +33532,7 @@
         <v>372</v>
       </c>
       <c r="B175" s="6" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C175" s="9"/>
     </row>
@@ -33532,7 +33541,7 @@
         <v>372</v>
       </c>
       <c r="B176" s="6" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C176" s="9"/>
     </row>
@@ -33552,7 +33561,7 @@
         <v>372</v>
       </c>
       <c r="B178" s="6" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C178" s="9"/>
     </row>
@@ -33569,16 +33578,16 @@
     </row>
     <row r="180" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A180" s="5" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B180" s="6" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="C180" s="9"/>
     </row>
     <row r="181" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A181" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B181" s="6" t="s">
         <v>16</v>
@@ -33587,10 +33596,10 @@
     </row>
     <row r="182" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A182" s="5" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B182" s="6" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C182" s="9"/>
     </row>
@@ -33643,7 +33652,7 @@
         <v>372</v>
       </c>
       <c r="B187" s="6" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C187" s="9"/>
     </row>
@@ -33652,7 +33661,7 @@
         <v>372</v>
       </c>
       <c r="B188" s="6" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C188" s="9"/>
     </row>
@@ -33683,7 +33692,7 @@
         <v>372</v>
       </c>
       <c r="B191" s="6" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C191" s="9"/>
     </row>
@@ -33692,10 +33701,10 @@
         <v>372</v>
       </c>
       <c r="B192" s="6" t="s">
+        <v>430</v>
+      </c>
+      <c r="C192" s="6" t="s">
         <v>431</v>
-      </c>
-      <c r="C192" s="6" t="s">
-        <v>432</v>
       </c>
     </row>
     <row r="193" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -33777,7 +33786,7 @@
     </row>
     <row r="200" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A200" s="5" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B200" s="6" t="s">
         <v>18</v>
@@ -33824,381 +33833,381 @@
         <v>372</v>
       </c>
       <c r="B204" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="C204" s="2" t="s">
         <v>433</v>
-      </c>
-      <c r="C204" s="2" t="s">
-        <v>434</v>
       </c>
     </row>
     <row r="205" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A205" s="5" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B205" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="C205" s="2" t="s">
         <v>542</v>
-      </c>
-      <c r="C205" s="2" t="s">
-        <v>543</v>
       </c>
     </row>
     <row r="206" spans="1:3" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A206" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="B206" s="2" t="s">
         <v>451</v>
       </c>
-      <c r="B206" s="2" t="s">
+      <c r="C206" s="2" t="s">
         <v>452</v>
-      </c>
-      <c r="C206" s="2" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="207" spans="1:3" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A207" s="2" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B207" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="C207" s="2" t="s">
         <v>454</v>
-      </c>
-      <c r="C207" s="2" t="s">
-        <v>455</v>
       </c>
     </row>
     <row r="208" spans="1:3" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A208" s="2" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B208" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="C208" s="2" t="s">
         <v>456</v>
-      </c>
-      <c r="C208" s="2" t="s">
-        <v>457</v>
       </c>
     </row>
     <row r="209" spans="1:3" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A209" s="2" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B209" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="C209" s="2" t="s">
         <v>458</v>
-      </c>
-      <c r="C209" s="2" t="s">
-        <v>459</v>
       </c>
     </row>
     <row r="210" spans="1:3" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A210" s="2" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B210" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="C210" s="2" t="s">
         <v>460</v>
-      </c>
-      <c r="C210" s="2" t="s">
-        <v>461</v>
       </c>
     </row>
     <row r="211" spans="1:3" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A211" s="2" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B211" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="C211" s="2" t="s">
         <v>462</v>
-      </c>
-      <c r="C211" s="2" t="s">
-        <v>463</v>
       </c>
     </row>
     <row r="212" spans="1:3" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A212" s="2" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B212" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="C212" s="2" t="s">
         <v>466</v>
-      </c>
-      <c r="C212" s="2" t="s">
-        <v>467</v>
       </c>
     </row>
     <row r="213" spans="1:3" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A213" s="2" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B213" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="C213" s="2" t="s">
         <v>468</v>
-      </c>
-      <c r="C213" s="2" t="s">
-        <v>469</v>
       </c>
     </row>
     <row r="214" spans="1:3" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A214" s="2" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B214" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="C214" s="2" t="s">
         <v>470</v>
-      </c>
-      <c r="C214" s="2" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="215" spans="1:3" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A215" s="2" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B215" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="C215" s="2" t="s">
         <v>472</v>
-      </c>
-      <c r="C215" s="2" t="s">
-        <v>473</v>
       </c>
     </row>
     <row r="216" spans="1:3" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A216" s="2" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B216" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="C216" s="2" t="s">
         <v>474</v>
-      </c>
-      <c r="C216" s="2" t="s">
-        <v>475</v>
       </c>
     </row>
     <row r="217" spans="1:3" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A217" s="2" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B217" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="C217" s="2" t="s">
         <v>476</v>
-      </c>
-      <c r="C217" s="2" t="s">
-        <v>477</v>
       </c>
     </row>
     <row r="218" spans="1:3" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A218" s="2" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B218" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="C218" s="2" t="s">
         <v>478</v>
-      </c>
-      <c r="C218" s="2" t="s">
-        <v>479</v>
       </c>
     </row>
     <row r="219" spans="1:3" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A219" s="2" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B219" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="C219" s="2" t="s">
         <v>482</v>
-      </c>
-      <c r="C219" s="2" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="220" spans="1:3" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A220" s="2" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B220" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="C220" s="2" t="s">
         <v>484</v>
-      </c>
-      <c r="C220" s="2" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="221" spans="1:3" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A221" s="2" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B221" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="C221" s="2" t="s">
         <v>486</v>
-      </c>
-      <c r="C221" s="2" t="s">
-        <v>487</v>
       </c>
     </row>
     <row r="222" spans="1:3" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A222" s="2" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B222" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="C222" s="2" t="s">
         <v>488</v>
-      </c>
-      <c r="C222" s="2" t="s">
-        <v>489</v>
       </c>
     </row>
     <row r="223" spans="1:3" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A223" s="2" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B223" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="C223" s="2" t="s">
         <v>490</v>
-      </c>
-      <c r="C223" s="2" t="s">
-        <v>491</v>
       </c>
     </row>
     <row r="224" spans="1:3" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A224" s="2" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B224" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="C224" s="2" t="s">
         <v>492</v>
-      </c>
-      <c r="C224" s="2" t="s">
-        <v>493</v>
       </c>
     </row>
     <row r="225" spans="1:3" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A225" s="2" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B225" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="C225" s="2" t="s">
         <v>494</v>
-      </c>
-      <c r="C225" s="2" t="s">
-        <v>495</v>
       </c>
     </row>
     <row r="226" spans="1:3" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A226" s="2" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B226" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="C226" s="2" t="s">
         <v>496</v>
-      </c>
-      <c r="C226" s="2" t="s">
-        <v>497</v>
       </c>
     </row>
     <row r="227" spans="1:3" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A227" s="2" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B227" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="C227" s="2" t="s">
         <v>498</v>
-      </c>
-      <c r="C227" s="2" t="s">
-        <v>499</v>
       </c>
     </row>
     <row r="228" spans="1:3" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A228" s="2" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B228" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="C228" s="2" t="s">
         <v>500</v>
-      </c>
-      <c r="C228" s="2" t="s">
-        <v>501</v>
       </c>
     </row>
     <row r="229" spans="1:3" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A229" s="2" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B229" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="C229" s="2" t="s">
         <v>502</v>
-      </c>
-      <c r="C229" s="2" t="s">
-        <v>503</v>
       </c>
     </row>
     <row r="230" spans="1:3" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A230" s="2" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B230" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="C230" s="2" t="s">
         <v>506</v>
-      </c>
-      <c r="C230" s="2" t="s">
-        <v>507</v>
       </c>
     </row>
     <row r="231" spans="1:3" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A231" s="2" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B231" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="C231" s="2" t="s">
         <v>508</v>
-      </c>
-      <c r="C231" s="2" t="s">
-        <v>509</v>
       </c>
     </row>
     <row r="232" spans="1:3" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A232" s="2" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B232" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="C232" s="2" t="s">
         <v>510</v>
-      </c>
-      <c r="C232" s="2" t="s">
-        <v>511</v>
       </c>
     </row>
     <row r="233" spans="1:3" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A233" s="2" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B233" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="C233" s="2" t="s">
         <v>512</v>
-      </c>
-      <c r="C233" s="2" t="s">
-        <v>513</v>
       </c>
     </row>
     <row r="234" spans="1:3" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A234" s="2" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B234" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="C234" s="2" t="s">
         <v>514</v>
-      </c>
-      <c r="C234" s="2" t="s">
-        <v>515</v>
       </c>
     </row>
     <row r="235" spans="1:3" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A235" s="2" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B235" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="C235" s="2" t="s">
         <v>516</v>
-      </c>
-      <c r="C235" s="2" t="s">
-        <v>517</v>
       </c>
     </row>
     <row r="236" spans="1:3" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A236" s="2" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B236" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="C236" s="2" t="s">
         <v>518</v>
-      </c>
-      <c r="C236" s="2" t="s">
-        <v>519</v>
       </c>
     </row>
     <row r="237" spans="1:3" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A237" s="2" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B237" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="C237" s="2" t="s">
         <v>522</v>
-      </c>
-      <c r="C237" s="2" t="s">
-        <v>523</v>
       </c>
     </row>
     <row r="238" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A238" s="2" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="C238" s="8"/>
     </row>
@@ -34229,7 +34238,7 @@
         <v>372</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C241" s="8"/>
     </row>
@@ -34238,10 +34247,10 @@
         <v>372</v>
       </c>
       <c r="B242" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="C242" s="2" t="s">
         <v>437</v>
-      </c>
-      <c r="C242" s="2" t="s">
-        <v>438</v>
       </c>
     </row>
     <row r="243" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -34249,7 +34258,7 @@
         <v>372</v>
       </c>
       <c r="B243" s="2" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C243" s="8"/>
     </row>
@@ -34280,7 +34289,7 @@
         <v>372</v>
       </c>
       <c r="B246" s="2" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C246" s="8"/>
     </row>
@@ -34300,7 +34309,7 @@
         <v>372</v>
       </c>
       <c r="B248" s="2" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C248" s="8"/>
     </row>
@@ -34331,7 +34340,7 @@
         <v>372</v>
       </c>
       <c r="B251" s="2" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="C251" s="8"/>
     </row>
@@ -34340,7 +34349,7 @@
         <v>372</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C252" s="8"/>
     </row>
@@ -38119,7 +38128,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="42" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="10" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B1" s="11" t="s">
         <v>1</v>
@@ -38911,343 +38920,343 @@
     </row>
     <row r="73" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A73" s="12" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B73" s="7" t="s">
+        <v>511</v>
+      </c>
+      <c r="C73" s="7" t="s">
         <v>512</v>
-      </c>
-      <c r="C73" s="7" t="s">
-        <v>513</v>
       </c>
     </row>
     <row r="74" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A74" s="12" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B74" s="7" t="s">
+        <v>499</v>
+      </c>
+      <c r="C74" s="7" t="s">
         <v>500</v>
-      </c>
-      <c r="C74" s="7" t="s">
-        <v>501</v>
       </c>
     </row>
     <row r="75" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A75" s="12" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B75" s="7" t="s">
+        <v>475</v>
+      </c>
+      <c r="C75" s="7" t="s">
         <v>476</v>
-      </c>
-      <c r="C75" s="7" t="s">
-        <v>477</v>
       </c>
     </row>
     <row r="76" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A76" s="12" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B76" s="7" t="s">
+        <v>455</v>
+      </c>
+      <c r="C76" s="7" t="s">
         <v>456</v>
-      </c>
-      <c r="C76" s="7" t="s">
-        <v>457</v>
       </c>
     </row>
     <row r="77" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A77" s="12" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B77" s="7" t="s">
+        <v>453</v>
+      </c>
+      <c r="C77" s="7" t="s">
         <v>454</v>
-      </c>
-      <c r="C77" s="7" t="s">
-        <v>455</v>
       </c>
     </row>
     <row r="78" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A78" s="12" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B78" s="7" t="s">
+        <v>457</v>
+      </c>
+      <c r="C78" s="7" t="s">
         <v>458</v>
-      </c>
-      <c r="C78" s="7" t="s">
-        <v>459</v>
       </c>
     </row>
     <row r="79" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A79" s="12" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B79" s="7" t="s">
+        <v>521</v>
+      </c>
+      <c r="C79" s="7" t="s">
         <v>522</v>
-      </c>
-      <c r="C79" s="7" t="s">
-        <v>523</v>
       </c>
     </row>
     <row r="80" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A80" s="12" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B80" s="7" t="s">
+        <v>505</v>
+      </c>
+      <c r="C80" s="7" t="s">
         <v>506</v>
-      </c>
-      <c r="C80" s="7" t="s">
-        <v>507</v>
       </c>
     </row>
     <row r="81" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A81" s="12" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B81" s="7" t="s">
+        <v>467</v>
+      </c>
+      <c r="C81" s="7" t="s">
         <v>468</v>
-      </c>
-      <c r="C81" s="7" t="s">
-        <v>469</v>
       </c>
     </row>
     <row r="82" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A82" s="12" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B82" s="7" t="s">
+        <v>465</v>
+      </c>
+      <c r="C82" s="7" t="s">
         <v>466</v>
-      </c>
-      <c r="C82" s="7" t="s">
-        <v>467</v>
       </c>
     </row>
     <row r="83" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A83" s="12" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B83" s="7" t="s">
+        <v>507</v>
+      </c>
+      <c r="C83" s="7" t="s">
         <v>508</v>
-      </c>
-      <c r="C83" s="7" t="s">
-        <v>509</v>
       </c>
     </row>
     <row r="84" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A84" s="12" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B84" s="7" t="s">
+        <v>479</v>
+      </c>
+      <c r="C84" s="7" t="s">
         <v>480</v>
-      </c>
-      <c r="C84" s="7" t="s">
-        <v>481</v>
       </c>
     </row>
     <row r="85" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A85" s="12" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B85" s="7" t="s">
+        <v>477</v>
+      </c>
+      <c r="C85" s="7" t="s">
         <v>478</v>
-      </c>
-      <c r="C85" s="7" t="s">
-        <v>479</v>
       </c>
     </row>
     <row r="86" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A86" s="12" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B86" s="7" t="s">
+        <v>519</v>
+      </c>
+      <c r="C86" s="7" t="s">
         <v>520</v>
-      </c>
-      <c r="C86" s="7" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="87" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A87" s="12" t="s">
+        <v>450</v>
+      </c>
+      <c r="B87" s="7" t="s">
         <v>451</v>
       </c>
-      <c r="B87" s="7" t="s">
+      <c r="C87" s="7" t="s">
         <v>452</v>
-      </c>
-      <c r="C87" s="7" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="88" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A88" s="12" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B88" s="7" t="s">
+        <v>493</v>
+      </c>
+      <c r="C88" s="7" t="s">
         <v>494</v>
-      </c>
-      <c r="C88" s="7" t="s">
-        <v>495</v>
       </c>
     </row>
     <row r="89" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A89" s="12" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B89" s="7" t="s">
+        <v>481</v>
+      </c>
+      <c r="C89" s="7" t="s">
         <v>482</v>
-      </c>
-      <c r="C89" s="7" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="90" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A90" s="12" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B90" s="7" t="s">
+        <v>513</v>
+      </c>
+      <c r="C90" s="7" t="s">
         <v>514</v>
-      </c>
-      <c r="C90" s="7" t="s">
-        <v>515</v>
       </c>
     </row>
     <row r="91" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A91" s="12" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B91" s="7" t="s">
+        <v>495</v>
+      </c>
+      <c r="C91" s="7" t="s">
         <v>496</v>
-      </c>
-      <c r="C91" s="7" t="s">
-        <v>497</v>
       </c>
     </row>
     <row r="92" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A92" s="12" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B92" s="7" t="s">
+        <v>515</v>
+      </c>
+      <c r="C92" s="7" t="s">
         <v>516</v>
-      </c>
-      <c r="C92" s="7" t="s">
-        <v>517</v>
       </c>
     </row>
     <row r="93" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A93" s="12" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B93" s="7" t="s">
+        <v>489</v>
+      </c>
+      <c r="C93" s="7" t="s">
         <v>490</v>
-      </c>
-      <c r="C93" s="7" t="s">
-        <v>491</v>
       </c>
     </row>
     <row r="94" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A94" s="12" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B94" s="7" t="s">
+        <v>483</v>
+      </c>
+      <c r="C94" s="7" t="s">
         <v>484</v>
-      </c>
-      <c r="C94" s="7" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="95" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A95" s="12" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B95" s="7" t="s">
+        <v>473</v>
+      </c>
+      <c r="C95" s="7" t="s">
         <v>474</v>
-      </c>
-      <c r="C95" s="7" t="s">
-        <v>475</v>
       </c>
     </row>
     <row r="96" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A96" s="12" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B96" s="7" t="s">
+        <v>469</v>
+      </c>
+      <c r="C96" s="7" t="s">
         <v>470</v>
-      </c>
-      <c r="C96" s="7" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="97" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A97" s="12" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B97" s="7" t="s">
+        <v>501</v>
+      </c>
+      <c r="C97" s="7" t="s">
         <v>502</v>
-      </c>
-      <c r="C97" s="7" t="s">
-        <v>503</v>
       </c>
     </row>
     <row r="98" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A98" s="12" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B98" s="7" t="s">
+        <v>463</v>
+      </c>
+      <c r="C98" s="7" t="s">
         <v>464</v>
-      </c>
-      <c r="C98" s="7" t="s">
-        <v>465</v>
       </c>
     </row>
     <row r="99" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A99" s="12" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B99" s="7" t="s">
+        <v>503</v>
+      </c>
+      <c r="C99" s="7" t="s">
         <v>504</v>
-      </c>
-      <c r="C99" s="7" t="s">
-        <v>505</v>
       </c>
     </row>
     <row r="100" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A100" s="12" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B100" s="7" t="s">
+        <v>517</v>
+      </c>
+      <c r="C100" s="7" t="s">
         <v>518</v>
-      </c>
-      <c r="C100" s="7" t="s">
-        <v>519</v>
       </c>
     </row>
     <row r="101" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A101" s="12" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B101" s="7" t="s">
+        <v>471</v>
+      </c>
+      <c r="C101" s="7" t="s">
         <v>472</v>
-      </c>
-      <c r="C101" s="7" t="s">
-        <v>473</v>
       </c>
     </row>
     <row r="102" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A102" s="12" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B102" s="7" t="s">
+        <v>461</v>
+      </c>
+      <c r="C102" s="7" t="s">
         <v>462</v>
-      </c>
-      <c r="C102" s="7" t="s">
-        <v>463</v>
       </c>
     </row>
     <row r="103" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A103" s="12" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B103" s="7" t="s">
+        <v>487</v>
+      </c>
+      <c r="C103" s="7" t="s">
         <v>488</v>
-      </c>
-      <c r="C103" s="7" t="s">
-        <v>489</v>
       </c>
     </row>
     <row r="104" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -39527,7 +39536,7 @@
     </row>
     <row r="129" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A129" s="12" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B129" s="7" t="s">
         <v>18</v>
@@ -39552,10 +39561,10 @@
         <v>372</v>
       </c>
       <c r="B131" s="7" t="s">
+        <v>404</v>
+      </c>
+      <c r="C131" s="7" t="s">
         <v>405</v>
-      </c>
-      <c r="C131" s="7" t="s">
-        <v>406</v>
       </c>
     </row>
     <row r="132" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -39563,10 +39572,10 @@
         <v>372</v>
       </c>
       <c r="B132" s="7" t="s">
+        <v>406</v>
+      </c>
+      <c r="C132" s="7" t="s">
         <v>407</v>
-      </c>
-      <c r="C132" s="7" t="s">
-        <v>408</v>
       </c>
     </row>
     <row r="133" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -39574,10 +39583,10 @@
         <v>372</v>
       </c>
       <c r="B133" s="7" t="s">
+        <v>410</v>
+      </c>
+      <c r="C133" s="7" t="s">
         <v>411</v>
-      </c>
-      <c r="C133" s="7" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="134" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -39585,10 +39594,10 @@
         <v>372</v>
       </c>
       <c r="B134" s="7" t="s">
+        <v>414</v>
+      </c>
+      <c r="C134" s="7" t="s">
         <v>415</v>
-      </c>
-      <c r="C134" s="7" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="135" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -39596,10 +39605,10 @@
         <v>372</v>
       </c>
       <c r="B135" s="7" t="s">
+        <v>432</v>
+      </c>
+      <c r="C135" s="7" t="s">
         <v>433</v>
-      </c>
-      <c r="C135" s="7" t="s">
-        <v>434</v>
       </c>
     </row>
     <row r="136" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -39607,10 +39616,10 @@
         <v>372</v>
       </c>
       <c r="B136" s="7" t="s">
+        <v>436</v>
+      </c>
+      <c r="C136" s="7" t="s">
         <v>437</v>
-      </c>
-      <c r="C136" s="7" t="s">
-        <v>438</v>
       </c>
     </row>
     <row r="137" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -39692,40 +39701,40 @@
     </row>
     <row r="144" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A144" s="12" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B144" s="7" t="s">
+        <v>525</v>
+      </c>
+      <c r="C144" s="7" t="s">
         <v>526</v>
-      </c>
-      <c r="C144" s="7" t="s">
-        <v>527</v>
       </c>
     </row>
     <row r="145" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A145" s="12" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B145" s="7" t="s">
+        <v>532</v>
+      </c>
+      <c r="C145" s="7" t="s">
         <v>533</v>
-      </c>
-      <c r="C145" s="7" t="s">
-        <v>534</v>
       </c>
     </row>
     <row r="146" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A146" s="12" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B146" s="7" t="s">
+        <v>541</v>
+      </c>
+      <c r="C146" s="7" t="s">
         <v>542</v>
-      </c>
-      <c r="C146" s="7" t="s">
-        <v>543</v>
       </c>
     </row>
     <row r="147" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A147" s="3" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B147" s="3" t="s">
         <v>10</v>
@@ -39734,7 +39743,7 @@
     </row>
     <row r="148" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A148" s="3" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B148" s="3" t="s">
         <v>4</v>
@@ -39791,70 +39800,70 @@
         <v>372</v>
       </c>
       <c r="B154" s="3" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C154" s="8"/>
     </row>
     <row r="155" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A155" s="3" t="s">
+        <v>523</v>
+      </c>
+      <c r="B155" s="3" t="s">
         <v>524</v>
-      </c>
-      <c r="B155" s="3" t="s">
-        <v>525</v>
       </c>
       <c r="C155" s="8"/>
     </row>
     <row r="156" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A156" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B156" s="3" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C156" s="8"/>
     </row>
     <row r="157" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A157" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B157" s="3" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="C157" s="8"/>
     </row>
     <row r="158" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A158" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B158" s="3" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="C158" s="8"/>
     </row>
     <row r="159" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A159" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B159" s="3" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="C159" s="8"/>
     </row>
     <row r="160" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A160" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B160" s="3" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="C160" s="8"/>
     </row>
     <row r="161" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A161" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B161" s="3" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="C161" s="8"/>
     </row>
@@ -39863,7 +39872,7 @@
         <v>372</v>
       </c>
       <c r="B162" s="3" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="C162" s="8"/>
     </row>
